--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -506,25 +506,25 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-5999621555.39</v>
+        <v>-11969286612.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-8000000000</v>
+        <v>-8011508504.57</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-59831842.36060165</v>
+        <v>-119364940.4623891</v>
       </c>
       <c r="I2" t="n">
-        <v>-19948979.55720657</v>
+        <v>39469348.8003759</v>
       </c>
       <c r="J2" t="n">
-        <v>-59831842.36060165</v>
+        <v>-119364940.4623891</v>
       </c>
       <c r="K2" t="n">
-        <v>-19948979.55720657</v>
+        <v>39469348.8003759</v>
       </c>
     </row>
     <row r="3">
@@ -545,25 +545,25 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>2175377097.22</v>
+        <v>4214343154.54</v>
       </c>
       <c r="F3" t="n">
-        <v>-400000000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>19940956.72451666</v>
+        <v>38631478.91661666</v>
       </c>
       <c r="I3" t="n">
-        <v>-23607623.39118333</v>
+        <v>-38631478.91661666</v>
       </c>
       <c r="J3" t="n">
-        <v>19940956.72451666</v>
+        <v>38631478.91661666</v>
       </c>
       <c r="K3" t="n">
-        <v>-23607623.39118333</v>
+        <v>-38631478.91661666</v>
       </c>
     </row>
     <row r="4">
@@ -584,25 +584,25 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>10750880995.23</v>
+        <v>21654457449.59</v>
       </c>
       <c r="F4" t="n">
-        <v>-800000000</v>
+        <v>-1888284222.06</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>89590674.96025001</v>
+        <v>180453812.0799167</v>
       </c>
       <c r="I4" t="n">
-        <v>-96257341.62691666</v>
+        <v>-196189513.9304167</v>
       </c>
       <c r="J4" t="n">
-        <v>89590674.96025001</v>
+        <v>180453812.0799167</v>
       </c>
       <c r="K4" t="n">
-        <v>-96257341.62691666</v>
+        <v>-196189513.9304167</v>
       </c>
     </row>
     <row r="5">
@@ -623,25 +623,25 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>6038877197.75</v>
+        <v>11308668299.67</v>
       </c>
       <c r="F5" t="n">
-        <v>-800000000</v>
+        <v>-950368395.63</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>45291578.983125</v>
+        <v>84815012.24752501</v>
       </c>
       <c r="I5" t="n">
-        <v>-51291578.983125</v>
+        <v>-91942775.21474999</v>
       </c>
       <c r="J5" t="n">
-        <v>45291578.983125</v>
+        <v>84815012.24752501</v>
       </c>
       <c r="K5" t="n">
-        <v>-51291578.983125</v>
+        <v>-91942775.21474999</v>
       </c>
     </row>
     <row r="6">
@@ -662,25 +662,25 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>138537078.78</v>
+        <v>287898315.0900002</v>
       </c>
       <c r="F6" t="n">
-        <v>-800000000</v>
+        <v>-937266212.77</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>923580.5252</v>
+        <v>1919322.100600001</v>
       </c>
       <c r="I6" t="n">
-        <v>-6256913.858533333</v>
+        <v>-8167763.519066669</v>
       </c>
       <c r="J6" t="n">
-        <v>923580.5252</v>
+        <v>1919322.100600001</v>
       </c>
       <c r="K6" t="n">
-        <v>-6256913.858533333</v>
+        <v>-8167763.519066669</v>
       </c>
     </row>
     <row r="7">
@@ -701,25 +701,25 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>2293685276.16</v>
+        <v>4592568652.700001</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-933556315.13</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>13379830.7776</v>
+        <v>26789983.80741667</v>
       </c>
       <c r="I7" t="n">
-        <v>-13379830.7776</v>
+        <v>-32235728.97900834</v>
       </c>
       <c r="J7" t="n">
-        <v>13379830.7776</v>
+        <v>26789983.80741667</v>
       </c>
       <c r="K7" t="n">
-        <v>-13379830.7776</v>
+        <v>-32235728.97900834</v>
       </c>
     </row>
     <row r="8">
@@ -740,25 +740,25 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6994820480.68</v>
+        <v>14895344121.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-400000000</v>
+        <v>-534184986.24</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>34974102.4034</v>
+        <v>74476720.60875</v>
       </c>
       <c r="I8" t="n">
-        <v>-36974102.4034</v>
+        <v>-77147645.53995</v>
       </c>
       <c r="J8" t="n">
-        <v>34974102.4034</v>
+        <v>74476720.60875</v>
       </c>
       <c r="K8" t="n">
-        <v>-36974102.4034</v>
+        <v>-77147645.53995</v>
       </c>
     </row>
     <row r="9">
@@ -779,25 +779,25 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-1132468695.5</v>
+        <v>-2265065811.22</v>
       </c>
       <c r="F9" t="n">
-        <v>-400000000</v>
+        <v>-522253278.41</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-4718619.564583333</v>
+        <v>-9437774.213416666</v>
       </c>
       <c r="I9" t="n">
-        <v>3051952.897916666</v>
+        <v>7261718.886708331</v>
       </c>
       <c r="J9" t="n">
-        <v>-4718619.564583333</v>
+        <v>-9437774.213416666</v>
       </c>
       <c r="K9" t="n">
-        <v>3051952.897916666</v>
+        <v>7261718.886708331</v>
       </c>
     </row>
     <row r="10">
@@ -818,25 +818,25 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-826591809.5599999</v>
+        <v>-1653631904.25</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-512692413.08</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-2755306.031866667</v>
+        <v>-5512106.347500001</v>
       </c>
       <c r="I10" t="n">
-        <v>2755306.031866667</v>
+        <v>3803131.637233334</v>
       </c>
       <c r="J10" t="n">
-        <v>-2755306.031866667</v>
+        <v>-5512106.347500001</v>
       </c>
       <c r="K10" t="n">
-        <v>2755306.031866667</v>
+        <v>3803131.637233334</v>
       </c>
     </row>
     <row r="11">
@@ -857,25 +857,25 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-479933073.1900001</v>
+        <v>-1103413874.16</v>
       </c>
       <c r="F11" t="n">
-        <v>-400000000</v>
+        <v>-522547792.53</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-1199832.682975</v>
+        <v>-2758534.6854</v>
       </c>
       <c r="I11" t="n">
-        <v>199832.6829750001</v>
+        <v>1452165.204075</v>
       </c>
       <c r="J11" t="n">
-        <v>-1199832.682975</v>
+        <v>-2758534.6854</v>
       </c>
       <c r="K11" t="n">
-        <v>199832.6829750001</v>
+        <v>1452165.204075</v>
       </c>
     </row>
     <row r="12">
@@ -896,25 +896,25 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-818538934.8799999</v>
+        <v>-1617508459.13</v>
       </c>
       <c r="F12" t="n">
-        <v>-400000000</v>
+        <v>-516937918.48</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-1364231.558133333</v>
+        <v>-2695847.431883333</v>
       </c>
       <c r="I12" t="n">
-        <v>697564.8914666664</v>
+        <v>1834284.234416666</v>
       </c>
       <c r="J12" t="n">
-        <v>-1364231.558133333</v>
+        <v>-2695847.431883333</v>
       </c>
       <c r="K12" t="n">
-        <v>697564.8914666664</v>
+        <v>1834284.234416666</v>
       </c>
     </row>
     <row r="13">
@@ -935,25 +935,25 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-811840769.16</v>
+        <v>-1623521087.52</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-503998763.6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-676533.9743000002</v>
+        <v>-1352934.239600001</v>
       </c>
       <c r="I13" t="n">
-        <v>676533.9743000002</v>
+        <v>932935.2699333339</v>
       </c>
       <c r="J13" t="n">
-        <v>-676533.9743000002</v>
+        <v>-1352934.239600001</v>
       </c>
       <c r="K13" t="n">
-        <v>676533.9743000002</v>
+        <v>932935.2699333339</v>
       </c>
     </row>
     <row r="14">
@@ -974,10 +974,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-434460589.52</v>
+        <v>-1146624337.12</v>
       </c>
       <c r="F14" t="n">
-        <v>-400000000</v>
+        <v>-520727333.41</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17888722698.62</v>
+        <v>35574227907.64</v>
       </c>
       <c r="C2" t="n">
-        <v>-12800000000</v>
+        <v>-16354326135.91</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>133554358.2016317</v>
+        <v>265964192.380636</v>
       </c>
       <c r="F2" t="n">
-        <v>-240335180.1194399</v>
+        <v>-389561322.0670658</v>
       </c>
       <c r="G2" t="n">
-        <v>133554358.2016317</v>
+        <v>265964192.380636</v>
       </c>
       <c r="H2" t="n">
-        <v>-240335180.1194399</v>
+        <v>-389561322.0670658</v>
       </c>
     </row>
   </sheetData>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1635690752.42</v>
+        <v>-3271381504.99</v>
       </c>
       <c r="D2" t="n">
-        <v>-551041892.6027397</v>
+        <v>-1102083785.205479</v>
       </c>
       <c r="E2" t="n">
-        <v>-2186732645.02274</v>
+        <v>-4373465290.195479</v>
       </c>
     </row>
     <row r="3">
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>891224973.27</v>
+        <v>1772042953.29</v>
       </c>
       <c r="D3" t="n">
-        <v>52385409.72</v>
+        <v>102556093.5293151</v>
       </c>
       <c r="E3" t="n">
-        <v>943610382.99</v>
+        <v>1874599046.819315</v>
       </c>
     </row>
     <row r="4">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1602040037.16</v>
+        <v>3196426808.51</v>
       </c>
       <c r="D4" t="n">
-        <v>168754858.2541759</v>
+        <v>337567414.8186869</v>
       </c>
       <c r="E4" t="n">
-        <v>1770794895.414176</v>
+        <v>3533994223.328687</v>
       </c>
     </row>
   </sheetData>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>857574258.01</v>
+        <v>1697088256.81</v>
       </c>
       <c r="C2" t="n">
-        <v>-329901624.6285638</v>
+        <v>-661960276.8574774</v>
       </c>
       <c r="D2" t="n">
-        <v>527672633.3814361</v>
+        <v>1035127979.952522</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -545,25 +545,25 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>4214343154.54</v>
+        <v>16458155778.43</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-948926786.59</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>38631478.91661666</v>
+        <v>150866427.9689417</v>
       </c>
       <c r="I3" t="n">
-        <v>-38631478.91661666</v>
+        <v>-159564923.5126833</v>
       </c>
       <c r="J3" t="n">
-        <v>38631478.91661666</v>
+        <v>150866427.9689417</v>
       </c>
       <c r="K3" t="n">
-        <v>-38631478.91661666</v>
+        <v>-159564923.5126833</v>
       </c>
     </row>
     <row r="4">
@@ -584,25 +584,25 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>21654457449.59</v>
+        <v>9948663064.66</v>
       </c>
       <c r="F4" t="n">
-        <v>-1888284222.06</v>
+        <v>-939357435.47</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>180453812.0799167</v>
+        <v>82905525.53883334</v>
       </c>
       <c r="I4" t="n">
-        <v>-196189513.9304167</v>
+        <v>-90733504.16775</v>
       </c>
       <c r="J4" t="n">
-        <v>180453812.0799167</v>
+        <v>82905525.53883334</v>
       </c>
       <c r="K4" t="n">
-        <v>-196189513.9304167</v>
+        <v>-90733504.16775</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +623,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>11308668299.67</v>
+        <v>11099174132.28</v>
       </c>
       <c r="F5" t="n">
         <v>-950368395.63</v>
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>84815012.24752501</v>
+        <v>83243805.9921</v>
       </c>
       <c r="I5" t="n">
-        <v>-91942775.21474999</v>
+        <v>-90371568.95932499</v>
       </c>
       <c r="J5" t="n">
-        <v>84815012.24752501</v>
+        <v>83243805.9921</v>
       </c>
       <c r="K5" t="n">
-        <v>-91942775.21474999</v>
+        <v>-90371568.95932499</v>
       </c>
     </row>
     <row r="6">
@@ -662,7 +662,7 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>287898315.0900002</v>
+        <v>3589192236.5</v>
       </c>
       <c r="F6" t="n">
         <v>-937266212.77</v>
@@ -671,16 +671,16 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1919322.100600001</v>
+        <v>23927948.24333334</v>
       </c>
       <c r="I6" t="n">
-        <v>-8167763.519066669</v>
+        <v>-30176389.6618</v>
       </c>
       <c r="J6" t="n">
-        <v>1919322.100600001</v>
+        <v>23927948.24333334</v>
       </c>
       <c r="K6" t="n">
-        <v>-8167763.519066669</v>
+        <v>-30176389.6618</v>
       </c>
     </row>
     <row r="7">
@@ -701,7 +701,7 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>4592568652.700001</v>
+        <v>1292202215.83</v>
       </c>
       <c r="F7" t="n">
         <v>-933556315.13</v>
@@ -710,16 +710,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>26789983.80741667</v>
+        <v>7537846.259008332</v>
       </c>
       <c r="I7" t="n">
-        <v>-32235728.97900834</v>
+        <v>-12983591.4306</v>
       </c>
       <c r="J7" t="n">
-        <v>26789983.80741667</v>
+        <v>7537846.259008332</v>
       </c>
       <c r="K7" t="n">
-        <v>-32235728.97900834</v>
+        <v>-12983591.4306</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>14895344121.75</v>
+        <v>14731847447.54</v>
       </c>
       <c r="F8" t="n">
         <v>-534184986.24</v>
@@ -749,16 +749,16 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>74476720.60875</v>
+        <v>73659237.2377</v>
       </c>
       <c r="I8" t="n">
-        <v>-77147645.53995</v>
+        <v>-76330162.1689</v>
       </c>
       <c r="J8" t="n">
-        <v>74476720.60875</v>
+        <v>73659237.2377</v>
       </c>
       <c r="K8" t="n">
-        <v>-77147645.53995</v>
+        <v>-76330162.1689</v>
       </c>
     </row>
     <row r="9">
@@ -779,7 +779,7 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-2265065811.22</v>
+        <v>-2289519782.09</v>
       </c>
       <c r="F9" t="n">
         <v>-522253278.41</v>
@@ -788,16 +788,16 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-9437774.213416666</v>
+        <v>-9539665.758708332</v>
       </c>
       <c r="I9" t="n">
-        <v>7261718.886708331</v>
+        <v>7363610.431999998</v>
       </c>
       <c r="J9" t="n">
-        <v>-9437774.213416666</v>
+        <v>-9539665.758708332</v>
       </c>
       <c r="K9" t="n">
-        <v>7261718.886708331</v>
+        <v>7363610.431999998</v>
       </c>
     </row>
     <row r="10">
@@ -818,7 +818,7 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-1653631904.25</v>
+        <v>-1632583477.45</v>
       </c>
       <c r="F10" t="n">
         <v>-512692413.08</v>
@@ -827,16 +827,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-5512106.347500001</v>
+        <v>-5441944.924833334</v>
       </c>
       <c r="I10" t="n">
-        <v>3803131.637233334</v>
+        <v>3732970.214566668</v>
       </c>
       <c r="J10" t="n">
-        <v>-5512106.347500001</v>
+        <v>-5441944.924833334</v>
       </c>
       <c r="K10" t="n">
-        <v>3803131.637233334</v>
+        <v>3732970.214566668</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-1103413874.16</v>
+        <v>-1062307276.65</v>
       </c>
       <c r="F11" t="n">
         <v>-522547792.53</v>
@@ -866,16 +866,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-2758534.6854</v>
+        <v>-2655768.191625</v>
       </c>
       <c r="I11" t="n">
-        <v>1452165.204075</v>
+        <v>1349398.7103</v>
       </c>
       <c r="J11" t="n">
-        <v>-2758534.6854</v>
+        <v>-2655768.191625</v>
       </c>
       <c r="K11" t="n">
-        <v>1452165.204075</v>
+        <v>1349398.7103</v>
       </c>
     </row>
     <row r="12">
@@ -896,7 +896,7 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-1617508459.13</v>
+        <v>-1673310261.43</v>
       </c>
       <c r="F12" t="n">
         <v>-516937918.48</v>
@@ -905,16 +905,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-2695847.431883333</v>
+        <v>-2788850.435716666</v>
       </c>
       <c r="I12" t="n">
-        <v>1834284.234416666</v>
+        <v>1927287.23825</v>
       </c>
       <c r="J12" t="n">
-        <v>-2695847.431883333</v>
+        <v>-2788850.435716666</v>
       </c>
       <c r="K12" t="n">
-        <v>1834284.234416666</v>
+        <v>1927287.23825</v>
       </c>
     </row>
     <row r="13">
@@ -935,7 +935,7 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-1623521087.52</v>
+        <v>-1603690311.79</v>
       </c>
       <c r="F13" t="n">
         <v>-503998763.6</v>
@@ -944,16 +944,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-1352934.239600001</v>
+        <v>-1336408.593158334</v>
       </c>
       <c r="I13" t="n">
-        <v>932935.2699333339</v>
+        <v>916409.6234916671</v>
       </c>
       <c r="J13" t="n">
-        <v>-1352934.239600001</v>
+        <v>-1336408.593158334</v>
       </c>
       <c r="K13" t="n">
-        <v>932935.2699333339</v>
+        <v>916409.6234916671</v>
       </c>
     </row>
     <row r="14">
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-1146624337.12</v>
+        <v>-1067621671.08</v>
       </c>
       <c r="F14" t="n">
         <v>-520727333.41</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35574227907.64</v>
+        <v>35820915482.45</v>
       </c>
       <c r="C2" t="n">
         <v>-16354326135.91</v>
@@ -1067,16 +1067,16 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>265964192.380636</v>
+        <v>281013212.8734859</v>
       </c>
       <c r="F2" t="n">
-        <v>-389561322.0670658</v>
+        <v>-405401114.8820741</v>
       </c>
       <c r="G2" t="n">
-        <v>265964192.380636</v>
+        <v>281013212.8734859</v>
       </c>
       <c r="H2" t="n">
-        <v>-389561322.0670658</v>
+        <v>-405401114.8820741</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -11,6 +11,8 @@
     <sheet name="NII_simple_summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="NII_base_detail" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="NII_base_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NII_shocked_detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NII_shocked_summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,63 +418,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tenor_bucket</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tenor_yf</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>remain_yf</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>net_gap_cf</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>net_ca_gap_cf</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>nii_base</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>nii_up_100bps</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>nii_dn_100bps</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>delta_nii_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>delta_nii_dn</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>gap_cf</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>gap_cf_ca</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_gap_without_ca</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>gap_cf_irs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_gap_with_irs</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>net_gap_with_irs_no_ca</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>d_nii_up_100_no_swap</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>d_nii_dn_100_no_swap</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>d_nii_up_100_with_swap</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>d_nii_dn_100_with_swap</t>
         </is>
       </c>
     </row>
@@ -506,25 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-11969286612.3</v>
+        <v>-1011745289.03</v>
       </c>
       <c r="F2" t="n">
-        <v>-8011508504.57</v>
+        <v>-720000000</v>
       </c>
       <c r="G2" t="n">
+        <v>-291745289.0300001</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>-119364940.4623891</v>
-      </c>
       <c r="I2" t="n">
-        <v>39469348.8003759</v>
+        <v>-1011745289.03</v>
       </c>
       <c r="J2" t="n">
-        <v>-119364940.4623891</v>
+        <v>-291745289.0300001</v>
       </c>
       <c r="K2" t="n">
-        <v>39469348.8003759</v>
+        <v>-10089733.84128548</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2909459.868682741</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-10089733.84128548</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2909459.868682741</v>
       </c>
     </row>
     <row r="3">
@@ -545,25 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>16458155778.43</v>
+        <v>483885792.13</v>
       </c>
       <c r="F3" t="n">
-        <v>-948926786.59</v>
+        <v>-72000000</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>555885792.13</v>
       </c>
       <c r="H3" t="n">
-        <v>150866427.9689417</v>
+        <v>-254676093.9591287</v>
       </c>
       <c r="I3" t="n">
-        <v>-159564923.5126833</v>
+        <v>229209698.1708713</v>
       </c>
       <c r="J3" t="n">
-        <v>150866427.9689417</v>
+        <v>301209698.1708713</v>
       </c>
       <c r="K3" t="n">
-        <v>-159564923.5126833</v>
+        <v>4435619.761191667</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-5095619.761191667</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2101088.899899654</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-2761088.899899654</v>
       </c>
     </row>
     <row r="4">
@@ -584,25 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>9948663064.66</v>
+        <v>2095460944.63</v>
       </c>
       <c r="F4" t="n">
-        <v>-939357435.47</v>
+        <v>-72000000</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2167460944.63</v>
       </c>
       <c r="H4" t="n">
-        <v>82905525.53883334</v>
+        <v>-352958621.154278</v>
       </c>
       <c r="I4" t="n">
-        <v>-90733504.16775</v>
+        <v>1742502323.475722</v>
       </c>
       <c r="J4" t="n">
-        <v>82905525.53883334</v>
+        <v>1814502323.475722</v>
       </c>
       <c r="K4" t="n">
-        <v>-90733504.16775</v>
+        <v>17462174.53858333</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-18062174.53858333</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14520852.69563102</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-15120852.69563102</v>
       </c>
     </row>
     <row r="5">
@@ -623,25 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>11099174132.28</v>
+        <v>339348271.12</v>
       </c>
       <c r="F5" t="n">
-        <v>-950368395.63</v>
+        <v>-72000000</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>411348271.12</v>
       </c>
       <c r="H5" t="n">
-        <v>83243805.9921</v>
+        <v>-499914075.7916012</v>
       </c>
       <c r="I5" t="n">
-        <v>-90371568.95932499</v>
+        <v>-160565804.6716012</v>
       </c>
       <c r="J5" t="n">
-        <v>83243805.9921</v>
+        <v>-88565804.67160118</v>
       </c>
       <c r="K5" t="n">
-        <v>-90371568.95932499</v>
+        <v>2545112.0334</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-3085112.0334</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1204243.535037009</v>
+      </c>
+      <c r="N5" t="n">
+        <v>664243.5350370088</v>
       </c>
     </row>
     <row r="6">
@@ -662,25 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>3589192236.5</v>
+        <v>57575606.97999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-937266212.77</v>
+        <v>-72000000</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>129575606.98</v>
       </c>
       <c r="H6" t="n">
-        <v>23927948.24333334</v>
+        <v>-149884271.2777902</v>
       </c>
       <c r="I6" t="n">
-        <v>-30176389.6618</v>
+        <v>-92308664.29779026</v>
       </c>
       <c r="J6" t="n">
-        <v>23927948.24333334</v>
+        <v>-20308664.29779026</v>
       </c>
       <c r="K6" t="n">
-        <v>-30176389.6618</v>
+        <v>383837.3798666667</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-863837.3798666667</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-615391.0953186018</v>
+      </c>
+      <c r="N6" t="n">
+        <v>135391.0953186018</v>
       </c>
     </row>
     <row r="7">
@@ -701,25 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>1292202215.83</v>
+        <v>504177160.38</v>
       </c>
       <c r="F7" t="n">
-        <v>-933556315.13</v>
+        <v>-72000000</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>576177160.38</v>
       </c>
       <c r="H7" t="n">
-        <v>7537846.259008332</v>
+        <v>-149844342.9148888</v>
       </c>
       <c r="I7" t="n">
-        <v>-12983591.4306</v>
+        <v>354332817.4651111</v>
       </c>
       <c r="J7" t="n">
-        <v>7537846.259008332</v>
+        <v>426332817.4651111</v>
       </c>
       <c r="K7" t="n">
-        <v>-12983591.4306</v>
+        <v>2941033.43555</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3361033.43555</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2066941.435213148</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-2486941.435213148</v>
       </c>
     </row>
     <row r="8">
@@ -740,25 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>14731847447.54</v>
+        <v>860652466.8900001</v>
       </c>
       <c r="F8" t="n">
-        <v>-534184986.24</v>
+        <v>-36000000</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>896652466.8900001</v>
       </c>
       <c r="H8" t="n">
-        <v>73659237.2377</v>
+        <v>-154346876.7123288</v>
       </c>
       <c r="I8" t="n">
-        <v>-76330162.1689</v>
+        <v>706305590.1776713</v>
       </c>
       <c r="J8" t="n">
-        <v>73659237.2377</v>
+        <v>742305590.1776713</v>
       </c>
       <c r="K8" t="n">
-        <v>-76330162.1689</v>
+        <v>4303262.334450001</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-4483262.334450001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3531527.950888357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-3711527.950888357</v>
       </c>
     </row>
     <row r="9">
@@ -779,25 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-2289519782.09</v>
+        <v>-195816900.17</v>
       </c>
       <c r="F9" t="n">
-        <v>-522253278.41</v>
+        <v>-36000000</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-159816900.17</v>
       </c>
       <c r="H9" t="n">
-        <v>-9539665.758708332</v>
+        <v>90336829.10397485</v>
       </c>
       <c r="I9" t="n">
-        <v>7363610.431999998</v>
+        <v>-105480071.0660252</v>
       </c>
       <c r="J9" t="n">
-        <v>-9539665.758708332</v>
+        <v>-69480071.06602517</v>
       </c>
       <c r="K9" t="n">
-        <v>7363610.431999998</v>
+        <v>-815903.7507083333</v>
+      </c>
+      <c r="L9" t="n">
+        <v>665903.7507083333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-439500.2961084382</v>
+      </c>
+      <c r="N9" t="n">
+        <v>289500.2961084382</v>
       </c>
     </row>
     <row r="10">
@@ -818,25 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-1632583477.45</v>
+        <v>-134836161.42</v>
       </c>
       <c r="F10" t="n">
-        <v>-512692413.08</v>
+        <v>-36000000</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-98836161.42000002</v>
       </c>
       <c r="H10" t="n">
-        <v>-5441944.924833334</v>
+        <v>6798456.09701325</v>
       </c>
       <c r="I10" t="n">
-        <v>3732970.214566668</v>
+        <v>-128037705.3229868</v>
       </c>
       <c r="J10" t="n">
-        <v>-5441944.924833334</v>
+        <v>-92037705.32298677</v>
       </c>
       <c r="K10" t="n">
-        <v>3732970.214566668</v>
+        <v>-449453.8714000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>329453.8714000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-426792.3510766226</v>
+      </c>
+      <c r="N10" t="n">
+        <v>306792.3510766226</v>
       </c>
     </row>
     <row r="11">
@@ -857,25 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-1062307276.65</v>
+        <v>23489211.14000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-522547792.53</v>
+        <v>-36000000</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>59489211.14000002</v>
       </c>
       <c r="H11" t="n">
-        <v>-2655768.191625</v>
+        <v>106004406.5798338</v>
       </c>
       <c r="I11" t="n">
-        <v>1349398.7103</v>
+        <v>129493617.7198338</v>
       </c>
       <c r="J11" t="n">
-        <v>-2655768.191625</v>
+        <v>165493617.7198339</v>
       </c>
       <c r="K11" t="n">
-        <v>1349398.7103</v>
+        <v>58723.02785000004</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-148723.02785</v>
+      </c>
+      <c r="M11" t="n">
+        <v>323734.0442995846</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-413734.0442995846</v>
       </c>
     </row>
     <row r="12">
@@ -896,25 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-1673310261.43</v>
+        <v>-135044007.53</v>
       </c>
       <c r="F12" t="n">
-        <v>-516937918.48</v>
+        <v>-36000000</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-99044007.53</v>
       </c>
       <c r="H12" t="n">
-        <v>-2788850.435716666</v>
+        <v>6746058.836739277</v>
       </c>
       <c r="I12" t="n">
-        <v>1927287.23825</v>
+        <v>-128297948.6932607</v>
       </c>
       <c r="J12" t="n">
-        <v>-2788850.435716666</v>
+        <v>-92297948.69326073</v>
       </c>
       <c r="K12" t="n">
-        <v>1927287.23825</v>
+        <v>-225073.3458833333</v>
+      </c>
+      <c r="L12" t="n">
+        <v>165073.3458833333</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-213829.9144887679</v>
+      </c>
+      <c r="N12" t="n">
+        <v>153829.9144887679</v>
       </c>
     </row>
     <row r="13">
@@ -935,25 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-1603690311.79</v>
+        <v>-134211468.78</v>
       </c>
       <c r="F13" t="n">
-        <v>-503998763.6</v>
+        <v>-36000000</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-98211468.77999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-1336408.593158334</v>
+        <v>6784611.497866606</v>
       </c>
       <c r="I13" t="n">
-        <v>916409.6234916671</v>
+        <v>-127426857.2821334</v>
       </c>
       <c r="J13" t="n">
-        <v>-1336408.593158334</v>
+        <v>-91426857.28213339</v>
       </c>
       <c r="K13" t="n">
-        <v>916409.6234916671</v>
+        <v>-111842.89065</v>
+      </c>
+      <c r="L13" t="n">
+        <v>81842.89065000002</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-106189.0477351112</v>
+      </c>
+      <c r="N13" t="n">
+        <v>76189.04773511119</v>
       </c>
     </row>
     <row r="14">
@@ -974,24 +1087,33 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-1067621671.08</v>
+        <v>-109342407.55</v>
       </c>
       <c r="F14" t="n">
-        <v>-520727333.41</v>
+        <v>-36000000</v>
       </c>
       <c r="G14" t="n">
+        <v>-73342407.55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13498282.0570402</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-95844125.4929598</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-59844125.4929598</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
+      <c r="M14" t="n">
         <v>-0</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1006,48 +1128,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>net_gap_cf</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>net_ca_gap_cf</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nii_base</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nii_up_100bps</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>nii_dn_100bps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>delta_nii_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>delta_nii_dn</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>d_nii_up_100_no_swap</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>d_nii_dn_100_no_swap</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>d_nii_up_100_with_swap</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>d_nii_dn_100_with_swap</t>
         </is>
       </c>
     </row>
@@ -1058,25 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35820915482.45</v>
+        <v>20437754.81096452</v>
       </c>
       <c r="C2" t="n">
-        <v>-16354326135.91</v>
+        <v>-30948028.78356726</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>9448464.944881732</v>
       </c>
       <c r="E2" t="n">
-        <v>281013212.8734859</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-405401114.8820741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>281013212.8734859</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-405401114.8820741</v>
+        <v>-19958738.91748447</v>
       </c>
     </row>
   </sheetData>
@@ -1094,27 +1192,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nii_interest</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>nii_renewal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nii_total</t>
         </is>
@@ -1132,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-3271381504.99</v>
+        <v>-123330404.73</v>
       </c>
       <c r="D2" t="n">
-        <v>-1102083785.205479</v>
+        <v>-97064491.28421247</v>
       </c>
       <c r="E2" t="n">
-        <v>-4373465290.195479</v>
+        <v>-220394896.0142125</v>
       </c>
     </row>
     <row r="3">
@@ -1153,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1772042953.29</v>
+        <v>108001745.88</v>
       </c>
       <c r="D3" t="n">
-        <v>102556093.5293151</v>
+        <v>3759129.314246576</v>
       </c>
       <c r="E3" t="n">
-        <v>1874599046.819315</v>
+        <v>111760875.1942466</v>
       </c>
     </row>
     <row r="4">
@@ -1174,13 +1272,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3196426808.51</v>
+        <v>572028977.8</v>
       </c>
       <c r="D4" t="n">
-        <v>337567414.8186869</v>
+        <v>30647795.06400019</v>
       </c>
       <c r="E4" t="n">
-        <v>3533994223.328687</v>
+        <v>602676772.8640002</v>
       </c>
     </row>
   </sheetData>
@@ -1198,22 +1296,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nii_interest</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nii_renewal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>nii_total</t>
         </is>
@@ -1226,13 +1324,2027 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1697088256.81</v>
+        <v>556700318.9499999</v>
       </c>
       <c r="C2" t="n">
-        <v>-661960276.8574774</v>
+        <v>-62657566.9059657</v>
       </c>
       <c r="D2" t="n">
-        <v>1035127979.952522</v>
+        <v>494042752.0440343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rate_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nii_interest</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nii_renewal</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>nii_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>delta_nii</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-88440256.50779517</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-39103316.21761597</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-127543572.7254111</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-127543572.7254111</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F5" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20285044.45110441</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1798622.303601288</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18486422.14750312</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>18486422.14750312</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F7" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>283983021.7546195</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23768398.55035754</v>
+      </c>
+      <c r="F8" t="n">
+        <v>307751420.304977</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>307751420.304977</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-33004509.66453836</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-14298083.33721216</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-47302593.00175052</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>-47302593.00175052</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F12" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7636691.405344562</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-654696.5183792791</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6981994.886965282</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6981994.886965282</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F14" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>105636598.280187</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9082094.487427209</v>
+      </c>
+      <c r="F15" t="n">
+        <v>114718692.7676142</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>114718692.7676142</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-59714618.06673019</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-18422606.22633189</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-78137224.29306208</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>-78137224.29306208</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F19" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13027119.3379819</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1264828.159439856</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11762291.17854204</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>11762291.17854204</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F21" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>194799829.7953675</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14945808.62942155</v>
+      </c>
+      <c r="F22" t="n">
+        <v>209745638.424789</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>209745638.424789</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-65498956.1715795</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-37327429.93962904</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-102826386.1112086</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>-102826386.1112086</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F26" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>15750637.86348905</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1254938.038150794</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14495699.82533826</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>14495699.82533826</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F28" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>206670081.1717829</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19003749.12332492</v>
+      </c>
+      <c r="F29" t="n">
+        <v>225673830.2951078</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>225673830.2951078</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-76108285.75487417</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-41155499.7907265</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-117263785.5456007</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>-117263785.5456007</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F33" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>18104123.06561163</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1481715.503231204</v>
+      </c>
+      <c r="F34" t="n">
+        <v>16622407.56238043</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>16622407.56238043</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F35" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>241180594.3495923</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21673258.63299607</v>
+      </c>
+      <c r="F36" t="n">
+        <v>262853852.9825884</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>262853852.9825884</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-45305017.78653013</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-12244015.25673077</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-57549033.0432609</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>-57549033.0432609</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F40" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9776813.2234874</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-965895.138161672</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8810918.085325729</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>8810918.085325729</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F42" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>148328362.9040446</v>
+      </c>
+      <c r="E43" t="n">
+        <v>11171524.55952817</v>
+      </c>
+      <c r="F43" t="n">
+        <v>159499887.4635728</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>159499887.4635728</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-83834121.54000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-11473502.60729568</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>-95307624.14729567</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>deposits</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-49611311.26421505</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-21735501.23588518</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-71346812.50010024</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>-71346812.50010024</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>76690534.49000001</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2253869.435616439</v>
+      </c>
+      <c r="F47" t="n">
+        <v>78944403.92561644</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>78944403.92561644</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fin_inst</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11398282.87246964</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-994870.2075526081</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10403412.66491704</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>10403412.66491704</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>183462781.77</v>
+      </c>
+      <c r="E49" t="n">
+        <v>19499123.76947068</v>
+      </c>
+      <c r="F49" t="n">
+        <v>202961905.5394707</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>202961905.5394707</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>loans</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>159062516.7739767</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13481615.06219128</v>
+      </c>
+      <c r="F50" t="n">
+        <v>172544131.836168</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>172544131.836168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nii_interest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nii_renewal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nii_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delta_nii</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sot_nii_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>delta_nii_reg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sot_nii_pct_reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>392147004.4179287</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-6854049.373068273</v>
+      </c>
+      <c r="D2" t="n">
+        <v>385292955.0448604</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-108749796.9991739</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-9.062483083264491</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-108749796.9991739</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-9.062483083264491</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>256587974.7409933</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4408805.229627218</v>
+      </c>
+      <c r="D3" t="n">
+        <v>260996779.9706205</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-233045972.0734138</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-19.42049767278449</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-233045972.0734138</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-19.42049767278449</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>324431525.7866192</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5537864.841441255</v>
+      </c>
+      <c r="D4" t="n">
+        <v>329969390.6280605</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-164073361.4159738</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-13.67278011799782</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-164073361.4159738</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-13.67278011799782</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>333240957.5836925</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-9299128.256663471</v>
+      </c>
+      <c r="D5" t="n">
+        <v>323941829.327029</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-170100922.7170053</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-14.17507689308378</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-170100922.7170053</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-14.17507689308378</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>359495626.3803298</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-10684466.06317019</v>
+      </c>
+      <c r="D6" t="n">
+        <v>348811160.3171597</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-145231591.7268746</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-12.10263264390622</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-145231591.7268746</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-12.10263264390622</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>289119353.0610019</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8241104.762427175</v>
+      </c>
+      <c r="D7" t="n">
+        <v>297360457.823429</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-196682294.2206053</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-16.39019118505044</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-196682294.2206053</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-16.39019118505044</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>297168683.1022313</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1030734.21654493</v>
+      </c>
+      <c r="D8" t="n">
+        <v>298199417.3187762</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-195843334.7252581</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-16.3202778937715</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-195843334.7252581</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-16.3202778937715</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1011745289.03</v>
+        <v>-939442484.0499998</v>
       </c>
       <c r="F2" t="n">
-        <v>-720000000</v>
+        <v>-640000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-291745289.0300001</v>
+        <v>-299442484.0499998</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1011745289.03</v>
+        <v>-939442484.0499998</v>
       </c>
       <c r="J2" t="n">
-        <v>-291745289.0300001</v>
+        <v>-299442484.0499998</v>
       </c>
       <c r="K2" t="n">
-        <v>-10089733.84128548</v>
+        <v>-9368686.690252054</v>
       </c>
       <c r="L2" t="n">
-        <v>2909459.868682741</v>
+        <v>2986220.936827396</v>
       </c>
       <c r="M2" t="n">
-        <v>-10089733.84128548</v>
+        <v>-9368686.690252054</v>
       </c>
       <c r="N2" t="n">
-        <v>2909459.868682741</v>
+        <v>2986220.936827396</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>483885792.13</v>
+        <v>575699100.39</v>
       </c>
       <c r="F3" t="n">
-        <v>-72000000</v>
+        <v>-64000000</v>
       </c>
       <c r="G3" t="n">
-        <v>555885792.13</v>
+        <v>639699100.39</v>
       </c>
       <c r="H3" t="n">
-        <v>-254676093.9591287</v>
+        <v>-555063100.8309005</v>
       </c>
       <c r="I3" t="n">
-        <v>229209698.1708713</v>
+        <v>20635999.55909944</v>
       </c>
       <c r="J3" t="n">
-        <v>301209698.1708713</v>
+        <v>84635999.55909944</v>
       </c>
       <c r="K3" t="n">
-        <v>4435619.761191667</v>
+        <v>5277241.753575</v>
       </c>
       <c r="L3" t="n">
-        <v>-5095619.761191667</v>
+        <v>-5863908.420241666</v>
       </c>
       <c r="M3" t="n">
-        <v>2101088.899899654</v>
+        <v>189163.3292917448</v>
       </c>
       <c r="N3" t="n">
-        <v>-2761088.899899654</v>
+        <v>-775829.9959584115</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>2095460944.63</v>
+        <v>1961135371.76</v>
       </c>
       <c r="F4" t="n">
-        <v>-72000000</v>
+        <v>-64000000</v>
       </c>
       <c r="G4" t="n">
-        <v>2167460944.63</v>
+        <v>2025135371.76</v>
       </c>
       <c r="H4" t="n">
-        <v>-352958621.154278</v>
+        <v>-507481570.8511116</v>
       </c>
       <c r="I4" t="n">
-        <v>1742502323.475722</v>
+        <v>1453653800.908888</v>
       </c>
       <c r="J4" t="n">
-        <v>1814502323.475722</v>
+        <v>1517653800.908888</v>
       </c>
       <c r="K4" t="n">
-        <v>17462174.53858333</v>
+        <v>16342794.76466667</v>
       </c>
       <c r="L4" t="n">
-        <v>-18062174.53858333</v>
+        <v>-16876128.098</v>
       </c>
       <c r="M4" t="n">
-        <v>14520852.69563102</v>
+        <v>12113781.67424074</v>
       </c>
       <c r="N4" t="n">
-        <v>-15120852.69563102</v>
+        <v>-12647115.00757407</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>339348271.12</v>
+        <v>531970690.13</v>
       </c>
       <c r="F5" t="n">
-        <v>-72000000</v>
+        <v>-64000000</v>
       </c>
       <c r="G5" t="n">
-        <v>411348271.12</v>
+        <v>595970690.13</v>
       </c>
       <c r="H5" t="n">
-        <v>-499914075.7916012</v>
+        <v>-557976082.4163486</v>
       </c>
       <c r="I5" t="n">
-        <v>-160565804.6716012</v>
+        <v>-26005392.28634858</v>
       </c>
       <c r="J5" t="n">
-        <v>-88565804.67160118</v>
+        <v>37994607.71365142</v>
       </c>
       <c r="K5" t="n">
-        <v>2545112.0334</v>
+        <v>3989780.175975</v>
       </c>
       <c r="L5" t="n">
-        <v>-3085112.0334</v>
+        <v>-4469780.175975</v>
       </c>
       <c r="M5" t="n">
-        <v>-1204243.535037009</v>
+        <v>-195040.4421476144</v>
       </c>
       <c r="N5" t="n">
-        <v>664243.5350370088</v>
+        <v>-284959.5578523856</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>57575606.97999999</v>
+        <v>78498009.31000002</v>
       </c>
       <c r="F6" t="n">
-        <v>-72000000</v>
+        <v>-64000000</v>
       </c>
       <c r="G6" t="n">
-        <v>129575606.98</v>
+        <v>142498009.31</v>
       </c>
       <c r="H6" t="n">
         <v>-149884271.2777902</v>
       </c>
       <c r="I6" t="n">
-        <v>-92308664.29779026</v>
+        <v>-71386261.96779023</v>
       </c>
       <c r="J6" t="n">
-        <v>-20308664.29779026</v>
+        <v>-7386261.967790231</v>
       </c>
       <c r="K6" t="n">
-        <v>383837.3798666667</v>
+        <v>523320.0620666668</v>
       </c>
       <c r="L6" t="n">
-        <v>-863837.3798666667</v>
+        <v>-949986.7287333334</v>
       </c>
       <c r="M6" t="n">
-        <v>-615391.0953186018</v>
+        <v>-475908.4131186016</v>
       </c>
       <c r="N6" t="n">
-        <v>135391.0953186018</v>
+        <v>49241.74645193488</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>504177160.38</v>
+        <v>517889994.42</v>
       </c>
       <c r="F7" t="n">
-        <v>-72000000</v>
+        <v>-64000000</v>
       </c>
       <c r="G7" t="n">
-        <v>576177160.38</v>
+        <v>581889994.42</v>
       </c>
       <c r="H7" t="n">
         <v>-149844342.9148888</v>
       </c>
       <c r="I7" t="n">
-        <v>354332817.4651111</v>
+        <v>368045651.5051111</v>
       </c>
       <c r="J7" t="n">
-        <v>426332817.4651111</v>
+        <v>432045651.5051111</v>
       </c>
       <c r="K7" t="n">
-        <v>2941033.43555</v>
+        <v>3021024.967449999</v>
       </c>
       <c r="L7" t="n">
-        <v>-3361033.43555</v>
+        <v>-3394358.300783333</v>
       </c>
       <c r="M7" t="n">
-        <v>2066941.435213148</v>
+        <v>2146932.967113148</v>
       </c>
       <c r="N7" t="n">
-        <v>-2486941.435213148</v>
+        <v>-2520266.300446481</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>860652466.8900001</v>
+        <v>902503166.1700001</v>
       </c>
       <c r="F8" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G8" t="n">
-        <v>896652466.8900001</v>
+        <v>934503166.1700001</v>
       </c>
       <c r="H8" t="n">
-        <v>-154346876.7123288</v>
+        <v>-297430610.8241635</v>
       </c>
       <c r="I8" t="n">
-        <v>706305590.1776713</v>
+        <v>605072555.3458366</v>
       </c>
       <c r="J8" t="n">
-        <v>742305590.1776713</v>
+        <v>637072555.3458366</v>
       </c>
       <c r="K8" t="n">
-        <v>4303262.334450001</v>
+        <v>4512515.83085</v>
       </c>
       <c r="L8" t="n">
-        <v>-4483262.334450001</v>
+        <v>-4672515.83085</v>
       </c>
       <c r="M8" t="n">
-        <v>3531527.950888357</v>
+        <v>3025362.776729183</v>
       </c>
       <c r="N8" t="n">
-        <v>-3711527.950888357</v>
+        <v>-3185362.776729183</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-195816900.17</v>
+        <v>-154283223.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-159816900.17</v>
+        <v>-122283223.6</v>
       </c>
       <c r="H9" t="n">
-        <v>90336829.10397485</v>
+        <v>63482820.57040198</v>
       </c>
       <c r="I9" t="n">
-        <v>-105480071.0660252</v>
+        <v>-90800403.02959804</v>
       </c>
       <c r="J9" t="n">
-        <v>-69480071.06602517</v>
+        <v>-58800403.02959804</v>
       </c>
       <c r="K9" t="n">
-        <v>-815903.7507083333</v>
+        <v>-642846.765</v>
       </c>
       <c r="L9" t="n">
-        <v>665903.7507083333</v>
+        <v>509513.4316666668</v>
       </c>
       <c r="M9" t="n">
-        <v>-439500.2961084382</v>
+        <v>-378335.0126233251</v>
       </c>
       <c r="N9" t="n">
-        <v>289500.2961084382</v>
+        <v>245001.6792899918</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-134836161.42</v>
+        <v>-105494922.47</v>
       </c>
       <c r="F10" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G10" t="n">
-        <v>-98836161.42000002</v>
+        <v>-73494922.47</v>
       </c>
       <c r="H10" t="n">
-        <v>6798456.09701325</v>
+        <v>11318465.07972154</v>
       </c>
       <c r="I10" t="n">
-        <v>-128037705.3229868</v>
+        <v>-94176457.39027846</v>
       </c>
       <c r="J10" t="n">
-        <v>-92037705.32298677</v>
+        <v>-62176457.39027846</v>
       </c>
       <c r="K10" t="n">
-        <v>-449453.8714000001</v>
+        <v>-351649.7415666667</v>
       </c>
       <c r="L10" t="n">
-        <v>329453.8714000001</v>
+        <v>244983.0749</v>
       </c>
       <c r="M10" t="n">
-        <v>-426792.3510766226</v>
+        <v>-313921.5246342616</v>
       </c>
       <c r="N10" t="n">
-        <v>306792.3510766226</v>
+        <v>207254.8579675949</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>23489211.14000002</v>
+        <v>-106354032.72</v>
       </c>
       <c r="F11" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G11" t="n">
-        <v>59489211.14000002</v>
+        <v>-74354032.72000001</v>
       </c>
       <c r="H11" t="n">
-        <v>106004406.5798338</v>
+        <v>63470643.38648102</v>
       </c>
       <c r="I11" t="n">
-        <v>129493617.7198338</v>
+        <v>-42883389.333519</v>
       </c>
       <c r="J11" t="n">
-        <v>165493617.7198339</v>
+        <v>-10883389.333519</v>
       </c>
       <c r="K11" t="n">
-        <v>58723.02785000004</v>
+        <v>-265885.0818</v>
       </c>
       <c r="L11" t="n">
-        <v>-148723.02785</v>
+        <v>185885.0818</v>
       </c>
       <c r="M11" t="n">
-        <v>323734.0442995846</v>
+        <v>-107208.4733337975</v>
       </c>
       <c r="N11" t="n">
-        <v>-413734.0442995846</v>
+        <v>27208.47333379749</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-135044007.53</v>
+        <v>-105737558.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G12" t="n">
-        <v>-99044007.53</v>
+        <v>-73737558.24999999</v>
       </c>
       <c r="H12" t="n">
-        <v>6746058.836739277</v>
+        <v>11243431.39456546</v>
       </c>
       <c r="I12" t="n">
-        <v>-128297948.6932607</v>
+        <v>-94494126.85543452</v>
       </c>
       <c r="J12" t="n">
-        <v>-92297948.69326073</v>
+        <v>-62494126.85543452</v>
       </c>
       <c r="K12" t="n">
-        <v>-225073.3458833333</v>
+        <v>-176229.2637499999</v>
       </c>
       <c r="L12" t="n">
-        <v>165073.3458833333</v>
+        <v>122895.9304166666</v>
       </c>
       <c r="M12" t="n">
-        <v>-213829.9144887679</v>
+        <v>-157490.2114257242</v>
       </c>
       <c r="N12" t="n">
-        <v>153829.9144887679</v>
+        <v>104156.8780923908</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-134211468.78</v>
+        <v>-105013009.69</v>
       </c>
       <c r="F13" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G13" t="n">
-        <v>-98211468.77999999</v>
+        <v>-73013009.69</v>
       </c>
       <c r="H13" t="n">
-        <v>6784611.497866606</v>
+        <v>11307685.82977768</v>
       </c>
       <c r="I13" t="n">
-        <v>-127426857.2821334</v>
+        <v>-93705323.86022232</v>
       </c>
       <c r="J13" t="n">
-        <v>-91426857.28213339</v>
+        <v>-61705323.86022232</v>
       </c>
       <c r="K13" t="n">
-        <v>-111842.89065</v>
+        <v>-87510.84140833338</v>
       </c>
       <c r="L13" t="n">
-        <v>81842.89065000002</v>
+        <v>60844.17474166669</v>
       </c>
       <c r="M13" t="n">
-        <v>-106189.0477351112</v>
+        <v>-78087.76988351863</v>
       </c>
       <c r="N13" t="n">
-        <v>76189.04773511119</v>
+        <v>51421.10321685196</v>
       </c>
     </row>
     <row r="14">
@@ -1087,22 +1087,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-109342407.55</v>
+        <v>-86650256.47999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-36000000</v>
+        <v>-32000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-73342407.55</v>
+        <v>-54650256.47999999</v>
       </c>
       <c r="H14" t="n">
-        <v>13498282.0570402</v>
+        <v>11236273.29889962</v>
       </c>
       <c r="I14" t="n">
-        <v>-95844125.4929598</v>
+        <v>-75413983.18110037</v>
       </c>
       <c r="J14" t="n">
-        <v>-59844125.4929598</v>
+        <v>-43413983.18110037</v>
       </c>
       <c r="K14" t="n">
         <v>-0</v>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20437754.81096452</v>
+        <v>22773869.17080628</v>
       </c>
       <c r="C2" t="n">
-        <v>-30948028.78356726</v>
+        <v>-32116334.92423094</v>
       </c>
       <c r="D2" t="n">
-        <v>9448464.944881732</v>
+        <v>6400562.209955915</v>
       </c>
       <c r="E2" t="n">
-        <v>-19958738.91748447</v>
+        <v>-15743027.96338057</v>
       </c>
     </row>
   </sheetData>
@@ -1188,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-123330404.73</v>
+        <v>-106562067.57</v>
       </c>
       <c r="D2" t="n">
-        <v>-97064491.28421247</v>
+        <v>-25848477.15462025</v>
       </c>
       <c r="E2" t="n">
-        <v>-220394896.0142125</v>
+        <v>-132410544.7246203</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>108001745.88</v>
+        <v>112601706.49</v>
       </c>
       <c r="D3" t="n">
-        <v>3759129.314246576</v>
+        <v>7667665.693972602</v>
       </c>
       <c r="E3" t="n">
-        <v>111760875.1942466</v>
+        <v>120269372.1839726</v>
       </c>
     </row>
     <row r="4">
@@ -1268,17 +1268,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>ir_swap</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-22325849.93</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-22325849.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>loans</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>572028977.8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>30647795.06400019</v>
-      </c>
-      <c r="E4" t="n">
-        <v>602676772.8640002</v>
+      <c r="C5" t="n">
+        <v>570955354.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>56311269.2946721</v>
+      </c>
+      <c r="E5" t="n">
+        <v>627266623.6946721</v>
       </c>
     </row>
   </sheetData>
@@ -1324,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>556700318.9499999</v>
+        <v>554669143.39</v>
       </c>
       <c r="C2" t="n">
-        <v>-62657566.9059657</v>
+        <v>38130457.83402446</v>
       </c>
       <c r="D2" t="n">
-        <v>494042752.0440343</v>
+        <v>592799601.2240244</v>
       </c>
     </row>
   </sheetData>
@@ -1344,1715 +1365,5645 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>rate_type</t>
+          <t>tenor_bucket</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>nii_interest</t>
+          <t>eba_bucket</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>nii_renewal</t>
+          <t>bucket_order</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>nii_total</t>
+          <t>tenor_yf</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>remain_yf</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>gap_cf</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gap_cf_irs</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gap_cf_total</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>gap_cf_ca</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>gap_adj</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>r_base</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>r_shocked</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>delta_r</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>delta_nii</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>delta_nii_reg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9972602739726028</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
+      <c r="J2" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.07754352080482141</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.02747158338321065</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8203621.746674323</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4101810.873337161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-83834121.54000001</v>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>-11473502.60729568</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>-95307624.14729567</v>
+        <v>575699100.39</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.08337755773034683</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02514989940008316</v>
+      </c>
+      <c r="P3" t="n">
+        <v>475743.8701872187</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>237871.9350936094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-88440256.50779517</v>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>-39103316.21761597</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>-127543572.7254111</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>-127543572.7254111</v>
+        <v>1961135371.76</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.08369379184910075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02530014515467949</v>
+      </c>
+      <c r="P4" t="n">
+        <v>30648043.47303869</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15324021.73651935</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>76690534.49000001</v>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>2253869.435616439</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>0.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>78944403.92561644</v>
+        <v>531970690.13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.08396522087656511</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02544697899977066</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-496319.0035436328</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-496319.0035436328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>20285044.45110441</v>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-1798622.303601288</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>18486422.14750312</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>18486422.14750312</v>
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08380359375583302</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02559354982454409</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1218018.568307064</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1218018.568307064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>183462781.77</v>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>19499123.76947068</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>202961905.5394707</v>
+        <v>517889994.42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J7" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08381995594343969</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.02573959809769572</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5526119.171618581</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2763059.58580929</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>283983021.7546195</v>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>23768398.55035754</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>307751420.304977</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>307751420.304977</v>
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J8" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.08388647441583164</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.02588744766971374</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7831892.056447658</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3915946.028223829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-154283223.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.08341197750438349</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02602676969992171</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-984683.8242964256</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-984683.8242964256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-83834121.54000001</v>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>-11473502.60729568</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-95307624.14729567</v>
+        <v>-105494922.47</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.08312099411366869</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.02616692125524978</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-821435.9815432675</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-821435.9815432675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-33004509.66453836</v>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>-14298083.33721216</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>-47302593.00175052</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-47302593.00175052</v>
+        <v>-106354032.72</v>
+      </c>
+      <c r="I11" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.08295275176741097</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.02630835803903212</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-282047.8901283572</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-282047.8901283572</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>76690534.49000001</v>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>2253869.435616439</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>78944403.92561644</v>
+        <v>-105737558.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.08287071239183845</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.02645013495868191</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-416563.7346881752</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-416563.7346881752</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>7636691.405344562</v>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>-654696.5183792791</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>6981994.886965282</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>6981994.886965282</v>
+        <v>-105013009.69</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.08285170738618473</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02659286987606641</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-207657.7903424628</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-207657.7903424628</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_up</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>183462781.77</v>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>19499123.76947068</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>202961905.5394707</v>
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.08286595312469469</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.02673608443001796</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>105636598.280187</v>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>9082094.487427209</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>114718692.7676142</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>114718692.7676142</v>
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.02753748516008958</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.07747761902794248</v>
+      </c>
+      <c r="P15" t="n">
+        <v>23136528.80767785</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11568264.40383892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>575699100.39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>84635999.55909944</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0331349453908647</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.02509271293939896</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1946767.937835948</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1946767.937835948</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>-83834121.54000001</v>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>-11473502.60729568</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>-95307624.14729567</v>
+        <v>1961135371.76</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1517653800.908888</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.03320699258664073</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.02518665410778054</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-31853851.11570883</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-31853851.11570883</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>-59714618.06673019</v>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>-18422606.22633189</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>-78137224.29306208</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>-78137224.29306208</v>
+        <v>531970690.13</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>37994607.71365142</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.03323339261266689</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.02528484926412755</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-720515.9466670005</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-720515.9466670005</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>76690534.49000001</v>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E19" t="n">
-        <v>2253869.435616439</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>78944403.92561644</v>
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-7386261.967790231</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.03283281915676661</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.02537722477452231</v>
+      </c>
+      <c r="P19" t="n">
+        <v>124961.8868000788</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>62480.9434000394</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>13027119.3379819</v>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E20" t="n">
-        <v>-1264828.159439856</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>11762291.17854204</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>11762291.17854204</v>
+        <v>517889994.42</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J20" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>432045651.5051111</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.03260901053869531</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.02547134730704866</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-6419457.824492295</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-6419457.824492295</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>183462781.77</v>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E21" t="n">
-        <v>19499123.76947068</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>202961905.5394707</v>
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J21" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>637072555.3458366</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.03243513705883272</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.02556388968728518</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-8143026.263828925</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-8143026.263828925</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>194799829.7953675</v>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E22" t="n">
-        <v>14945808.62942155</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>209745638.424789</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>209745638.424789</v>
+        <v>-154283223.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-58800403.02959804</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.03173641088008074</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.02564879692438105</v>
+      </c>
+      <c r="P22" t="n">
+        <v>628399.8318241333</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>314199.9159120666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-105494922.47</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-62176457.39027846</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.03122012932187956</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.02573394353653935</v>
+      </c>
+      <c r="P23" t="n">
+        <v>533348.481261157</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>266674.2406305785</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>-83834121.54000001</v>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E24" t="n">
-        <v>-11473502.60729568</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-95307624.14729567</v>
+        <v>-106354032.72</v>
+      </c>
+      <c r="I24" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-10883389.333519</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.03082552007485706</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.02581887365352179</v>
+      </c>
+      <c r="P24" t="n">
+        <v>70249.21353105344</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>35124.60676552672</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-65498956.1715795</v>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E25" t="n">
-        <v>-37327429.93962904</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>-102826386.1112086</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-102826386.1112086</v>
+        <v>-105737558.25</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-62494126.85543452</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.03051606872334229</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.02590450870981425</v>
+      </c>
+      <c r="P25" t="n">
+        <v>269813.2755731399</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>134906.6377865699</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>76690534.49000001</v>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>2253869.435616439</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>78944403.92561644</v>
+        <v>-105013009.69</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-61705323.86022232</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.03026857544468633</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.025990262065432</v>
+      </c>
+      <c r="P26" t="n">
+        <v>133644.7948299611</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>66822.39741498054</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>par_dn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>15750637.86348905</v>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E27" t="n">
-        <v>-1254938.038150794</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>14495699.82533826</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>14495699.82533826</v>
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-43413983.18110037</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.03005395945905409</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.02607590923562264</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>183462781.77</v>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>19499123.76947068</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>202961905.5394707</v>
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.02998523830907041</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.07502986587896165</v>
+      </c>
+      <c r="P28" t="n">
+        <v>22405575.63751067</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>11202787.81875534</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>206670081.1717829</v>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
       </c>
       <c r="E29" t="n">
-        <v>19003749.12332492</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>225673830.2951078</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>225673830.2951078</v>
+        <v>575699100.39</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>84635999.55909944</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.03834659693956599</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.01988106139069767</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-1542432.377839391</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-1542432.377839391</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1961135371.76</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1517653800.908888</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.04113736359982756</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.01725628309459371</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-21824219.69005828</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-21824219.69005828</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>-83834121.54000001</v>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E31" t="n">
-        <v>-11473502.60729568</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>-95307624.14729567</v>
+        <v>531970690.13</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>37994607.71365142</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.0436276127705737</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.01489062910622074</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-424322.7086252528</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-424322.7086252528</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>-76108285.75487417</v>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E32" t="n">
-        <v>-41155499.7907265</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>-117263785.5456007</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-117263785.5456007</v>
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-7386261.967790231</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.0455480154500596</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.01266202848122933</v>
+      </c>
+      <c r="P32" t="n">
+        <v>62350.03960398726</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>31175.01980199363</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>76690534.49000001</v>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E33" t="n">
-        <v>2253869.435616439</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>78944403.92561644</v>
+        <v>517889994.42</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J33" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>432045651.5051111</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.04746456405164672</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.01061579379409725</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-2675462.735175219</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-2675462.735175219</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>18104123.06561163</v>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E34" t="n">
-        <v>-1481715.503231204</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>16622407.56238043</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>16622407.56238043</v>
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J34" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L34" t="n">
+        <v>637072555.3458366</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.0492972557825806</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.008701770963537303</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-2771829.731887456</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-2771829.731887456</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>183462781.77</v>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E35" t="n">
-        <v>19499123.76947068</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>202961905.5394707</v>
+        <v>-154283223.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-58800403.02959804</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.05045136439179869</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-0.006933843412663093</v>
+      </c>
+      <c r="P35" t="n">
+        <v>169880.3280036305</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>84940.16400181527</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>241180594.3495923</v>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E36" t="n">
-        <v>21673258.63299607</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>262853852.9825884</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>262853852.9825884</v>
+        <v>-105494922.47</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-62176457.39027846</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.05166029289831464</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.005293779960104272</v>
+      </c>
+      <c r="P36" t="n">
+        <v>109716.1613743111</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>54858.08068715555</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-106354032.72</v>
+      </c>
+      <c r="I37" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-10883389.333519</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.05287569440126383</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.003768699327115023</v>
+      </c>
+      <c r="P37" t="n">
+        <v>10254.05551449096</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5127.027757245482</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>-83834121.54000001</v>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E38" t="n">
-        <v>-11473502.60729568</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-95307624.14729567</v>
+        <v>-105737558.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-62494126.85543452</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.0540637033638335</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.002356874069323035</v>
+      </c>
+      <c r="P38" t="n">
+        <v>24548.46451175965</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>12274.23225587983</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>-45305017.78653013</v>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E39" t="n">
-        <v>-12244015.25673077</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>-57549033.0432609</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>-57549033.0432609</v>
+        <v>-105013009.69</v>
+      </c>
+      <c r="I39" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-61705323.86022232</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.05521394741144346</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-0.001044890098674874</v>
+      </c>
+      <c r="P39" t="n">
+        <v>5372.94016142273</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2686.470080711365</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>steep</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>76690534.49000001</v>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
       </c>
       <c r="E40" t="n">
-        <v>2253869.435616439</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>78944403.92561644</v>
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.05630391743831353</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.000174048743636801</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>9776813.2234874</v>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
       </c>
       <c r="E41" t="n">
-        <v>-965895.138161672</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>8810918.085325729</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>8810918.085325729</v>
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.08033035812803568</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-0.02468474605999638</v>
+      </c>
+      <c r="P41" t="n">
+        <v>7371410.550462875</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3685705.275231437</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>183462781.77</v>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
       </c>
       <c r="E42" t="n">
-        <v>19499123.76947068</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>202961905.5394707</v>
+        <v>575699100.39</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J42" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.08318615436787802</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.02495849603761435</v>
+      </c>
+      <c r="P42" t="n">
+        <v>472123.2204589952</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>236061.6102294976</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>148328362.9040446</v>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E43" t="n">
-        <v>11171524.55952817</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>159499887.4635728</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>159499887.4635728</v>
+        <v>1961135371.76</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.08055379157089071</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.02216014487646945</v>
+      </c>
+      <c r="P43" t="n">
+        <v>26844315.69030953</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>13422157.84515477</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>0.25</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>531970690.13</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.07813840667889771</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.01962016480210327</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-382672.5618011282</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-382672.5618011282</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>-83834121.54000001</v>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E45" t="n">
-        <v>-11473502.60729568</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>-95307624.14729567</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-95307624.14729567</v>
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.07543344707084598</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.01722340313955706</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-819676.245664854</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>-819676.245664854</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>deposits</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>-49611311.26421505</v>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E46" t="n">
-        <v>-21735501.23588518</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>-71346812.50010024</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>-71346812.50010024</v>
+        <v>517889994.42</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J46" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.07309558198160494</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.01501522413586098</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3223667.970587295</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1611833.985293648</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>76690534.49000001</v>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
       </c>
       <c r="E47" t="n">
-        <v>2253869.435616439</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>78944403.92561644</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>78944403.92561644</v>
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J47" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.07094844672146827</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.01294941997535037</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3917669.317365836</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1958834.658682918</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fin_inst</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11398282.87246964</v>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E48" t="n">
-        <v>-994870.2075526081</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>10403412.66491704</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>10403412.66491704</v>
+        <v>-154283223.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.06842305743571853</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.01103784963125674</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-417600.4979575885</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>-417600.4979575885</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>183462781.77</v>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E49" t="n">
-        <v>19499123.76947068</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>202961905.5394707</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>202961905.5394707</v>
+        <v>-105494922.47</v>
+      </c>
+      <c r="I49" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.06621878897479672</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.009264716116377802</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-290839.3808556934</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-290839.3808556934</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>159062516.7739767</v>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
       </c>
       <c r="E50" t="n">
-        <v>13481615.06219128</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>172544131.836168</v>
-      </c>
-      <c r="G50" t="inlineStr">
+        <v>0.75</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-106354032.72</v>
+      </c>
+      <c r="I50" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.06426245745541011</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.007618063727031256</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-81672.09819346003</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-81672.09819346003</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-105737558.25</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.06251548466460592</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.006094907231449384</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-95988.82285011387</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-95988.82285011387</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-105013009.69</v>
+      </c>
+      <c r="I52" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.06094126886514148</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.004682431355023151</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-36564.06221464201</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-36564.06221464201</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.05950311578357481</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.003373247088898079</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.9972602739726028</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.08735529861555014</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-0.01765980557248192</v>
+      </c>
+      <c r="P54" t="n">
+        <v>5273608.114084664</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2636804.057042332</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H55" t="n">
+        <v>575699100.39</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J55" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L55" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.09058485068408295</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.03235719235381929</v>
+      </c>
+      <c r="P55" t="n">
+        <v>612079.4232181845</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>306039.7116090923</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1961135371.76</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.08832183864296361</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.02992819194854235</v>
+      </c>
+      <c r="P56" t="n">
+        <v>36254358.31694114</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>18127179.15847057</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H57" t="n">
+        <v>531970690.13</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.08624486047266533</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.02772661859587089</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-540781.1950196924</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-540781.1950196924</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H58" t="n">
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.08385907763058897</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.02564903369930005</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-1220659.092585942</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-1220659.092585942</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="H59" t="n">
+        <v>517889994.42</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J59" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L59" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.08181758148143689</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.02373722363569292</v>
+      </c>
+      <c r="P59" t="n">
+        <v>5096222.797120655</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2548111.398560327</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J60" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L60" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.07994919825034419</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.02195017150422629</v>
+      </c>
+      <c r="P60" t="n">
+        <v>6640723.181170784</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3320361.590585392</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-154283223.6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.07768043009699076</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.02029522229252897</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-767839.318223714</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-767839.318223714</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-105494922.47</v>
+      </c>
+      <c r="I62" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.07571604046176417</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.01876196760334525</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-588978.5475180765</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-588978.5475180765</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-106354032.72</v>
+      </c>
+      <c r="I63" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.07398436000341994</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.01733996627504109</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-185899.1312006691</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-185899.1312006691</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-105737558.25</v>
+      </c>
+      <c r="I64" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.07244727948281815</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.01602670204966161</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-252404.8694258294</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>-252404.8694258294</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-105013009.69</v>
+      </c>
+      <c r="I65" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.0710697595917701</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.01481092208165177</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-115655.1875274748</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-115655.1875274748</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I66" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.06981591961576861</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.01368605092109187</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.9972602739726028</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.01772687293857378</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-0.08728823124945828</v>
+      </c>
+      <c r="P67" t="n">
+        <v>26066194.36957637</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>13033097.18478818</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H68" t="n">
+        <v>575699100.39</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J68" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L68" t="n">
+        <v>84635999.55909944</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.02596200736148457</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-0.03226565096877909</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-2503265.98607034</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>-2503265.98607034</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1961135371.76</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1517653800.908888</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.02862082930181886</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-0.0297728173926024</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-37654024.56637441</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>-37654024.56637441</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H70" t="n">
+        <v>531970690.13</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L70" t="n">
+        <v>37994607.71365142</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.03098334217962151</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-0.02753489969717293</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-784633.2843216185</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-784633.2843216185</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H71" t="n">
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-7386261.967790231</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.0327782499425886</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-0.02543179398870032</v>
+      </c>
+      <c r="P71" t="n">
+        <v>125230.5951409423</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>62615.29757047114</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="H72" t="n">
+        <v>517889994.42</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J72" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L72" t="n">
+        <v>432045651.5051111</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.03457168212681622</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-0.02350867571892774</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-5924812.318253805</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>-5924812.318253805</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J73" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L73" t="n">
+        <v>637072555.3458366</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.03628245893619209</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-0.02171656780992581</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-6917514.674005289</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>-6917514.674005289</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-154283223.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-58800403.02959804</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.03732101742477235</v>
+      </c>
+      <c r="O74" t="n">
+        <v>-0.02006419037968943</v>
+      </c>
+      <c r="P74" t="n">
+        <v>491576.0336618008</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>245788.0168309004</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-105494922.47</v>
+      </c>
+      <c r="I75" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-62176457.39027846</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.03841598150227232</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-0.01853809135614659</v>
+      </c>
+      <c r="P75" t="n">
+        <v>384210.949100846</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>192105.474550423</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-106354032.72</v>
+      </c>
+      <c r="I76" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-10883389.333519</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.03951885651063976</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-0.01712553721773909</v>
+      </c>
+      <c r="P76" t="n">
+        <v>46595.97227158104</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>23297.98613579052</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-105737558.25</v>
+      </c>
+      <c r="I77" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-62494126.85543452</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.0405960223903211</v>
+      </c>
+      <c r="O77" t="n">
+        <v>-0.01582455504283544</v>
+      </c>
+      <c r="P77" t="n">
+        <v>164823.625046294</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>82411.81252314699</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-105013009.69</v>
+      </c>
+      <c r="I78" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-61705323.86022232</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.04163683720489108</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-0.01462200030522725</v>
+      </c>
+      <c r="P78" t="n">
+        <v>75187.93869319312</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>37593.96934659656</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I79" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-43413983.18110037</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.04261896504062945</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-0.01351090365404728</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>own</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>172544131.836168</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Overnight</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.00273972602739726</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.9972602739726028</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-939442484.0499998</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-640000000</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-299442484.0499998</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.1050151041880321</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.04253896657148259</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-0.06247613761654947</v>
+      </c>
+      <c r="P80" t="n">
+        <v>18656755.02026496</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>9328377.51013248</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H81" t="n">
+        <v>575699100.39</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-555063100.8309005</v>
+      </c>
+      <c r="J81" t="n">
+        <v>20635999.55909944</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L81" t="n">
+        <v>84635999.55909944</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.05822765833026367</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.04818573491561828</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-0.01004192341464538</v>
+      </c>
+      <c r="P81" t="n">
+        <v>-779082.5402199004</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>-779082.5402199004</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1961135371.76</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-507481570.8511116</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1453653800.908888</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1517653800.908888</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.05839364669442126</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.04830891037354634</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-0.01008473632087492</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-12754282.00711645</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>-12754282.00711645</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H83" t="n">
+        <v>531970690.13</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-557976082.4163486</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-26005392.28634858</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L83" t="n">
+        <v>37994607.71365142</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.05851824187679444</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.04838641196094517</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-0.01013182991584927</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-288716.177305598</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>-288716.177305598</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="H84" t="n">
+        <v>78498009.31000002</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-149884271.2777902</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-71386261.96779023</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-7386261.967790231</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.05821004393128892</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.04803495850217376</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-0.01017508542911516</v>
+      </c>
+      <c r="P84" t="n">
+        <v>50103.89768272657</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>25051.94884136329</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="H85" t="n">
+        <v>517889994.42</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-149844342.9148888</v>
+      </c>
+      <c r="J85" t="n">
+        <v>368045651.5051111</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="L85" t="n">
+        <v>432045651.5051111</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.05808035784574397</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.04786041751529452</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-0.01021994033044944</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-2575697.12074056</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>-2575697.12074056</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>902503166.1700001</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-297430610.8241635</v>
+      </c>
+      <c r="J86" t="n">
+        <v>605072555.3458366</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L86" t="n">
+        <v>637072555.3458366</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.0579990267461179</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.04773570697588347</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-0.01026331977023442</v>
+      </c>
+      <c r="P86" t="n">
+        <v>-3269239.676177345</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>-3269239.676177345</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-154283223.6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>63482820.57040198</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-90800403.02959804</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-58800403.02959804</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.05738520780446178</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.04708113683929442</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-0.01030407096516736</v>
+      </c>
+      <c r="P87" t="n">
+        <v>252451.4689989251</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>126225.7344994625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-105494922.47</v>
+      </c>
+      <c r="I88" t="n">
+        <v>11318465.07972154</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-94176457.39027846</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-62176457.39027846</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.05695407285841891</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.04660915432675217</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-0.01034491853166675</v>
+      </c>
+      <c r="P88" t="n">
+        <v>214403.4620966932</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>107201.7310483466</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-106354032.72</v>
+      </c>
+      <c r="I89" t="n">
+        <v>63470643.38648102</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-42883389.333519</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-10883389.333519</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.05664439372837885</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.04625895250573434</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-0.01038544122264451</v>
+      </c>
+      <c r="P89" t="n">
+        <v>28257.20005660443</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>14128.60002830222</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-105737558.25</v>
+      </c>
+      <c r="I90" t="n">
+        <v>11243431.39456546</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-94494126.85543452</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-62494126.85543452</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.05642057743315654</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.04599405363004969</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-0.01042652380310684</v>
+      </c>
+      <c r="P90" t="n">
+        <v>108599.4168687611</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>54299.70843438055</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-105013009.69</v>
+      </c>
+      <c r="I91" t="n">
+        <v>11307685.82977768</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-93705323.86022232</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-61705323.86022232</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.05625883751011833</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.04579124656081188</v>
+      </c>
+      <c r="O91" t="n">
+        <v>-0.01046759094930644</v>
+      </c>
+      <c r="P91" t="n">
+        <v>53825.5074636072</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>26912.7537318036</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-86650256.47999999</v>
+      </c>
+      <c r="I92" t="n">
+        <v>11236273.29889962</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-75413983.18110037</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-32000000</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-43413983.18110037</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.05612986869467673</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.04562123316148581</v>
+      </c>
+      <c r="O92" t="n">
+        <v>-0.01050863553319092</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3066,51 +7017,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nii_interest</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>nii_renewal</t>
+          <t>delta_nii</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>nii_total</t>
+          <t>delta_nii_reg</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>sot_nii_pct</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>delta_nii</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>sot_nii_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>delta_nii_reg</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>sot_nii_pct_reg</t>
         </is>
@@ -3119,232 +7055,169 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>392147004.4179287</v>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>-6854049.373068273</v>
+        <v>41834065.10000002</v>
       </c>
       <c r="D2" t="n">
-        <v>385292955.0448604</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>par_up</t>
-        </is>
+        <v>20917032.55000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.324114727777779</v>
       </c>
       <c r="F2" t="n">
-        <v>-108749796.9991739</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-9.062483083264491</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-108749796.9991739</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-9.062483083264491</v>
+        <v>1.16205736388889</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>256587974.7409933</v>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>4408805.229627218</v>
+        <v>-42041798.58999991</v>
       </c>
       <c r="D3" t="n">
-        <v>260996779.9706205</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>par_dn</t>
-        </is>
+        <v>-42041798.58999991</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-2.335655477222217</v>
       </c>
       <c r="F3" t="n">
-        <v>-233045972.0734138</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-19.42049767278449</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-233045972.0734138</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-19.42049767278449</v>
+        <v>-2.335655477222217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>324431525.7866192</v>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>5537864.841441255</v>
+        <v>1003055.190000057</v>
       </c>
       <c r="D4" t="n">
-        <v>329969390.6280605</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>steep</t>
-        </is>
+        <v>501527.5950000286</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05572528833333652</v>
       </c>
       <c r="F4" t="n">
-        <v>-164073361.4159738</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-13.67278011799782</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-164073361.4159738</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-13.67278011799782</v>
+        <v>0.02786264416666826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>333240957.5836925</v>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>-9299128.256663471</v>
+        <v>4421016.350000024</v>
       </c>
       <c r="D5" t="n">
-        <v>323941829.327029</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
+        <v>2210508.175000012</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2456120194444457</v>
       </c>
       <c r="F5" t="n">
-        <v>-170100922.7170053</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-14.17507689308378</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-170100922.7170053</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-14.17507689308378</v>
+        <v>0.1228060097222229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>359495626.3803298</v>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>-10684466.06317019</v>
+        <v>20762838.7700001</v>
       </c>
       <c r="D6" t="n">
-        <v>348811160.3171597</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sr_up</t>
-        </is>
+        <v>10381419.38500005</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.153491042777783</v>
       </c>
       <c r="F6" t="n">
-        <v>-145231591.7268746</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-12.10263264390622</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-145231591.7268746</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-12.10263264390622</v>
+        <v>0.5767455213888917</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>289119353.0610019</v>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>8241104.762427175</v>
+        <v>-20897206.02999997</v>
       </c>
       <c r="D7" t="n">
-        <v>297360457.823429</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sr_dn</t>
-        </is>
+        <v>-20897206.02999997</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.160955890555554</v>
       </c>
       <c r="F7" t="n">
-        <v>-196682294.2206053</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-16.39019118505044</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-196682294.2206053</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-16.39019118505044</v>
+        <v>-1.160955890555554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>297168683.1022313</v>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>1030734.21654493</v>
+        <v>-16852473.81999993</v>
       </c>
       <c r="D8" t="n">
-        <v>298199417.3187762</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
+        <v>-16852473.81999993</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.9362485455555519</v>
       </c>
       <c r="F8" t="n">
-        <v>-195843334.7252581</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-16.3202778937715</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-195843334.7252581</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-16.3202778937715</v>
+        <v>-0.9362485455555519</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="F2" t="n">
         <v>-640000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="J2" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="K2" t="n">
-        <v>-9368686.690252054</v>
+        <v>-9404719.292187398</v>
       </c>
       <c r="L2" t="n">
-        <v>2986220.936827396</v>
+        <v>3022253.53876274</v>
       </c>
       <c r="M2" t="n">
-        <v>-9368686.690252054</v>
+        <v>-9404719.292187398</v>
       </c>
       <c r="N2" t="n">
-        <v>2986220.936827396</v>
+        <v>3022253.53876274</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="F3" t="n">
         <v>-64000000</v>
       </c>
       <c r="G3" t="n">
-        <v>639699100.39</v>
+        <v>612709791.53</v>
       </c>
       <c r="H3" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="I3" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="J3" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="K3" t="n">
-        <v>5277241.753575</v>
+        <v>5029839.755691666</v>
       </c>
       <c r="L3" t="n">
-        <v>-5863908.420241666</v>
+        <v>-5616506.422358333</v>
       </c>
       <c r="M3" t="n">
-        <v>189163.3292917448</v>
+        <v>592846.730165804</v>
       </c>
       <c r="N3" t="n">
-        <v>-775829.9959584115</v>
+        <v>-1179513.396832471</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="F4" t="n">
         <v>-64000000</v>
       </c>
       <c r="G4" t="n">
-        <v>2025135371.76</v>
+        <v>2054072267.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="I4" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="J4" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="K4" t="n">
-        <v>16342794.76466667</v>
+        <v>16583935.56583334</v>
       </c>
       <c r="L4" t="n">
-        <v>-16876128.098</v>
+        <v>-17117268.89916667</v>
       </c>
       <c r="M4" t="n">
-        <v>12113781.67424074</v>
+        <v>12866141.6534896</v>
       </c>
       <c r="N4" t="n">
-        <v>-12647115.00757407</v>
+        <v>-13399474.98682293</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="F5" t="n">
         <v>-64000000</v>
       </c>
       <c r="G5" t="n">
-        <v>595970690.13</v>
+        <v>385318332.1300001</v>
       </c>
       <c r="H5" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="I5" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="J5" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="K5" t="n">
-        <v>3989780.175975</v>
+        <v>2409887.490975001</v>
       </c>
       <c r="L5" t="n">
-        <v>-4469780.175975</v>
+        <v>-2889887.490975001</v>
       </c>
       <c r="M5" t="n">
-        <v>-195040.4421476144</v>
+        <v>-1315052.236736654</v>
       </c>
       <c r="N5" t="n">
-        <v>-284959.5578523856</v>
+        <v>835052.2367366543</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="F6" t="n">
         <v>-64000000</v>
       </c>
       <c r="G6" t="n">
-        <v>142498009.31</v>
+        <v>146481230.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="I6" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="J6" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="K6" t="n">
-        <v>523320.0620666668</v>
+        <v>549874.8686666667</v>
       </c>
       <c r="L6" t="n">
-        <v>-949986.7287333334</v>
+        <v>-976541.5353333335</v>
       </c>
       <c r="M6" t="n">
-        <v>-475908.4131186016</v>
+        <v>-246513.772698705</v>
       </c>
       <c r="N6" t="n">
-        <v>49241.74645193488</v>
+        <v>-180152.8939679617</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="F7" t="n">
         <v>-64000000</v>
       </c>
       <c r="G7" t="n">
-        <v>581889994.42</v>
+        <v>582697858.84</v>
       </c>
       <c r="H7" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="I7" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="J7" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="K7" t="n">
-        <v>3021024.967449999</v>
+        <v>3025737.5099</v>
       </c>
       <c r="L7" t="n">
-        <v>-3394358.300783333</v>
+        <v>-3399070.843233333</v>
       </c>
       <c r="M7" t="n">
-        <v>2146932.967113148</v>
+        <v>2329084.370555738</v>
       </c>
       <c r="N7" t="n">
-        <v>-2520266.300446481</v>
+        <v>-2702417.703889071</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="F8" t="n">
         <v>-32000000</v>
       </c>
       <c r="G8" t="n">
-        <v>934503166.1700001</v>
+        <v>701118580.01</v>
       </c>
       <c r="H8" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="I8" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="J8" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="K8" t="n">
-        <v>4512515.83085</v>
+        <v>3345592.90005</v>
       </c>
       <c r="L8" t="n">
-        <v>-4672515.83085</v>
+        <v>-3505592.90005</v>
       </c>
       <c r="M8" t="n">
-        <v>3025362.776729183</v>
+        <v>2305675.693223142</v>
       </c>
       <c r="N8" t="n">
-        <v>-3185362.776729183</v>
+        <v>-2465675.693223142</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="F9" t="n">
         <v>-32000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-122283223.6</v>
+        <v>-121952841.84</v>
       </c>
       <c r="H9" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="I9" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="J9" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="K9" t="n">
-        <v>-642846.765</v>
+        <v>-641470.1743333333</v>
       </c>
       <c r="L9" t="n">
-        <v>509513.4316666668</v>
+        <v>508136.841</v>
       </c>
       <c r="M9" t="n">
-        <v>-378335.0126233251</v>
+        <v>-384448.877829104</v>
       </c>
       <c r="N9" t="n">
-        <v>245001.6792899918</v>
+        <v>251115.5444957706</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="F10" t="n">
         <v>-32000000</v>
       </c>
       <c r="G10" t="n">
-        <v>-73494922.47</v>
+        <v>-73287618.78999999</v>
       </c>
       <c r="H10" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="I10" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="J10" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="K10" t="n">
-        <v>-351649.7415666667</v>
+        <v>-350958.7293000001</v>
       </c>
       <c r="L10" t="n">
-        <v>244983.0749</v>
+        <v>244292.0626333333</v>
       </c>
       <c r="M10" t="n">
-        <v>-313921.5246342616</v>
+        <v>-319269.4860931732</v>
       </c>
       <c r="N10" t="n">
-        <v>207254.8579675949</v>
+        <v>212602.8194265065</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="F11" t="n">
         <v>-32000000</v>
       </c>
       <c r="G11" t="n">
-        <v>-74354032.72000001</v>
+        <v>23329255.51999998</v>
       </c>
       <c r="H11" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="I11" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="J11" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="K11" t="n">
-        <v>-265885.0818</v>
+        <v>-21676.86120000005</v>
       </c>
       <c r="L11" t="n">
-        <v>185885.0818</v>
+        <v>-58323.13879999996</v>
       </c>
       <c r="M11" t="n">
-        <v>-107208.4733337975</v>
+        <v>132506.4590335504</v>
       </c>
       <c r="N11" t="n">
-        <v>27208.47333379749</v>
+        <v>-212506.4590335504</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="F12" t="n">
         <v>-32000000</v>
       </c>
       <c r="G12" t="n">
-        <v>-73737558.24999999</v>
+        <v>-73791543.78999999</v>
       </c>
       <c r="H12" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="I12" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="J12" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="K12" t="n">
-        <v>-176229.2637499999</v>
+        <v>-176319.23965</v>
       </c>
       <c r="L12" t="n">
-        <v>122895.9304166666</v>
+        <v>122985.9063166666</v>
       </c>
       <c r="M12" t="n">
-        <v>-157490.2114257242</v>
+        <v>-160578.4356976083</v>
       </c>
       <c r="N12" t="n">
-        <v>104156.8780923908</v>
+        <v>107245.102364275</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="F13" t="n">
         <v>-32000000</v>
       </c>
       <c r="G13" t="n">
-        <v>-73013009.69</v>
+        <v>-73084497.29000002</v>
       </c>
       <c r="H13" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="I13" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="J13" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="K13" t="n">
-        <v>-87510.84140833338</v>
+        <v>-87570.41440833338</v>
       </c>
       <c r="L13" t="n">
-        <v>60844.17474166669</v>
+        <v>60903.74774166672</v>
       </c>
       <c r="M13" t="n">
-        <v>-78087.76988351863</v>
+        <v>-79655.034327489</v>
       </c>
       <c r="N13" t="n">
-        <v>51421.10321685196</v>
+        <v>52988.36766082233</v>
       </c>
     </row>
     <row r="14">
@@ -1087,34 +1087,34 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="F14" t="n">
         <v>-32000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-54650256.47999999</v>
+        <v>58344865.39000002</v>
       </c>
       <c r="H14" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="I14" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="J14" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>-0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22773869.17080628</v>
+        <v>20262153.38003761</v>
       </c>
       <c r="C2" t="n">
-        <v>-32116334.92423094</v>
+        <v>-29604619.13346227</v>
       </c>
       <c r="D2" t="n">
-        <v>6400562.209955915</v>
+        <v>6316017.770897699</v>
       </c>
       <c r="E2" t="n">
-        <v>-15743027.96338057</v>
+        <v>-15658483.52432236</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-106562067.57</v>
+        <v>-106563147.18</v>
       </c>
       <c r="D2" t="n">
-        <v>-25848477.15462025</v>
+        <v>-25848911.73608779</v>
       </c>
       <c r="E2" t="n">
-        <v>-132410544.7246203</v>
+        <v>-132412058.9160878</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>112601706.49</v>
+        <v>87225562.51000001</v>
       </c>
       <c r="D3" t="n">
-        <v>7667665.693972602</v>
+        <v>5260169.800000001</v>
       </c>
       <c r="E3" t="n">
-        <v>120269372.1839726</v>
+        <v>92485732.31</v>
       </c>
     </row>
     <row r="4">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-22325849.93</v>
+        <v>-18501945.84</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-22325849.93</v>
+        <v>-18501945.84</v>
       </c>
     </row>
     <row r="5">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>570955354.4</v>
+        <v>570375617.05</v>
       </c>
       <c r="D5" t="n">
-        <v>56311269.2946721</v>
+        <v>56431275.63671397</v>
       </c>
       <c r="E5" t="n">
-        <v>627266623.6946721</v>
+        <v>626806892.6867139</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>554669143.39</v>
+        <v>532536086.54</v>
       </c>
       <c r="C2" t="n">
-        <v>38130457.83402446</v>
+        <v>35842533.70062618</v>
       </c>
       <c r="D2" t="n">
-        <v>592799601.2240244</v>
+        <v>568378620.2406261</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K2" t="n">
         <v>-640000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M2" t="n">
         <v>0.1050151041880321</v>
@@ -1510,10 +1510,10 @@
         <v>-0.02747158338321065</v>
       </c>
       <c r="P2" t="n">
-        <v>8203621.746674323</v>
+        <v>8302609.009532409</v>
       </c>
       <c r="Q2" t="n">
-        <v>4101810.873337161</v>
+        <v>4151304.504766204</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I3" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J3" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K3" t="n">
         <v>-64000000</v>
       </c>
       <c r="L3" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="M3" t="n">
         <v>0.05822765833026367</v>
@@ -1571,10 +1571,10 @@
         <v>0.02514989940008316</v>
       </c>
       <c r="P3" t="n">
-        <v>475743.8701872187</v>
+        <v>1491003.562333822</v>
       </c>
       <c r="Q3" t="n">
-        <v>237871.9350936094</v>
+        <v>745501.7811669109</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J4" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K4" t="n">
         <v>-64000000</v>
       </c>
       <c r="L4" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="M4" t="n">
         <v>0.05839364669442126</v>
@@ -1632,10 +1632,10 @@
         <v>0.02530014515467949</v>
       </c>
       <c r="P4" t="n">
-        <v>30648043.47303869</v>
+        <v>32551525.14139548</v>
       </c>
       <c r="Q4" t="n">
-        <v>15324021.73651935</v>
+        <v>16275762.57069774</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I5" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J5" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K5" t="n">
         <v>-64000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="M5" t="n">
         <v>0.05851824187679444</v>
@@ -1693,10 +1693,10 @@
         <v>0.02544697899977066</v>
       </c>
       <c r="P5" t="n">
-        <v>-496319.0035436328</v>
+        <v>-3346410.665183908</v>
       </c>
       <c r="Q5" t="n">
-        <v>-496319.0035436328</v>
+        <v>-3346410.665183908</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J6" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K6" t="n">
         <v>-64000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="M6" t="n">
         <v>0.05821004393128892</v>
@@ -1754,10 +1754,10 @@
         <v>0.02559354982454409</v>
       </c>
       <c r="P6" t="n">
-        <v>-1218018.568307064</v>
+        <v>-630916.2524000645</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1218018.568307064</v>
+        <v>-630916.2524000645</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I7" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J7" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K7" t="n">
         <v>-64000000</v>
       </c>
       <c r="L7" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="M7" t="n">
         <v>0.05808035784574397</v>
@@ -1815,10 +1815,10 @@
         <v>0.02573959809769572</v>
       </c>
       <c r="P7" t="n">
-        <v>5526119.171618581</v>
+        <v>5994969.563372931</v>
       </c>
       <c r="Q7" t="n">
-        <v>2763059.58580929</v>
+        <v>2997484.781686465</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I8" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J8" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K8" t="n">
         <v>-32000000</v>
       </c>
       <c r="L8" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="M8" t="n">
         <v>0.0579990267461179</v>
@@ -1876,10 +1876,10 @@
         <v>0.02588744766971374</v>
       </c>
       <c r="P8" t="n">
-        <v>7831892.056447658</v>
+        <v>5968805.885164502</v>
       </c>
       <c r="Q8" t="n">
-        <v>3915946.028223829</v>
+        <v>2984402.942582251</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I9" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J9" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K9" t="n">
         <v>-32000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="M9" t="n">
         <v>0.05738520780446178</v>
@@ -1937,10 +1937,10 @@
         <v>0.02602676969992171</v>
       </c>
       <c r="P9" t="n">
-        <v>-984683.8242964256</v>
+        <v>-1000596.240465143</v>
       </c>
       <c r="Q9" t="n">
-        <v>-984683.8242964256</v>
+        <v>-1000596.240465143</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I10" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J10" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K10" t="n">
         <v>-32000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="M10" t="n">
         <v>0.05695407285841891</v>
@@ -1998,10 +1998,10 @@
         <v>0.02616692125524978</v>
       </c>
       <c r="P10" t="n">
-        <v>-821435.9815432675</v>
+        <v>-835429.9501804125</v>
       </c>
       <c r="Q10" t="n">
-        <v>-821435.9815432675</v>
+        <v>-835429.9501804125</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I11" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J11" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K11" t="n">
         <v>-32000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="M11" t="n">
         <v>0.05664439372837885</v>
@@ -2059,10 +2059,10 @@
         <v>0.02630835803903212</v>
       </c>
       <c r="P11" t="n">
-        <v>-282047.8901283572</v>
+        <v>348602.7366738985</v>
       </c>
       <c r="Q11" t="n">
-        <v>-282047.8901283572</v>
+        <v>174301.3683369493</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I12" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J12" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K12" t="n">
         <v>-32000000</v>
       </c>
       <c r="L12" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="M12" t="n">
         <v>0.05642057743315654</v>
@@ -2120,10 +2120,10 @@
         <v>0.02645013495868191</v>
       </c>
       <c r="P12" t="n">
-        <v>-416563.7346881752</v>
+        <v>-424732.1295655764</v>
       </c>
       <c r="Q12" t="n">
-        <v>-416563.7346881752</v>
+        <v>-424732.1295655764</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I13" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J13" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K13" t="n">
         <v>-32000000</v>
       </c>
       <c r="L13" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="M13" t="n">
         <v>0.05625883751011833</v>
@@ -2181,10 +2181,10 @@
         <v>0.02659286987606641</v>
       </c>
       <c r="P13" t="n">
-        <v>-207657.7903424628</v>
+        <v>-211825.5962844518</v>
       </c>
       <c r="Q13" t="n">
-        <v>-207657.7903424628</v>
+        <v>-211825.5962844518</v>
       </c>
     </row>
     <row r="14">
@@ -2218,34 +2218,34 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I14" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J14" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K14" t="n">
         <v>-32000000</v>
       </c>
       <c r="L14" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08286595312469469</v>
+        <v>0.08285710130558432</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02673608443001796</v>
+        <v>0.02673584606951374</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K15" t="n">
         <v>-640000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M15" t="n">
         <v>0.1050151041880321</v>
@@ -2303,10 +2303,10 @@
         <v>-0.07747761902794248</v>
       </c>
       <c r="P15" t="n">
-        <v>23136528.80767785</v>
+        <v>23415700.82821106</v>
       </c>
       <c r="Q15" t="n">
-        <v>11568264.40383892</v>
+        <v>11707850.41410553</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I16" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J16" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K16" t="n">
         <v>-64000000</v>
       </c>
       <c r="L16" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="M16" t="n">
         <v>0.05822765833026367</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02509271293939896</v>
       </c>
       <c r="P16" t="n">
-        <v>-1946767.937835948</v>
+        <v>-2959719.107489256</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1946767.937835948</v>
+        <v>-2959719.107489256</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I17" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J17" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K17" t="n">
         <v>-64000000</v>
       </c>
       <c r="L17" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="M17" t="n">
         <v>0.05839364669442126</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02518665410778054</v>
       </c>
       <c r="P17" t="n">
-        <v>-31853851.11570883</v>
+        <v>-33748794.17189663</v>
       </c>
       <c r="Q17" t="n">
-        <v>-31853851.11570883</v>
+        <v>-33748794.17189663</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I18" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J18" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K18" t="n">
         <v>-64000000</v>
       </c>
       <c r="L18" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="M18" t="n">
         <v>0.05851824187679444</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02528484926412755</v>
       </c>
       <c r="P18" t="n">
-        <v>-720515.9466670005</v>
+        <v>2111416.993355886</v>
       </c>
       <c r="Q18" t="n">
-        <v>-720515.9466670005</v>
+        <v>1055708.496677943</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I19" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J19" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K19" t="n">
         <v>-64000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="M19" t="n">
         <v>0.05821004393128892</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02537722477452231</v>
       </c>
       <c r="P19" t="n">
-        <v>124961.8868000788</v>
+        <v>-457178.0484005649</v>
       </c>
       <c r="Q19" t="n">
-        <v>62480.9434000394</v>
+        <v>-457178.0484005649</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J20" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K20" t="n">
         <v>-64000000</v>
       </c>
       <c r="L20" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="M20" t="n">
         <v>0.05808035784574397</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02547134730704866</v>
       </c>
       <c r="P20" t="n">
-        <v>-6419457.824492295</v>
+        <v>-6883421.99044755</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6419457.824492295</v>
+        <v>-6883421.99044755</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I21" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J21" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K21" t="n">
         <v>-32000000</v>
       </c>
       <c r="L21" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="M21" t="n">
         <v>0.0579990267461179</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02556388968728518</v>
       </c>
       <c r="P21" t="n">
-        <v>-8143026.263828925</v>
+        <v>-6303226.14261768</v>
       </c>
       <c r="Q21" t="n">
-        <v>-8143026.263828925</v>
+        <v>-6303226.14261768</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I22" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J22" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K22" t="n">
         <v>-32000000</v>
       </c>
       <c r="L22" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="M22" t="n">
         <v>0.05738520780446178</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02564879692438105</v>
       </c>
       <c r="P22" t="n">
-        <v>628399.8318241333</v>
+        <v>644081.1605327394</v>
       </c>
       <c r="Q22" t="n">
-        <v>314199.9159120666</v>
+        <v>322040.5802663697</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I23" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J23" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K23" t="n">
         <v>-32000000</v>
       </c>
       <c r="L23" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="M23" t="n">
         <v>0.05695407285841891</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02573394353653935</v>
       </c>
       <c r="P23" t="n">
-        <v>533348.481261157</v>
+        <v>547110.895083079</v>
       </c>
       <c r="Q23" t="n">
-        <v>266674.2406305785</v>
+        <v>273555.4475415395</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I24" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J24" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K24" t="n">
         <v>-32000000</v>
       </c>
       <c r="L24" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="M24" t="n">
         <v>0.05664439372837885</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02581887365352179</v>
       </c>
       <c r="P24" t="n">
-        <v>70249.21353105344</v>
+        <v>-548667.7416344541</v>
       </c>
       <c r="Q24" t="n">
-        <v>35124.60676552672</v>
+        <v>-548667.7416344541</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I25" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J25" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K25" t="n">
         <v>-32000000</v>
       </c>
       <c r="L25" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="M25" t="n">
         <v>0.05642057743315654</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02590450870981425</v>
       </c>
       <c r="P25" t="n">
-        <v>269813.2755731399</v>
+        <v>277813.1688280281</v>
       </c>
       <c r="Q25" t="n">
-        <v>134906.6377865699</v>
+        <v>138906.5844140141</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I26" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J26" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K26" t="n">
         <v>-32000000</v>
       </c>
       <c r="L26" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="M26" t="n">
         <v>0.05625883751011833</v>
@@ -2974,10 +2974,10 @@
         <v>-0.025990262065432</v>
       </c>
       <c r="P26" t="n">
-        <v>133644.7948299611</v>
+        <v>137718.1561924235</v>
       </c>
       <c r="Q26" t="n">
-        <v>66822.39741498054</v>
+        <v>68859.07809621173</v>
       </c>
     </row>
     <row r="27">
@@ -3011,34 +3011,34 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I27" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J27" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K27" t="n">
         <v>-32000000</v>
       </c>
       <c r="L27" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="M27" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N27" t="n">
-        <v>0.03005395945905409</v>
+        <v>0.030045538435584</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.02607590923562264</v>
+        <v>-0.02607571680048659</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K28" t="n">
         <v>-640000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M28" t="n">
         <v>0.1050151041880321</v>
@@ -3096,10 +3096,10 @@
         <v>-0.07502986587896165</v>
       </c>
       <c r="P28" t="n">
-        <v>22405575.63751067</v>
+        <v>22675927.76655857</v>
       </c>
       <c r="Q28" t="n">
-        <v>11202787.81875534</v>
+        <v>11337963.88327928</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I29" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J29" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K29" t="n">
         <v>-64000000</v>
       </c>
       <c r="L29" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="M29" t="n">
         <v>0.05822765833026367</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01988106139069767</v>
       </c>
       <c r="P29" t="n">
-        <v>-1542432.377839391</v>
+        <v>-2344997.825357669</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1542432.377839391</v>
+        <v>-2344997.825357669</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J30" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K30" t="n">
         <v>-64000000</v>
       </c>
       <c r="L30" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="M30" t="n">
         <v>0.05839364669442126</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01725628309459371</v>
       </c>
       <c r="P30" t="n">
-        <v>-21824219.69005828</v>
+        <v>-23122513.36915437</v>
       </c>
       <c r="Q30" t="n">
-        <v>-21824219.69005828</v>
+        <v>-23122513.36915437</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I31" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J31" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K31" t="n">
         <v>-64000000</v>
       </c>
       <c r="L31" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="M31" t="n">
         <v>0.05851824187679444</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01489062910622074</v>
       </c>
       <c r="P31" t="n">
-        <v>-424322.7086252528</v>
+        <v>1243445.314156556</v>
       </c>
       <c r="Q31" t="n">
-        <v>-424322.7086252528</v>
+        <v>621722.657078278</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I32" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J32" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K32" t="n">
         <v>-64000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="M32" t="n">
         <v>0.05821004393128892</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01266202848122933</v>
       </c>
       <c r="P32" t="n">
-        <v>62350.03960398726</v>
+        <v>-228110.1074398218</v>
       </c>
       <c r="Q32" t="n">
-        <v>31175.01980199363</v>
+        <v>-228110.1074398218</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I33" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J33" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K33" t="n">
         <v>-64000000</v>
       </c>
       <c r="L33" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="M33" t="n">
         <v>0.05808035784574397</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01061579379409725</v>
       </c>
       <c r="P33" t="n">
-        <v>-2675462.735175219</v>
+        <v>-2868830.909000414</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2675462.735175219</v>
+        <v>-2868830.909000414</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I34" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J34" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K34" t="n">
         <v>-32000000</v>
       </c>
       <c r="L34" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="M34" t="n">
         <v>0.0579990267461179</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008701770963537303</v>
       </c>
       <c r="P34" t="n">
-        <v>-2771829.731887456</v>
+        <v>-2145574.515278884</v>
       </c>
       <c r="Q34" t="n">
-        <v>-2771829.731887456</v>
+        <v>-2145574.515278884</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I35" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J35" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K35" t="n">
         <v>-32000000</v>
       </c>
       <c r="L35" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="M35" t="n">
         <v>0.05738520780446178</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006933843412663093</v>
       </c>
       <c r="P35" t="n">
-        <v>169880.3280036305</v>
+        <v>174119.5864019305</v>
       </c>
       <c r="Q35" t="n">
-        <v>84940.16400181527</v>
+        <v>87059.79320096526</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I36" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J36" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K36" t="n">
         <v>-32000000</v>
       </c>
       <c r="L36" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="M36" t="n">
         <v>0.05695407285841891</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005293779960104272</v>
       </c>
       <c r="P36" t="n">
-        <v>109716.1613743111</v>
+        <v>112547.2544941707</v>
       </c>
       <c r="Q36" t="n">
-        <v>54858.08068715555</v>
+        <v>56273.62724708537</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I37" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J37" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K37" t="n">
         <v>-32000000</v>
       </c>
       <c r="L37" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="M37" t="n">
         <v>0.05664439372837885</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003768699327115023</v>
       </c>
       <c r="P37" t="n">
-        <v>10254.05551449096</v>
+        <v>-80087.29491673374</v>
       </c>
       <c r="Q37" t="n">
-        <v>5127.027757245482</v>
+        <v>-80087.29491673374</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I38" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J38" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K38" t="n">
         <v>-32000000</v>
       </c>
       <c r="L38" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="M38" t="n">
         <v>0.05642057743315654</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002356874069323035</v>
       </c>
       <c r="P38" t="n">
-        <v>24548.46451175965</v>
+        <v>25276.32008242542</v>
       </c>
       <c r="Q38" t="n">
-        <v>12274.23225587983</v>
+        <v>12638.16004121271</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I39" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J39" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K39" t="n">
         <v>-32000000</v>
       </c>
       <c r="L39" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="M39" t="n">
         <v>0.05625883751011833</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001044890098674874</v>
       </c>
       <c r="P39" t="n">
-        <v>5372.94016142273</v>
+        <v>5536.702071373712</v>
       </c>
       <c r="Q39" t="n">
-        <v>2686.470080711365</v>
+        <v>2768.351035686856</v>
       </c>
     </row>
     <row r="40">
@@ -3804,34 +3804,34 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I40" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J40" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K40" t="n">
         <v>-32000000</v>
       </c>
       <c r="L40" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05630391743831353</v>
+        <v>0.05629528248589444</v>
       </c>
       <c r="O40" t="n">
-        <v>0.000174048743636801</v>
+        <v>0.0001740272498238493</v>
       </c>
       <c r="P40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K41" t="n">
         <v>-640000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M41" t="n">
         <v>0.1050151041880321</v>
@@ -3889,10 +3889,10 @@
         <v>-0.02468474605999638</v>
       </c>
       <c r="P41" t="n">
-        <v>7371410.550462875</v>
+        <v>7460356.113328367</v>
       </c>
       <c r="Q41" t="n">
-        <v>3685705.275231437</v>
+        <v>3730178.056664183</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I42" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J42" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K42" t="n">
         <v>-64000000</v>
       </c>
       <c r="L42" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="M42" t="n">
         <v>0.05822765833026367</v>
@@ -3950,10 +3950,10 @@
         <v>0.02495849603761435</v>
       </c>
       <c r="P42" t="n">
-        <v>472123.2204589952</v>
+        <v>1479656.276575584</v>
       </c>
       <c r="Q42" t="n">
-        <v>236061.6102294976</v>
+        <v>739828.1382877921</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I43" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J43" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K43" t="n">
         <v>-64000000</v>
       </c>
       <c r="L43" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="M43" t="n">
         <v>0.05839364669442126</v>
@@ -4011,10 +4011,10 @@
         <v>0.02216014487646945</v>
       </c>
       <c r="P43" t="n">
-        <v>26844315.69030953</v>
+        <v>28511556.30425076</v>
       </c>
       <c r="Q43" t="n">
-        <v>13422157.84515477</v>
+        <v>14255778.15212538</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I44" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J44" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K44" t="n">
         <v>-64000000</v>
       </c>
       <c r="L44" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="M44" t="n">
         <v>0.05851824187679444</v>
@@ -4072,10 +4072,10 @@
         <v>0.01962016480210327</v>
       </c>
       <c r="P44" t="n">
-        <v>-382672.5618011282</v>
+        <v>-2580154.160814768</v>
       </c>
       <c r="Q44" t="n">
-        <v>-382672.5618011282</v>
+        <v>-2580154.160814768</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I45" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J45" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K45" t="n">
         <v>-64000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="M45" t="n">
         <v>0.05821004393128892</v>
@@ -4133,10 +4133,10 @@
         <v>0.01722340313955706</v>
       </c>
       <c r="P45" t="n">
-        <v>-819676.245664854</v>
+        <v>-424580.6086642931</v>
       </c>
       <c r="Q45" t="n">
-        <v>-819676.245664854</v>
+        <v>-424580.6086642931</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J46" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K46" t="n">
         <v>-64000000</v>
       </c>
       <c r="L46" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="M46" t="n">
         <v>0.05808035784574397</v>
@@ -4194,10 +4194,10 @@
         <v>0.01501522413586098</v>
       </c>
       <c r="P46" t="n">
-        <v>3223667.970587295</v>
+        <v>3497172.385522508</v>
       </c>
       <c r="Q46" t="n">
-        <v>1611833.985293648</v>
+        <v>1748586.192761254</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I47" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J47" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K47" t="n">
         <v>-32000000</v>
       </c>
       <c r="L47" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="M47" t="n">
         <v>0.0579990267461179</v>
@@ -4255,10 +4255,10 @@
         <v>0.01294941997535037</v>
       </c>
       <c r="P47" t="n">
-        <v>3917669.317365836</v>
+        <v>2985716.287850357</v>
       </c>
       <c r="Q47" t="n">
-        <v>1958834.658682918</v>
+        <v>1492858.143925178</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I48" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J48" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K48" t="n">
         <v>-32000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="M48" t="n">
         <v>0.05738520780446178</v>
@@ -4316,10 +4316,10 @@
         <v>0.01103784963125674</v>
       </c>
       <c r="P48" t="n">
-        <v>-417600.4979575885</v>
+        <v>-424348.8904383044</v>
       </c>
       <c r="Q48" t="n">
-        <v>-417600.4979575885</v>
+        <v>-424348.8904383044</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I49" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J49" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K49" t="n">
         <v>-32000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="M49" t="n">
         <v>0.05695407285841891</v>
@@ -4377,10 +4377,10 @@
         <v>0.009264716116377802</v>
       </c>
       <c r="P49" t="n">
-        <v>-290839.3808556934</v>
+        <v>-295794.115327508</v>
       </c>
       <c r="Q49" t="n">
-        <v>-290839.3808556934</v>
+        <v>-295794.115327508</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I50" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J50" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K50" t="n">
         <v>-32000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="M50" t="n">
         <v>0.05664439372837885</v>
@@ -4438,10 +4438,10 @@
         <v>0.007618063727031256</v>
       </c>
       <c r="P50" t="n">
-        <v>-81672.09819346003</v>
+        <v>100944.2649160843</v>
       </c>
       <c r="Q50" t="n">
-        <v>-81672.09819346003</v>
+        <v>50472.13245804216</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I51" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J51" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K51" t="n">
         <v>-32000000</v>
       </c>
       <c r="L51" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="M51" t="n">
         <v>0.05642057743315654</v>
@@ -4499,10 +4499,10 @@
         <v>0.006094907231449384</v>
       </c>
       <c r="P51" t="n">
-        <v>-95988.82285011387</v>
+        <v>-97871.06689481827</v>
       </c>
       <c r="Q51" t="n">
-        <v>-95988.82285011387</v>
+        <v>-97871.06689481827</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I52" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J52" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K52" t="n">
         <v>-32000000</v>
       </c>
       <c r="L52" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="M52" t="n">
         <v>0.05625883751011833</v>
@@ -4560,10 +4560,10 @@
         <v>0.004682431355023151</v>
       </c>
       <c r="P52" t="n">
-        <v>-36564.06221464201</v>
+        <v>-37297.923032048</v>
       </c>
       <c r="Q52" t="n">
-        <v>-36564.06221464201</v>
+        <v>-37297.923032048</v>
       </c>
     </row>
     <row r="53">
@@ -4597,34 +4597,34 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I53" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J53" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K53" t="n">
         <v>-32000000</v>
       </c>
       <c r="L53" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N53" t="n">
-        <v>0.05950311578357481</v>
+        <v>0.05949445427920219</v>
       </c>
       <c r="O53" t="n">
-        <v>0.003373247088898079</v>
+        <v>0.003373199043131603</v>
       </c>
       <c r="P53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K54" t="n">
         <v>-640000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M54" t="n">
         <v>0.1050151041880321</v>
@@ -4682,10 +4682,10 @@
         <v>-0.01765980557248192</v>
       </c>
       <c r="P54" t="n">
-        <v>5273608.114084664</v>
+        <v>5337240.988529545</v>
       </c>
       <c r="Q54" t="n">
-        <v>2636804.057042332</v>
+        <v>2668620.494264773</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I55" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J55" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K55" t="n">
         <v>-64000000</v>
       </c>
       <c r="L55" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="M55" t="n">
         <v>0.05822765833026367</v>
@@ -4743,10 +4743,10 @@
         <v>0.03235719235381929</v>
       </c>
       <c r="P55" t="n">
-        <v>612079.4232181845</v>
+        <v>1918285.568430772</v>
       </c>
       <c r="Q55" t="n">
-        <v>306039.7116090923</v>
+        <v>959142.7842153859</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I56" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J56" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K56" t="n">
         <v>-64000000</v>
       </c>
       <c r="L56" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="M56" t="n">
         <v>0.05839364669442126</v>
@@ -4804,10 +4804,10 @@
         <v>0.02992819194854235</v>
       </c>
       <c r="P56" t="n">
-        <v>36254358.31694114</v>
+        <v>38506035.70427726</v>
       </c>
       <c r="Q56" t="n">
-        <v>18127179.15847057</v>
+        <v>19253017.85213863</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I57" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J57" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K57" t="n">
         <v>-64000000</v>
       </c>
       <c r="L57" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="M57" t="n">
         <v>0.05851824187679444</v>
@@ -4865,10 +4865,10 @@
         <v>0.02772661859587089</v>
       </c>
       <c r="P57" t="n">
-        <v>-540781.1950196924</v>
+        <v>-3646195.180164413</v>
       </c>
       <c r="Q57" t="n">
-        <v>-540781.1950196924</v>
+        <v>-3646195.180164413</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I58" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J58" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K58" t="n">
         <v>-64000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="M58" t="n">
         <v>0.05821004393128892</v>
@@ -4926,10 +4926,10 @@
         <v>0.02564903369930005</v>
       </c>
       <c r="P58" t="n">
-        <v>-1220659.092585942</v>
+        <v>-632284.0063290679</v>
       </c>
       <c r="Q58" t="n">
-        <v>-1220659.092585942</v>
+        <v>-632284.0063290679</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I59" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J59" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K59" t="n">
         <v>-64000000</v>
       </c>
       <c r="L59" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="M59" t="n">
         <v>0.05808035784574397</v>
@@ -4987,10 +4987,10 @@
         <v>0.02373722363569292</v>
       </c>
       <c r="P59" t="n">
-        <v>5096222.797120655</v>
+        <v>5528599.657027863</v>
       </c>
       <c r="Q59" t="n">
-        <v>2548111.398560327</v>
+        <v>2764299.828513931</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J60" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K60" t="n">
         <v>-32000000</v>
       </c>
       <c r="L60" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="M60" t="n">
         <v>0.0579990267461179</v>
@@ -5048,10 +5048,10 @@
         <v>0.02195017150422629</v>
       </c>
       <c r="P60" t="n">
-        <v>6640723.181170784</v>
+        <v>5060997.689937379</v>
       </c>
       <c r="Q60" t="n">
-        <v>3320361.590585392</v>
+        <v>2530498.84496869</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I61" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J61" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K61" t="n">
         <v>-32000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="M61" t="n">
         <v>0.05738520780446178</v>
@@ -5109,10 +5109,10 @@
         <v>0.02029522229252897</v>
       </c>
       <c r="P61" t="n">
-        <v>-767839.318223714</v>
+        <v>-780247.5435654979</v>
       </c>
       <c r="Q61" t="n">
-        <v>-767839.318223714</v>
+        <v>-780247.5435654979</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I62" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J62" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K62" t="n">
         <v>-32000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="M62" t="n">
         <v>0.05695407285841891</v>
@@ -5170,10 +5170,10 @@
         <v>0.01876196760334525</v>
       </c>
       <c r="P62" t="n">
-        <v>-588978.5475180765</v>
+        <v>-599012.3754816803</v>
       </c>
       <c r="Q62" t="n">
-        <v>-588978.5475180765</v>
+        <v>-599012.3754816803</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I63" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J63" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K63" t="n">
         <v>-32000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="M63" t="n">
         <v>0.05664439372837885</v>
@@ -5231,10 +5231,10 @@
         <v>0.01733996627504109</v>
       </c>
       <c r="P63" t="n">
-        <v>-185899.1312006691</v>
+        <v>229765.7530866877</v>
       </c>
       <c r="Q63" t="n">
-        <v>-185899.1312006691</v>
+        <v>114882.8765433439</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I64" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J64" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K64" t="n">
         <v>-32000000</v>
       </c>
       <c r="L64" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="M64" t="n">
         <v>0.05642057743315654</v>
@@ -5292,10 +5292,10 @@
         <v>0.01602670204966161</v>
       </c>
       <c r="P64" t="n">
-        <v>-252404.8694258294</v>
+        <v>-257354.2744526314</v>
       </c>
       <c r="Q64" t="n">
-        <v>-252404.8694258294</v>
+        <v>-257354.2744526314</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I65" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J65" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K65" t="n">
         <v>-32000000</v>
       </c>
       <c r="L65" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="M65" t="n">
         <v>0.05625883751011833</v>
@@ -5353,10 +5353,10 @@
         <v>0.01481092208165177</v>
       </c>
       <c r="P65" t="n">
-        <v>-115655.1875274748</v>
+        <v>-117976.4506835737</v>
       </c>
       <c r="Q65" t="n">
-        <v>-115655.1875274748</v>
+        <v>-117976.4506835737</v>
       </c>
     </row>
     <row r="66">
@@ -5390,34 +5390,34 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I66" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J66" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K66" t="n">
         <v>-32000000</v>
       </c>
       <c r="L66" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="M66" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N66" t="n">
-        <v>0.06981591961576861</v>
+        <v>0.06980717394620273</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01368605092109187</v>
+        <v>0.01368591871013214</v>
       </c>
       <c r="P66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K67" t="n">
         <v>-640000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M67" t="n">
         <v>0.1050151041880321</v>
@@ -5475,10 +5475,10 @@
         <v>-0.08728823124945828</v>
       </c>
       <c r="P67" t="n">
-        <v>26066194.36957637</v>
+        <v>26380716.57860157</v>
       </c>
       <c r="Q67" t="n">
-        <v>13033097.18478818</v>
+        <v>13190358.28930079</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I68" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J68" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K68" t="n">
         <v>-64000000</v>
       </c>
       <c r="L68" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="M68" t="n">
         <v>0.05822765833026367</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03226565096877909</v>
       </c>
       <c r="P68" t="n">
-        <v>-2503265.98607034</v>
+        <v>-3805776.757519552</v>
       </c>
       <c r="Q68" t="n">
-        <v>-2503265.98607034</v>
+        <v>-3805776.757519552</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I69" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J69" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K69" t="n">
         <v>-64000000</v>
       </c>
       <c r="L69" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="M69" t="n">
         <v>0.05839364669442126</v>
@@ -5597,10 +5597,10 @@
         <v>-0.0297728173926024</v>
       </c>
       <c r="P69" t="n">
-        <v>-37654024.56637441</v>
+        <v>-39894012.19394226</v>
       </c>
       <c r="Q69" t="n">
-        <v>-37654024.56637441</v>
+        <v>-39894012.19394226</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I70" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J70" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K70" t="n">
         <v>-64000000</v>
       </c>
       <c r="L70" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="M70" t="n">
         <v>0.05851824187679444</v>
@@ -5658,10 +5658,10 @@
         <v>-0.02753489969717293</v>
       </c>
       <c r="P70" t="n">
-        <v>-784633.2843216185</v>
+        <v>2299307.958044368</v>
       </c>
       <c r="Q70" t="n">
-        <v>-784633.2843216185</v>
+        <v>1149653.979022184</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I71" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J71" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K71" t="n">
         <v>-64000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="M71" t="n">
         <v>0.05821004393128892</v>
@@ -5719,10 +5719,10 @@
         <v>-0.02543179398870032</v>
       </c>
       <c r="P71" t="n">
-        <v>125230.5951409423</v>
+        <v>-458161.1285861375</v>
       </c>
       <c r="Q71" t="n">
-        <v>62615.29757047114</v>
+        <v>-458161.1285861375</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J72" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K72" t="n">
         <v>-64000000</v>
       </c>
       <c r="L72" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="M72" t="n">
         <v>0.05808035784574397</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02350867571892774</v>
       </c>
       <c r="P72" t="n">
-        <v>-5924812.318253805</v>
+        <v>-6353026.145781747</v>
       </c>
       <c r="Q72" t="n">
-        <v>-5924812.318253805</v>
+        <v>-6353026.145781747</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I73" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J73" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K73" t="n">
         <v>-32000000</v>
       </c>
       <c r="L73" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="M73" t="n">
         <v>0.0579990267461179</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02171656780992581</v>
       </c>
       <c r="P73" t="n">
-        <v>-6917514.674005289</v>
+        <v>-5354601.338916618</v>
       </c>
       <c r="Q73" t="n">
-        <v>-6917514.674005289</v>
+        <v>-5354601.338916618</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I74" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J74" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K74" t="n">
         <v>-32000000</v>
       </c>
       <c r="L74" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="M74" t="n">
         <v>0.05738520780446178</v>
@@ -5902,10 +5902,10 @@
         <v>-0.02006419037968943</v>
       </c>
       <c r="P74" t="n">
-        <v>491576.0336618008</v>
+        <v>503843.0092062514</v>
       </c>
       <c r="Q74" t="n">
-        <v>245788.0168309004</v>
+        <v>251921.5046031257</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I75" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J75" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K75" t="n">
         <v>-32000000</v>
       </c>
       <c r="L75" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="M75" t="n">
         <v>0.05695407285841891</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01853809135614659</v>
       </c>
       <c r="P75" t="n">
-        <v>384210.949100846</v>
+        <v>394125.0489102915</v>
       </c>
       <c r="Q75" t="n">
-        <v>192105.474550423</v>
+        <v>197062.5244551457</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I76" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J76" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K76" t="n">
         <v>-32000000</v>
       </c>
       <c r="L76" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="M76" t="n">
         <v>0.05664439372837885</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01712553721773909</v>
       </c>
       <c r="P76" t="n">
-        <v>46595.97227158104</v>
+        <v>-363928.7273189013</v>
       </c>
       <c r="Q76" t="n">
-        <v>23297.98613579052</v>
+        <v>-363928.7273189013</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I77" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J77" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K77" t="n">
         <v>-32000000</v>
       </c>
       <c r="L77" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="M77" t="n">
         <v>0.05642057743315654</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01582455504283544</v>
       </c>
       <c r="P77" t="n">
-        <v>164823.625046294</v>
+        <v>169710.6025437991</v>
       </c>
       <c r="Q77" t="n">
-        <v>82411.81252314699</v>
+        <v>84855.30127189953</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I78" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J78" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K78" t="n">
         <v>-32000000</v>
       </c>
       <c r="L78" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="M78" t="n">
         <v>0.05625883751011833</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01462200030522725</v>
       </c>
       <c r="P78" t="n">
-        <v>75187.93869319312</v>
+        <v>77479.59281100379</v>
       </c>
       <c r="Q78" t="n">
-        <v>37593.96934659656</v>
+        <v>38739.7964055019</v>
       </c>
     </row>
     <row r="79">
@@ -6183,34 +6183,34 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I79" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J79" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K79" t="n">
         <v>-32000000</v>
       </c>
       <c r="L79" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="M79" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N79" t="n">
-        <v>0.04261896504062945</v>
+        <v>0.04261044181554507</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.01351090365404728</v>
+        <v>-0.01351081342052551</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="80">
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-939442484.0499998</v>
+        <v>-943055643.3100001</v>
       </c>
       <c r="K80" t="n">
         <v>-640000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-299442484.0499998</v>
+        <v>-303055643.3100001</v>
       </c>
       <c r="M80" t="n">
         <v>0.1050151041880321</v>
@@ -6268,10 +6268,10 @@
         <v>-0.06247613761654947</v>
       </c>
       <c r="P80" t="n">
-        <v>18656755.02026496</v>
+        <v>18881872.79998446</v>
       </c>
       <c r="Q80" t="n">
-        <v>9328377.51013248</v>
+        <v>9440936.399992229</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>575699100.39</v>
+        <v>548709791.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-555063100.8309005</v>
+        <v>-484035602.7846395</v>
       </c>
       <c r="J81" t="n">
-        <v>20635999.55909944</v>
+        <v>64674188.74536043</v>
       </c>
       <c r="K81" t="n">
         <v>-64000000</v>
       </c>
       <c r="L81" t="n">
-        <v>84635999.55909944</v>
+        <v>128674188.7453604</v>
       </c>
       <c r="M81" t="n">
         <v>0.05822765833026367</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01004192341464538</v>
       </c>
       <c r="P81" t="n">
-        <v>-779082.5402199004</v>
+        <v>-1184458.31975399</v>
       </c>
       <c r="Q81" t="n">
-        <v>-779082.5402199004</v>
+        <v>-1184458.31975399</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>1961135371.76</v>
+        <v>1990072267.9</v>
       </c>
       <c r="I82" t="n">
-        <v>-507481570.8511116</v>
+        <v>-446135269.4812486</v>
       </c>
       <c r="J82" t="n">
-        <v>1453653800.908888</v>
+        <v>1543936998.418751</v>
       </c>
       <c r="K82" t="n">
         <v>-64000000</v>
       </c>
       <c r="L82" t="n">
-        <v>1517653800.908888</v>
+        <v>1607936998.418751</v>
       </c>
       <c r="M82" t="n">
         <v>0.05839364669442126</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01008473632087492</v>
       </c>
       <c r="P82" t="n">
-        <v>-12754282.00711645</v>
+        <v>-13513017.20802682</v>
       </c>
       <c r="Q82" t="n">
-        <v>-12754282.00711645</v>
+        <v>-13513017.20802682</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>531970690.13</v>
+        <v>321318332.1300001</v>
       </c>
       <c r="I83" t="n">
-        <v>-557976082.4163486</v>
+        <v>-496658630.361554</v>
       </c>
       <c r="J83" t="n">
-        <v>-26005392.28634858</v>
+        <v>-175340298.2315539</v>
       </c>
       <c r="K83" t="n">
         <v>-64000000</v>
       </c>
       <c r="L83" t="n">
-        <v>37994607.71365142</v>
+        <v>-111340298.2315539</v>
       </c>
       <c r="M83" t="n">
         <v>0.05851824187679444</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01013182991584927</v>
       </c>
       <c r="P83" t="n">
-        <v>-288716.177305598</v>
+        <v>846060.7233465279</v>
       </c>
       <c r="Q83" t="n">
-        <v>-288716.177305598</v>
+        <v>423030.3616732639</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>78498009.31000002</v>
+        <v>82481230.3</v>
       </c>
       <c r="I84" t="n">
-        <v>-149884271.2777902</v>
+        <v>-119458296.2048057</v>
       </c>
       <c r="J84" t="n">
-        <v>-71386261.96779023</v>
+        <v>-36977065.90480575</v>
       </c>
       <c r="K84" t="n">
         <v>-64000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-7386261.967790231</v>
+        <v>27022934.09519425</v>
       </c>
       <c r="M84" t="n">
         <v>0.05821004393128892</v>
@@ -6512,10 +6512,10 @@
         <v>-0.01017508542911516</v>
       </c>
       <c r="P84" t="n">
-        <v>50103.89768272657</v>
+        <v>-183307.1086426336</v>
       </c>
       <c r="Q84" t="n">
-        <v>25051.94884136329</v>
+        <v>-183307.1086426336</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>517889994.42</v>
+        <v>518697858.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-149844342.9148888</v>
+        <v>-119426252.4590164</v>
       </c>
       <c r="J85" t="n">
-        <v>368045651.5051111</v>
+        <v>399271606.3809837</v>
       </c>
       <c r="K85" t="n">
         <v>-64000000</v>
       </c>
       <c r="L85" t="n">
-        <v>432045651.5051111</v>
+        <v>463271606.3809837</v>
       </c>
       <c r="M85" t="n">
         <v>0.05808035784574397</v>
@@ -6573,10 +6573,10 @@
         <v>-0.01021994033044944</v>
       </c>
       <c r="P85" t="n">
-        <v>-2575697.12074056</v>
+        <v>-2761854.76816965</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2575697.12074056</v>
+        <v>-2761854.76816965</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>902503166.1700001</v>
+        <v>669118580.01</v>
       </c>
       <c r="I86" t="n">
-        <v>-297430610.8241635</v>
+        <v>-207983441.3653717</v>
       </c>
       <c r="J86" t="n">
-        <v>605072555.3458366</v>
+        <v>461135138.6446283</v>
       </c>
       <c r="K86" t="n">
         <v>-32000000</v>
       </c>
       <c r="L86" t="n">
-        <v>637072555.3458366</v>
+        <v>493135138.6446283</v>
       </c>
       <c r="M86" t="n">
         <v>0.0579990267461179</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01026331977023442</v>
       </c>
       <c r="P86" t="n">
-        <v>-3269239.676177345</v>
+        <v>-2530601.808924354</v>
       </c>
       <c r="Q86" t="n">
-        <v>-3269239.676177345</v>
+        <v>-2530601.808924354</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-154283223.6</v>
+        <v>-153952841.84</v>
       </c>
       <c r="I87" t="n">
-        <v>63482820.57040198</v>
+        <v>61685111.16101505</v>
       </c>
       <c r="J87" t="n">
-        <v>-90800403.02959804</v>
+        <v>-92267730.67898495</v>
       </c>
       <c r="K87" t="n">
         <v>-32000000</v>
       </c>
       <c r="L87" t="n">
-        <v>-58800403.02959804</v>
+        <v>-60267730.67898495</v>
       </c>
       <c r="M87" t="n">
         <v>0.05738520780446178</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01030407096516736</v>
       </c>
       <c r="P87" t="n">
-        <v>252451.4689989251</v>
+        <v>258751.2390941062</v>
       </c>
       <c r="Q87" t="n">
-        <v>126225.7344994625</v>
+        <v>129375.6195470531</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-105494922.47</v>
+        <v>-105287618.79</v>
       </c>
       <c r="I88" t="n">
-        <v>11318465.07972154</v>
+        <v>9506772.962048057</v>
       </c>
       <c r="J88" t="n">
-        <v>-94176457.39027846</v>
+        <v>-95780845.82795194</v>
       </c>
       <c r="K88" t="n">
         <v>-32000000</v>
       </c>
       <c r="L88" t="n">
-        <v>-62176457.39027846</v>
+        <v>-63780845.82795194</v>
       </c>
       <c r="M88" t="n">
         <v>0.05695407285841891</v>
@@ -6756,10 +6756,10 @@
         <v>-0.01034491853166675</v>
       </c>
       <c r="P88" t="n">
-        <v>214403.4620966932</v>
+        <v>219935.8846569866</v>
       </c>
       <c r="Q88" t="n">
-        <v>107201.7310483466</v>
+        <v>109967.9423284933</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-106354032.72</v>
+        <v>-8670744.480000019</v>
       </c>
       <c r="I89" t="n">
-        <v>63470643.38648102</v>
+        <v>61673328.09342016</v>
       </c>
       <c r="J89" t="n">
-        <v>-42883389.333519</v>
+        <v>53002583.61342014</v>
       </c>
       <c r="K89" t="n">
         <v>-32000000</v>
       </c>
       <c r="L89" t="n">
-        <v>-10883389.333519</v>
+        <v>85002583.61342014</v>
       </c>
       <c r="M89" t="n">
         <v>0.05664439372837885</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01038544122264451</v>
       </c>
       <c r="P89" t="n">
-        <v>28257.20005660443</v>
+        <v>-220697.3339725251</v>
       </c>
       <c r="Q89" t="n">
-        <v>14128.60002830222</v>
+        <v>-220697.3339725251</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>-105737558.25</v>
+        <v>-105791543.79</v>
       </c>
       <c r="I90" t="n">
-        <v>11243431.39456546</v>
+        <v>9444482.371434988</v>
       </c>
       <c r="J90" t="n">
-        <v>-94494126.85543452</v>
+        <v>-96347061.41856501</v>
       </c>
       <c r="K90" t="n">
         <v>-32000000</v>
       </c>
       <c r="L90" t="n">
-        <v>-62494126.85543452</v>
+        <v>-64347061.41856501</v>
       </c>
       <c r="M90" t="n">
         <v>0.05642057743315654</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01042652380310684</v>
       </c>
       <c r="P90" t="n">
-        <v>108599.4168687611</v>
+        <v>111819.3612567743</v>
       </c>
       <c r="Q90" t="n">
-        <v>54299.70843438055</v>
+        <v>55909.68062838717</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>-105013009.69</v>
+        <v>-105084497.29</v>
       </c>
       <c r="I91" t="n">
-        <v>11307685.82977768</v>
+        <v>9498456.09701325</v>
       </c>
       <c r="J91" t="n">
-        <v>-93705323.86022232</v>
+        <v>-95586041.19298677</v>
       </c>
       <c r="K91" t="n">
         <v>-32000000</v>
       </c>
       <c r="L91" t="n">
-        <v>-61705323.86022232</v>
+        <v>-63586041.19298677</v>
       </c>
       <c r="M91" t="n">
         <v>0.05625883751011833</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01046759094930644</v>
       </c>
       <c r="P91" t="n">
-        <v>53825.5074636072</v>
+        <v>55466.05577449461</v>
       </c>
       <c r="Q91" t="n">
-        <v>26912.7537318036</v>
+        <v>27733.02788724731</v>
       </c>
     </row>
     <row r="92">
@@ -6976,34 +6976,34 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-86650256.47999999</v>
+        <v>26344865.39000002</v>
       </c>
       <c r="I92" t="n">
-        <v>11236273.29889962</v>
+        <v>9437731.866157647</v>
       </c>
       <c r="J92" t="n">
-        <v>-75413983.18110037</v>
+        <v>35782597.25615767</v>
       </c>
       <c r="K92" t="n">
         <v>-32000000</v>
       </c>
       <c r="L92" t="n">
-        <v>-43413983.18110037</v>
+        <v>67782597.25615767</v>
       </c>
       <c r="M92" t="n">
-        <v>0.05612986869467673</v>
+        <v>0.05612125523607059</v>
       </c>
       <c r="N92" t="n">
-        <v>0.04562123316148581</v>
+        <v>0.04561268519858142</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.01050863553319092</v>
+        <v>-0.01050857003748917</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41834065.10000002</v>
+        <v>27261139.98000002</v>
       </c>
       <c r="D2" t="n">
-        <v>20917032.55000001</v>
+        <v>13630569.99000001</v>
       </c>
       <c r="E2" t="n">
-        <v>2.324114727777779</v>
+        <v>1.703821248750001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.16205736388889</v>
+        <v>0.8519106243750006</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-42041798.58999991</v>
+        <v>-24923766.77999997</v>
       </c>
       <c r="D3" t="n">
-        <v>-42041798.58999991</v>
+        <v>-24923766.77999997</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.335655477222217</v>
+        <v>-1.557735423749998</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.335655477222217</v>
+        <v>-1.557735423749998</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1003055.190000057</v>
+        <v>8734244.889999986</v>
       </c>
       <c r="D4" t="n">
-        <v>501527.5950000286</v>
+        <v>4367122.444999993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05572528833333652</v>
+        <v>0.5458903056249991</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02786264416666826</v>
+        <v>0.2729451528124995</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4421016.350000024</v>
+        <v>-3401887.860000014</v>
       </c>
       <c r="D5" t="n">
-        <v>2210508.175000012</v>
+        <v>-3401887.860000014</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2456120194444457</v>
+        <v>-0.2126179912500009</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1228060097222229</v>
+        <v>-0.2126179912500009</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20762838.7700001</v>
+        <v>7559235.600000024</v>
       </c>
       <c r="D6" t="n">
-        <v>10381419.38500005</v>
+        <v>3779617.800000012</v>
       </c>
       <c r="E6" t="n">
-        <v>1.153491042777783</v>
+        <v>0.4724522250000014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5767455213888917</v>
+        <v>0.2362261125000007</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-20897206.02999997</v>
+        <v>-5138259.879999995</v>
       </c>
       <c r="D7" t="n">
-        <v>-20897206.02999997</v>
+        <v>-5138259.879999995</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.160955890555554</v>
+        <v>-0.3211412424999997</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.160955890555554</v>
+        <v>-0.3211412424999997</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-16852473.81999993</v>
+        <v>-9224288.169999957</v>
       </c>
       <c r="D8" t="n">
-        <v>-16852473.81999993</v>
+        <v>-9224288.169999957</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9362485455555519</v>
+        <v>-0.5765180106249973</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9362485455555519</v>
+        <v>-0.5765180106249973</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="F2" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="J2" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="K2" t="n">
-        <v>-9404719.292187398</v>
+        <v>-13317035.44209644</v>
       </c>
       <c r="L2" t="n">
-        <v>3022253.53876274</v>
+        <v>6535665.579082741</v>
       </c>
       <c r="M2" t="n">
-        <v>-9404719.292187398</v>
+        <v>-13317035.44209644</v>
       </c>
       <c r="N2" t="n">
-        <v>3022253.53876274</v>
+        <v>6535665.579082741</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="F3" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="G3" t="n">
-        <v>612709791.53</v>
+        <v>201911619.36</v>
       </c>
       <c r="H3" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="I3" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="J3" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="K3" t="n">
-        <v>5029839.755691666</v>
+        <v>1227523.177466667</v>
       </c>
       <c r="L3" t="n">
-        <v>-5616506.422358333</v>
+        <v>-1850856.5108</v>
       </c>
       <c r="M3" t="n">
-        <v>592846.730165804</v>
+        <v>400055.6828937197</v>
       </c>
       <c r="N3" t="n">
-        <v>-1179513.396832471</v>
+        <v>-1023389.016227053</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="F4" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="G4" t="n">
-        <v>2054072267.9</v>
+        <v>2432336920.83</v>
       </c>
       <c r="H4" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="I4" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="J4" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="K4" t="n">
-        <v>16583935.56583334</v>
+        <v>19702807.67358333</v>
       </c>
       <c r="L4" t="n">
-        <v>-17117268.89916667</v>
+        <v>-20269474.34025</v>
       </c>
       <c r="M4" t="n">
-        <v>12866141.6534896</v>
+        <v>19273719.77403995</v>
       </c>
       <c r="N4" t="n">
-        <v>-13399474.98682293</v>
+        <v>-19840386.44070662</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="F5" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="G5" t="n">
-        <v>385318332.1300001</v>
+        <v>-89998693</v>
       </c>
       <c r="H5" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="I5" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="J5" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="K5" t="n">
-        <v>2409887.490975001</v>
+        <v>-1184990.1975</v>
       </c>
       <c r="L5" t="n">
-        <v>-2889887.490975001</v>
+        <v>674990.1975</v>
       </c>
       <c r="M5" t="n">
-        <v>-1315052.236736654</v>
+        <v>-1875364.478321918</v>
       </c>
       <c r="N5" t="n">
-        <v>835052.2367366543</v>
+        <v>1365364.478321918</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="F6" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="G6" t="n">
-        <v>146481230.3</v>
+        <v>-126599255.21</v>
       </c>
       <c r="H6" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="I6" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="J6" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="K6" t="n">
-        <v>549874.8686666667</v>
+        <v>-1297328.368066667</v>
       </c>
       <c r="L6" t="n">
-        <v>-976541.5353333335</v>
+        <v>843995.0347333335</v>
       </c>
       <c r="M6" t="n">
-        <v>-246513.772698705</v>
+        <v>-1640384.989071233</v>
       </c>
       <c r="N6" t="n">
-        <v>-180152.8939679617</v>
+        <v>1187051.6557379</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="F7" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="G7" t="n">
-        <v>582697858.84</v>
+        <v>466501812.66</v>
       </c>
       <c r="H7" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="I7" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="J7" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="K7" t="n">
-        <v>3025737.5099</v>
+        <v>2324593.907183333</v>
       </c>
       <c r="L7" t="n">
-        <v>-3399070.843233333</v>
+        <v>-2721260.57385</v>
       </c>
       <c r="M7" t="n">
-        <v>2329084.370555738</v>
+        <v>2024495.03732032</v>
       </c>
       <c r="N7" t="n">
-        <v>-2702417.703889071</v>
+        <v>-2421161.703986986</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="F8" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G8" t="n">
-        <v>701118580.01</v>
+        <v>806422393.1500001</v>
       </c>
       <c r="H8" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="I8" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="J8" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="K8" t="n">
-        <v>3345592.90005</v>
+        <v>3862111.96575</v>
       </c>
       <c r="L8" t="n">
-        <v>-3505592.90005</v>
+        <v>-4032111.96575</v>
       </c>
       <c r="M8" t="n">
-        <v>2305675.693223142</v>
+        <v>3408114.190317708</v>
       </c>
       <c r="N8" t="n">
-        <v>-2465675.693223142</v>
+        <v>-3578114.190317708</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="F9" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-121952841.84</v>
+        <v>-1157733.020000003</v>
       </c>
       <c r="H9" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="I9" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="J9" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="K9" t="n">
-        <v>-641470.1743333333</v>
+        <v>-146490.55425</v>
       </c>
       <c r="L9" t="n">
-        <v>508136.841</v>
+        <v>4823.887583333347</v>
       </c>
       <c r="M9" t="n">
-        <v>-384448.877829104</v>
+        <v>-137127.4844094431</v>
       </c>
       <c r="N9" t="n">
-        <v>251115.5444957706</v>
+        <v>-4539.182257223579</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G10" t="n">
-        <v>-73287618.78999999</v>
+        <v>-1284909.430000007</v>
       </c>
       <c r="H10" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="I10" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="J10" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="K10" t="n">
-        <v>-350958.7293000001</v>
+        <v>-117616.3647666667</v>
       </c>
       <c r="L10" t="n">
-        <v>244292.0626333333</v>
+        <v>4283.031433333358</v>
       </c>
       <c r="M10" t="n">
-        <v>-319269.4860931732</v>
+        <v>-110062.5246588742</v>
       </c>
       <c r="N10" t="n">
-        <v>212602.8194265065</v>
+        <v>-3270.808674459147</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="F11" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G11" t="n">
-        <v>23329255.51999998</v>
+        <v>-1779408.350000001</v>
       </c>
       <c r="H11" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="I11" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="J11" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="K11" t="n">
-        <v>-21676.86120000005</v>
+        <v>-89448.520875</v>
       </c>
       <c r="L11" t="n">
-        <v>-58323.13879999996</v>
+        <v>4448.520875000004</v>
       </c>
       <c r="M11" t="n">
-        <v>132506.4590335504</v>
+        <v>-83828.06837107007</v>
       </c>
       <c r="N11" t="n">
-        <v>-212506.4590335504</v>
+        <v>-1171.931628929935</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G12" t="n">
-        <v>-73791543.78999999</v>
+        <v>-1814156.50999999</v>
       </c>
       <c r="H12" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="I12" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="J12" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="K12" t="n">
-        <v>-176319.23965</v>
+        <v>-59690.26084999997</v>
       </c>
       <c r="L12" t="n">
-        <v>122985.9063166666</v>
+        <v>3023.594183333317</v>
       </c>
       <c r="M12" t="n">
-        <v>-160578.4356976083</v>
+        <v>-55942.45038514481</v>
       </c>
       <c r="N12" t="n">
-        <v>107245.102364275</v>
+        <v>-724.2162815218418</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="F13" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G13" t="n">
-        <v>-73084497.29000002</v>
+        <v>-1845139.960000001</v>
       </c>
       <c r="H13" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="I13" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="J13" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="K13" t="n">
-        <v>-87570.41440833338</v>
+        <v>-29870.94996666668</v>
       </c>
       <c r="L13" t="n">
-        <v>60903.74774166672</v>
+        <v>1537.616633333335</v>
       </c>
       <c r="M13" t="n">
-        <v>-79655.034327489</v>
+        <v>-27986.33566170373</v>
       </c>
       <c r="N13" t="n">
-        <v>52988.36766082233</v>
+        <v>-346.9976716296128</v>
       </c>
     </row>
     <row r="14">
@@ -1087,31 +1087,31 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="G14" t="n">
-        <v>58344865.39000002</v>
+        <v>-2463708.530000009</v>
       </c>
       <c r="H14" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="I14" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="J14" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="K14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>-0</v>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20262153.38003761</v>
+        <v>10874566.06561189</v>
       </c>
       <c r="C2" t="n">
-        <v>-29604619.13346227</v>
+        <v>-20800935.92862559</v>
       </c>
       <c r="D2" t="n">
-        <v>6316017.770897699</v>
+        <v>7858652.911595874</v>
       </c>
       <c r="E2" t="n">
-        <v>-15658483.52432236</v>
+        <v>-17785022.77460957</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-106563147.18</v>
+        <v>-62182847.84</v>
       </c>
       <c r="D2" t="n">
-        <v>-25848911.73608779</v>
+        <v>-92931037.85249965</v>
       </c>
       <c r="E2" t="n">
-        <v>-132412058.9160878</v>
+        <v>-155113885.6924997</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>87225562.51000001</v>
+        <v>95246548.3</v>
       </c>
       <c r="D3" t="n">
-        <v>5260169.800000001</v>
+        <v>-53934.26191780856</v>
       </c>
       <c r="E3" t="n">
-        <v>92485732.31</v>
+        <v>95192614.0380822</v>
       </c>
     </row>
     <row r="4">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-18501945.84</v>
+        <v>-4807833.930000001</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-18501945.84</v>
+        <v>-4807833.930000001</v>
       </c>
     </row>
     <row r="5">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>570375617.05</v>
+        <v>620220848.35</v>
       </c>
       <c r="D5" t="n">
-        <v>56431275.63671397</v>
+        <v>59143938.52582265</v>
       </c>
       <c r="E5" t="n">
-        <v>626806892.6867139</v>
+        <v>679364786.8758227</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>532536086.54</v>
+        <v>648476714.88</v>
       </c>
       <c r="C2" t="n">
-        <v>35842533.70062618</v>
+        <v>-33841033.58859481</v>
       </c>
       <c r="D2" t="n">
-        <v>568378620.2406261</v>
+        <v>614635681.2914052</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K2" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M2" t="n">
         <v>0.1050151041880321</v>
@@ -1510,10 +1510,10 @@
         <v>-0.02747158338321065</v>
       </c>
       <c r="P2" t="n">
-        <v>8302609.009532409</v>
+        <v>17954508.19205512</v>
       </c>
       <c r="Q2" t="n">
-        <v>4151304.504766204</v>
+        <v>8977254.096027562</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I3" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J3" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K3" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L3" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="M3" t="n">
         <v>0.05822765833026367</v>
@@ -1571,10 +1571,10 @@
         <v>0.02514989940008316</v>
       </c>
       <c r="P3" t="n">
-        <v>1491003.562333822</v>
+        <v>1006136.017920862</v>
       </c>
       <c r="Q3" t="n">
-        <v>745501.7811669109</v>
+        <v>503068.0089604312</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I4" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J4" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K4" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L4" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="M4" t="n">
         <v>0.05839364669442126</v>
@@ -1632,10 +1632,10 @@
         <v>0.02530014515467949</v>
       </c>
       <c r="P4" t="n">
-        <v>32551525.14139548</v>
+        <v>48762790.79538272</v>
       </c>
       <c r="Q4" t="n">
-        <v>16275762.57069774</v>
+        <v>24381395.39769136</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I5" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J5" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K5" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="M5" t="n">
         <v>0.05851824187679444</v>
@@ -1693,10 +1693,10 @@
         <v>0.02544697899977066</v>
       </c>
       <c r="P5" t="n">
-        <v>-3346410.665183908</v>
+        <v>-4772236.049677371</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3346410.665183908</v>
+        <v>-4772236.049677371</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I6" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J6" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K6" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="M6" t="n">
         <v>0.05821004393128892</v>
@@ -1754,10 +1754,10 @@
         <v>0.02559354982454409</v>
       </c>
       <c r="P6" t="n">
-        <v>-630916.2524000645</v>
+        <v>-4198327.494922882</v>
       </c>
       <c r="Q6" t="n">
-        <v>-630916.2524000645</v>
+        <v>-4198327.494922882</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I7" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J7" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K7" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L7" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="M7" t="n">
         <v>0.05808035784574397</v>
@@ -1815,10 +1815,10 @@
         <v>0.02573959809769572</v>
       </c>
       <c r="P7" t="n">
-        <v>5994969.563372931</v>
+        <v>5210968.861140452</v>
       </c>
       <c r="Q7" t="n">
-        <v>2997484.781686465</v>
+        <v>2605484.430570226</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I8" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J8" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K8" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L8" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="M8" t="n">
         <v>0.0579990267461179</v>
@@ -1876,10 +1876,10 @@
         <v>0.02588744766971374</v>
       </c>
       <c r="P8" t="n">
-        <v>5968805.885164502</v>
+        <v>8822737.775425846</v>
       </c>
       <c r="Q8" t="n">
-        <v>2984402.942582251</v>
+        <v>4411368.887712923</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I9" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J9" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K9" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="M9" t="n">
         <v>0.05738520780446178</v>
@@ -1937,10 +1937,10 @@
         <v>0.02602676969992171</v>
       </c>
       <c r="P9" t="n">
-        <v>-1000596.240465143</v>
+        <v>-356898.545625418</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1000596.240465143</v>
+        <v>-356898.545625418</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I10" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J10" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K10" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="M10" t="n">
         <v>0.05695407285841891</v>
@@ -1998,10 +1998,10 @@
         <v>0.02616692125524978</v>
       </c>
       <c r="P10" t="n">
-        <v>-835429.9501804125</v>
+        <v>-287999.7415902748</v>
       </c>
       <c r="Q10" t="n">
-        <v>-835429.9501804125</v>
+        <v>-287999.7415902748</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I11" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J11" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K11" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L11" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="M11" t="n">
         <v>0.05664439372837885</v>
@@ -2059,10 +2059,10 @@
         <v>0.02630835803903212</v>
       </c>
       <c r="P11" t="n">
-        <v>348602.7366738985</v>
+        <v>-220537.8836426575</v>
       </c>
       <c r="Q11" t="n">
-        <v>174301.3683369493</v>
+        <v>-220537.8836426575</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I12" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J12" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K12" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L12" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="M12" t="n">
         <v>0.05642057743315654</v>
@@ -2120,10 +2120,10 @@
         <v>0.02645013495868191</v>
       </c>
       <c r="P12" t="n">
-        <v>-424732.1295655764</v>
+        <v>-147968.5362606447</v>
       </c>
       <c r="Q12" t="n">
-        <v>-424732.1295655764</v>
+        <v>-147968.5362606447</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I13" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J13" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K13" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L13" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="M13" t="n">
         <v>0.05625883751011833</v>
@@ -2181,10 +2181,10 @@
         <v>0.02659286987606641</v>
       </c>
       <c r="P13" t="n">
-        <v>-211825.5962844518</v>
+        <v>-74423.69825596042</v>
       </c>
       <c r="Q13" t="n">
-        <v>-211825.5962844518</v>
+        <v>-74423.69825596042</v>
       </c>
     </row>
     <row r="14">
@@ -2218,34 +2218,34 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I14" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J14" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K14" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L14" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08285710130558432</v>
+        <v>0.08286986959442011</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02673584606951374</v>
+        <v>0.02673619269116378</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K15" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M15" t="n">
         <v>0.1050151041880321</v>
@@ -2303,10 +2303,10 @@
         <v>-0.07747761902794248</v>
       </c>
       <c r="P15" t="n">
-        <v>23415700.82821106</v>
+        <v>50636780.78302096</v>
       </c>
       <c r="Q15" t="n">
-        <v>11707850.41410553</v>
+        <v>25318390.39151048</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I16" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J16" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K16" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L16" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="M16" t="n">
         <v>0.05822765833026367</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02509271293939896</v>
       </c>
       <c r="P16" t="n">
-        <v>-2959719.107489256</v>
+        <v>-2567960.680951935</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2959719.107489256</v>
+        <v>-2567960.680951935</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I17" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J17" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K17" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L17" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="M17" t="n">
         <v>0.05839364669442126</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02518665410778054</v>
       </c>
       <c r="P17" t="n">
-        <v>-33748794.17189663</v>
+        <v>-49971295.06467766</v>
       </c>
       <c r="Q17" t="n">
-        <v>-33748794.17189663</v>
+        <v>-49971295.06467766</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I18" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J18" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K18" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L18" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="M18" t="n">
         <v>0.05851824187679444</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02528484926412755</v>
       </c>
       <c r="P18" t="n">
-        <v>2111416.993355886</v>
+        <v>3452303.502496384</v>
       </c>
       <c r="Q18" t="n">
-        <v>1055708.496677943</v>
+        <v>1726151.751248192</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I19" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J19" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K19" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L19" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="M19" t="n">
         <v>0.05821004393128892</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02537722477452231</v>
       </c>
       <c r="P19" t="n">
-        <v>-457178.0484005649</v>
+        <v>3012407.668662956</v>
       </c>
       <c r="Q19" t="n">
-        <v>-457178.0484005649</v>
+        <v>1506203.834331478</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I20" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J20" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K20" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L20" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="M20" t="n">
         <v>0.05808035784574397</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02547134730704866</v>
       </c>
       <c r="P20" t="n">
-        <v>-6883421.99044755</v>
+        <v>-6167025.064877826</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6883421.99044755</v>
+        <v>-6167025.064877826</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I21" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J21" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K21" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L21" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="M21" t="n">
         <v>0.0579990267461179</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02556388968728518</v>
       </c>
       <c r="P21" t="n">
-        <v>-6303226.14261768</v>
+        <v>-9147051.64497916</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6303226.14261768</v>
+        <v>-9147051.64497916</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I22" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J22" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K22" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L22" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="M22" t="n">
         <v>0.05738520780446178</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02564879692438105</v>
       </c>
       <c r="P22" t="n">
-        <v>644081.1605327394</v>
+        <v>-11642.45639182811</v>
       </c>
       <c r="Q22" t="n">
-        <v>322040.5802663697</v>
+        <v>-11642.45639182811</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I23" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J23" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K23" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L23" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="M23" t="n">
         <v>0.05695407285841891</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02573394353653935</v>
       </c>
       <c r="P23" t="n">
-        <v>547110.895083079</v>
+        <v>-8417.080574735481</v>
       </c>
       <c r="Q23" t="n">
-        <v>273555.4475415395</v>
+        <v>-8417.080574735481</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I24" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J24" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K24" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L24" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="M24" t="n">
         <v>0.05664439372837885</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02581887365352179</v>
       </c>
       <c r="P24" t="n">
-        <v>-548667.7416344541</v>
+        <v>-3025.795465790799</v>
       </c>
       <c r="Q24" t="n">
-        <v>-548667.7416344541</v>
+        <v>-3025.795465790799</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I25" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J25" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K25" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L25" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="M25" t="n">
         <v>0.05642057743315654</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02590450870981425</v>
       </c>
       <c r="P25" t="n">
-        <v>277813.1688280281</v>
+        <v>-1876.046697247183</v>
       </c>
       <c r="Q25" t="n">
-        <v>138906.5844140141</v>
+        <v>-1876.046697247183</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I26" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J26" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K26" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L26" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="M26" t="n">
         <v>0.05625883751011833</v>
@@ -2974,10 +2974,10 @@
         <v>-0.025990262065432</v>
       </c>
       <c r="P26" t="n">
-        <v>137718.1561924235</v>
+        <v>-901.8560421748355</v>
       </c>
       <c r="Q26" t="n">
-        <v>68859.07809621173</v>
+        <v>-901.8560421748355</v>
       </c>
     </row>
     <row r="27">
@@ -3011,28 +3011,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I27" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J27" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K27" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L27" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="M27" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N27" t="n">
-        <v>0.030045538435584</v>
+        <v>0.03005768533093844</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.02607571680048659</v>
+        <v>-0.02607599157231788</v>
       </c>
       <c r="P27" t="n">
         <v>-0</v>
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K28" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M28" t="n">
         <v>0.1050151041880321</v>
@@ -3096,10 +3096,10 @@
         <v>-0.07502986587896165</v>
       </c>
       <c r="P28" t="n">
-        <v>22675927.76655857</v>
+        <v>49037011.18283243</v>
       </c>
       <c r="Q28" t="n">
-        <v>11337963.88327928</v>
+        <v>24518505.59141621</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I29" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J29" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K29" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L29" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="M29" t="n">
         <v>0.05822765833026367</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01988106139069767</v>
       </c>
       <c r="P29" t="n">
-        <v>-2344997.825357669</v>
+        <v>-2034605.985817574</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2344997.825357669</v>
+        <v>-2034605.985817574</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I30" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J30" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K30" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L30" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="M30" t="n">
         <v>0.05839364669442126</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01725628309459371</v>
       </c>
       <c r="P30" t="n">
-        <v>-23122513.36915437</v>
+        <v>-34237132.51269718</v>
       </c>
       <c r="Q30" t="n">
-        <v>-23122513.36915437</v>
+        <v>-34237132.51269718</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I31" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J31" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K31" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L31" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="M31" t="n">
         <v>0.05851824187679444</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01489062910622074</v>
       </c>
       <c r="P31" t="n">
-        <v>1243445.314156556</v>
+        <v>2033113.604150025</v>
       </c>
       <c r="Q31" t="n">
-        <v>621722.657078278</v>
+        <v>1016556.802075012</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I32" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J32" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K32" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L32" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="M32" t="n">
         <v>0.05821004393128892</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01266202848122933</v>
       </c>
       <c r="P32" t="n">
-        <v>-228110.1074398218</v>
+        <v>1503048.187364371</v>
       </c>
       <c r="Q32" t="n">
-        <v>-228110.1074398218</v>
+        <v>751524.0936821856</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I33" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J33" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K33" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L33" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="M33" t="n">
         <v>0.05808035784574397</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01061579379409725</v>
       </c>
       <c r="P33" t="n">
-        <v>-2868830.909000414</v>
+        <v>-2570255.339169097</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2868830.909000414</v>
+        <v>-2570255.339169097</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I34" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J34" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K34" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L34" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="M34" t="n">
         <v>0.0579990267461179</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008701770963537303</v>
       </c>
       <c r="P34" t="n">
-        <v>-2145574.515278884</v>
+        <v>-3113593.016552742</v>
       </c>
       <c r="Q34" t="n">
-        <v>-2145574.515278884</v>
+        <v>-3113593.016552742</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I35" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J35" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K35" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L35" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="M35" t="n">
         <v>0.05738520780446178</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006933843412663093</v>
       </c>
       <c r="P35" t="n">
-        <v>174119.5864019305</v>
+        <v>-3147.397899312691</v>
       </c>
       <c r="Q35" t="n">
-        <v>87059.79320096526</v>
+        <v>-3147.397899312691</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I36" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J36" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K36" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L36" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="M36" t="n">
         <v>0.05695407285841891</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005293779960104272</v>
       </c>
       <c r="P36" t="n">
-        <v>112547.2544941707</v>
+        <v>-1731.494141418705</v>
       </c>
       <c r="Q36" t="n">
-        <v>56273.62724708537</v>
+        <v>-1731.494141418705</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I37" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J37" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K37" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L37" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="M37" t="n">
         <v>0.05664439372837885</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003768699327115023</v>
       </c>
       <c r="P37" t="n">
-        <v>-80087.29491673374</v>
+        <v>-441.665794137306</v>
       </c>
       <c r="Q37" t="n">
-        <v>-80087.29491673374</v>
+        <v>-441.665794137306</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I38" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J38" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K38" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L38" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="M38" t="n">
         <v>0.05642057743315654</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002356874069323035</v>
       </c>
       <c r="P38" t="n">
-        <v>25276.32008242542</v>
+        <v>-170.688657450038</v>
       </c>
       <c r="Q38" t="n">
-        <v>12638.16004121271</v>
+        <v>-170.688657450038</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I39" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J39" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K39" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L39" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="M39" t="n">
         <v>0.05625883751011833</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001044890098674874</v>
       </c>
       <c r="P39" t="n">
-        <v>5536.702071373712</v>
+        <v>-36.25744313490175</v>
       </c>
       <c r="Q39" t="n">
-        <v>2768.351035686856</v>
+        <v>-36.25744313490175</v>
       </c>
     </row>
     <row r="40">
@@ -3804,34 +3804,34 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I40" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J40" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K40" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L40" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05629528248589444</v>
+        <v>0.05630773793266308</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0001740272498238493</v>
+        <v>0.0001740610294067579</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K41" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M41" t="n">
         <v>0.1050151041880321</v>
@@ -3889,10 +3889,10 @@
         <v>-0.02468474605999638</v>
       </c>
       <c r="P41" t="n">
-        <v>7460356.113328367</v>
+        <v>16133124.51527166</v>
       </c>
       <c r="Q41" t="n">
-        <v>3730178.056664183</v>
+        <v>8066562.257635831</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I42" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J42" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K42" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L42" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="M42" t="n">
         <v>0.05822765833026367</v>
@@ -3950,10 +3950,10 @@
         <v>0.02495849603761435</v>
       </c>
       <c r="P42" t="n">
-        <v>1479656.276575584</v>
+        <v>998478.8176328007</v>
       </c>
       <c r="Q42" t="n">
-        <v>739828.1382877921</v>
+        <v>499239.4088164003</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I43" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J43" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K43" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L43" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="M43" t="n">
         <v>0.05839364669442126</v>
@@ -4011,10 +4011,10 @@
         <v>0.02216014487646945</v>
       </c>
       <c r="P43" t="n">
-        <v>28511556.30425076</v>
+        <v>42710842.25011992</v>
       </c>
       <c r="Q43" t="n">
-        <v>14255778.15212538</v>
+        <v>21355421.12505996</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I44" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J44" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K44" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L44" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="M44" t="n">
         <v>0.05851824187679444</v>
@@ -4072,10 +4072,10 @@
         <v>0.01962016480210327</v>
       </c>
       <c r="P44" t="n">
-        <v>-2580154.160814768</v>
+        <v>-3679496.012868645</v>
       </c>
       <c r="Q44" t="n">
-        <v>-2580154.160814768</v>
+        <v>-3679496.012868645</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I45" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J45" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K45" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="M45" t="n">
         <v>0.05821004393128892</v>
@@ -4133,10 +4133,10 @@
         <v>0.01722340313955706</v>
       </c>
       <c r="P45" t="n">
-        <v>-424580.6086642931</v>
+        <v>-2825301.197085175</v>
       </c>
       <c r="Q45" t="n">
-        <v>-424580.6086642931</v>
+        <v>-2825301.197085175</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I46" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J46" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K46" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L46" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="M46" t="n">
         <v>0.05808035784574397</v>
@@ -4194,10 +4194,10 @@
         <v>0.01501522413586098</v>
       </c>
       <c r="P46" t="n">
-        <v>3497172.385522508</v>
+        <v>3039824.674730283</v>
       </c>
       <c r="Q46" t="n">
-        <v>1748586.192761254</v>
+        <v>1519912.337365141</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I47" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J47" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K47" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L47" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="M47" t="n">
         <v>0.0579990267461179</v>
@@ -4255,10 +4255,10 @@
         <v>0.01294941997535037</v>
       </c>
       <c r="P47" t="n">
-        <v>2985716.287850357</v>
+        <v>4413310.197437519</v>
       </c>
       <c r="Q47" t="n">
-        <v>1492858.143925178</v>
+        <v>2206655.09871876</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I48" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J48" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K48" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="M48" t="n">
         <v>0.05738520780446178</v>
@@ -4316,10 +4316,10 @@
         <v>0.01103784963125674</v>
       </c>
       <c r="P48" t="n">
-        <v>-424348.8904383044</v>
+        <v>-151359.2553223936</v>
       </c>
       <c r="Q48" t="n">
-        <v>-424348.8904383044</v>
+        <v>-151359.2553223936</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I49" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J49" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K49" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="M49" t="n">
         <v>0.05695407285841891</v>
@@ -4377,10 +4377,10 @@
         <v>0.009264716116377802</v>
       </c>
       <c r="P49" t="n">
-        <v>-295794.115327508</v>
+        <v>-101969.8046016301</v>
       </c>
       <c r="Q49" t="n">
-        <v>-295794.115327508</v>
+        <v>-101969.8046016301</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I50" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J50" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K50" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L50" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="M50" t="n">
         <v>0.05664439372837885</v>
@@ -4438,10 +4438,10 @@
         <v>0.007618063727031256</v>
       </c>
       <c r="P50" t="n">
-        <v>100944.2649160843</v>
+        <v>-63860.7566964745</v>
       </c>
       <c r="Q50" t="n">
-        <v>50472.13245804216</v>
+        <v>-63860.7566964745</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I51" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J51" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K51" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L51" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="M51" t="n">
         <v>0.05642057743315654</v>
@@ -4499,10 +4499,10 @@
         <v>0.006094907231449384</v>
       </c>
       <c r="P51" t="n">
-        <v>-97871.06689481827</v>
+        <v>-34096.40453974175</v>
       </c>
       <c r="Q51" t="n">
-        <v>-97871.06689481827</v>
+        <v>-34096.40453974175</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I52" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J52" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K52" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L52" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="M52" t="n">
         <v>0.05625883751011833</v>
@@ -4560,10 +4560,10 @@
         <v>0.004682431355023151</v>
       </c>
       <c r="P52" t="n">
-        <v>-37297.923032048</v>
+        <v>-13104.40956145641</v>
       </c>
       <c r="Q52" t="n">
-        <v>-37297.923032048</v>
+        <v>-13104.40956145641</v>
       </c>
     </row>
     <row r="53">
@@ -4597,34 +4597,34 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I53" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J53" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K53" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L53" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N53" t="n">
-        <v>0.05949445427920219</v>
+        <v>0.05950694809658197</v>
       </c>
       <c r="O53" t="n">
-        <v>0.003373199043131603</v>
+        <v>0.003373271193325644</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="54">
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M54" t="n">
         <v>0.1050151041880321</v>
@@ -4682,10 +4682,10 @@
         <v>-0.01765980557248192</v>
       </c>
       <c r="P54" t="n">
-        <v>5337240.988529545</v>
+        <v>11541858.34133637</v>
       </c>
       <c r="Q54" t="n">
-        <v>2668620.494264773</v>
+        <v>5770929.170668184</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I55" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J55" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K55" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L55" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="M55" t="n">
         <v>0.05822765833026367</v>
@@ -4743,10 +4743,10 @@
         <v>0.03235719235381929</v>
       </c>
       <c r="P55" t="n">
-        <v>1918285.568430772</v>
+        <v>1294467.868363062</v>
       </c>
       <c r="Q55" t="n">
-        <v>959142.7842153859</v>
+        <v>647233.9341815311</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I56" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J56" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K56" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L56" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="M56" t="n">
         <v>0.05839364669442126</v>
@@ -4804,10 +4804,10 @@
         <v>0.02992819194854235</v>
       </c>
       <c r="P56" t="n">
-        <v>38506035.70427726</v>
+        <v>57682758.4959884</v>
       </c>
       <c r="Q56" t="n">
-        <v>19253017.85213863</v>
+        <v>28841379.2479942</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I57" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J57" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K57" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L57" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="M57" t="n">
         <v>0.05851824187679444</v>
@@ -4865,10 +4865,10 @@
         <v>0.02772661859587089</v>
       </c>
       <c r="P57" t="n">
-        <v>-3646195.180164413</v>
+        <v>-5199751.561867619</v>
       </c>
       <c r="Q57" t="n">
-        <v>-3646195.180164413</v>
+        <v>-5199751.561867619</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I58" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J58" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K58" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="M58" t="n">
         <v>0.05821004393128892</v>
@@ -4926,10 +4926,10 @@
         <v>0.02564903369930005</v>
       </c>
       <c r="P58" t="n">
-        <v>-632284.0063290679</v>
+        <v>-4207428.9864514</v>
       </c>
       <c r="Q58" t="n">
-        <v>-632284.0063290679</v>
+        <v>-4207428.9864514</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I59" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J59" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K59" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L59" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="M59" t="n">
         <v>0.05808035784574397</v>
@@ -4987,10 +4987,10 @@
         <v>0.02373722363569292</v>
       </c>
       <c r="P59" t="n">
-        <v>5528599.657027863</v>
+        <v>4805589.145022292</v>
       </c>
       <c r="Q59" t="n">
-        <v>2764299.828513931</v>
+        <v>2402794.572511146</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I60" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J60" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K60" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L60" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="M60" t="n">
         <v>0.0579990267461179</v>
@@ -5048,10 +5048,10 @@
         <v>0.02195017150422629</v>
       </c>
       <c r="P60" t="n">
-        <v>5060997.689937379</v>
+        <v>7480869.0983461</v>
       </c>
       <c r="Q60" t="n">
-        <v>2530498.84496869</v>
+        <v>3740434.54917305</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I61" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J61" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K61" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="M61" t="n">
         <v>0.05738520780446178</v>
@@ -5109,10 +5109,10 @@
         <v>0.02029522229252897</v>
       </c>
       <c r="P61" t="n">
-        <v>-780247.5435654979</v>
+        <v>-278303.2778504948</v>
       </c>
       <c r="Q61" t="n">
-        <v>-780247.5435654979</v>
+        <v>-278303.2778504948</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I62" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J62" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K62" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="M62" t="n">
         <v>0.05695407285841891</v>
@@ -5170,10 +5170,10 @@
         <v>0.01876196760334525</v>
       </c>
       <c r="P62" t="n">
-        <v>-599012.3754816803</v>
+        <v>-206498.9521992186</v>
       </c>
       <c r="Q62" t="n">
-        <v>-599012.3754816803</v>
+        <v>-206498.9521992186</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I63" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J63" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K63" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L63" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="M63" t="n">
         <v>0.05664439372837885</v>
@@ -5231,10 +5231,10 @@
         <v>0.01733996627504109</v>
       </c>
       <c r="P63" t="n">
-        <v>229765.7530866877</v>
+        <v>-145357.5878456194</v>
       </c>
       <c r="Q63" t="n">
-        <v>114882.8765433439</v>
+        <v>-145357.5878456194</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I64" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J64" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K64" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L64" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="M64" t="n">
         <v>0.05642057743315654</v>
@@ -5292,10 +5292,10 @@
         <v>0.01602670204966161</v>
       </c>
       <c r="P64" t="n">
-        <v>-257354.2744526314</v>
+        <v>-89657.29842506933</v>
       </c>
       <c r="Q64" t="n">
-        <v>-257354.2744526314</v>
+        <v>-89657.29842506933</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I65" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J65" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K65" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L65" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="M65" t="n">
         <v>0.05625883751011833</v>
@@ -5353,10 +5353,10 @@
         <v>0.01481092208165177</v>
       </c>
       <c r="P65" t="n">
-        <v>-117976.4506835737</v>
+        <v>-41450.34368364463</v>
       </c>
       <c r="Q65" t="n">
-        <v>-117976.4506835737</v>
+        <v>-41450.34368364463</v>
       </c>
     </row>
     <row r="66">
@@ -5390,34 +5390,34 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I66" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J66" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K66" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L66" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="M66" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N66" t="n">
-        <v>0.06980717394620273</v>
+        <v>0.06981978911298969</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01368591871013214</v>
+        <v>0.01368611220973337</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="67">
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K67" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M67" t="n">
         <v>0.1050151041880321</v>
@@ -5475,10 +5475,10 @@
         <v>-0.08728823124945828</v>
       </c>
       <c r="P67" t="n">
-        <v>26380716.57860157</v>
+        <v>57048668.84360989</v>
       </c>
       <c r="Q67" t="n">
-        <v>13190358.28930079</v>
+        <v>28524334.42180495</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I68" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J68" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K68" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L68" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="M68" t="n">
         <v>0.05822765833026367</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03226565096877909</v>
       </c>
       <c r="P68" t="n">
-        <v>-3805776.757519552</v>
+        <v>-3302031.280286429</v>
       </c>
       <c r="Q68" t="n">
-        <v>-3805776.757519552</v>
+        <v>-3302031.280286429</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I69" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J69" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K69" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L69" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="M69" t="n">
         <v>0.05839364669442126</v>
@@ -5597,10 +5597,10 @@
         <v>-0.0297728173926024</v>
       </c>
       <c r="P69" t="n">
-        <v>-39894012.19394226</v>
+        <v>-59070420.24978229</v>
       </c>
       <c r="Q69" t="n">
-        <v>-39894012.19394226</v>
+        <v>-59070420.24978229</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I70" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J70" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K70" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L70" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="M70" t="n">
         <v>0.05851824187679444</v>
@@ -5658,10 +5658,10 @@
         <v>-0.02753489969717293</v>
       </c>
       <c r="P70" t="n">
-        <v>2299307.958044368</v>
+        <v>3759517.396067685</v>
       </c>
       <c r="Q70" t="n">
-        <v>1149653.979022184</v>
+        <v>1879758.698033842</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I71" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J71" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K71" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L71" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="M71" t="n">
         <v>0.05821004393128892</v>
@@ -5719,10 +5719,10 @@
         <v>-0.02543179398870032</v>
       </c>
       <c r="P71" t="n">
-        <v>-458161.1285861375</v>
+        <v>3018885.316267188</v>
       </c>
       <c r="Q71" t="n">
-        <v>-458161.1285861375</v>
+        <v>1509442.658133594</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I72" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J72" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K72" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L72" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="M72" t="n">
         <v>0.05808035784574397</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02350867571892774</v>
       </c>
       <c r="P72" t="n">
-        <v>-6353026.145781747</v>
+        <v>-5691830.536211658</v>
       </c>
       <c r="Q72" t="n">
-        <v>-6353026.145781747</v>
+        <v>-5691830.536211658</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I73" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J73" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K73" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L73" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="M73" t="n">
         <v>0.0579990267461179</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02171656780992581</v>
       </c>
       <c r="P73" t="n">
-        <v>-5354601.338916618</v>
+        <v>-7770435.944569229</v>
       </c>
       <c r="Q73" t="n">
-        <v>-5354601.338916618</v>
+        <v>-7770435.944569229</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I74" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J74" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K74" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L74" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="M74" t="n">
         <v>0.05738520780446178</v>
@@ -5902,10 +5902,10 @@
         <v>-0.02006419037968943</v>
       </c>
       <c r="P74" t="n">
-        <v>503843.0092062514</v>
+        <v>-9107.501697704229</v>
       </c>
       <c r="Q74" t="n">
-        <v>251921.5046031257</v>
+        <v>-9107.501697704229</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I75" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J75" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K75" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L75" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="M75" t="n">
         <v>0.05695407285841891</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01853809135614659</v>
       </c>
       <c r="P75" t="n">
-        <v>394125.0489102915</v>
+        <v>-6063.455001560041</v>
       </c>
       <c r="Q75" t="n">
-        <v>197062.5244551457</v>
+        <v>-6063.455001560041</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I76" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J76" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K76" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L76" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="M76" t="n">
         <v>0.05664439372837885</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01712553721773909</v>
       </c>
       <c r="P76" t="n">
-        <v>-363928.7273189013</v>
+        <v>-2006.99587278852</v>
       </c>
       <c r="Q76" t="n">
-        <v>-363928.7273189013</v>
+        <v>-2006.99587278852</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I77" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J77" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K77" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L77" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="M77" t="n">
         <v>0.05642057743315654</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01582455504283544</v>
       </c>
       <c r="P77" t="n">
-        <v>169710.6025437991</v>
+        <v>-1146.040040985999</v>
       </c>
       <c r="Q77" t="n">
-        <v>84855.30127189953</v>
+        <v>-1146.040040985999</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I78" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J78" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K78" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L78" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="M78" t="n">
         <v>0.05625883751011833</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01462200030522725</v>
       </c>
       <c r="P78" t="n">
-        <v>77479.59281100379</v>
+        <v>-507.3800060481344</v>
       </c>
       <c r="Q78" t="n">
-        <v>38739.7964055019</v>
+        <v>-507.3800060481344</v>
       </c>
     </row>
     <row r="79">
@@ -6183,28 +6183,28 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I79" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J79" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K79" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L79" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="M79" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N79" t="n">
-        <v>0.04261044181554507</v>
+        <v>0.0426227362277094</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.01351081342052551</v>
+        <v>-0.01351094067554692</v>
       </c>
       <c r="P79" t="n">
         <v>-0</v>
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-943055643.3100001</v>
+        <v>-1335362070.43</v>
       </c>
       <c r="K80" t="n">
-        <v>-640000000</v>
+        <v>-680000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-303055643.3100001</v>
+        <v>-655362070.4300001</v>
       </c>
       <c r="M80" t="n">
         <v>0.1050151041880321</v>
@@ -6268,10 +6268,10 @@
         <v>-0.06247613761654947</v>
       </c>
       <c r="P80" t="n">
-        <v>18881872.79998446</v>
+        <v>40832314.21345187</v>
       </c>
       <c r="Q80" t="n">
-        <v>9440936.399992229</v>
+        <v>20416157.10672593</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>548709791.53</v>
+        <v>133911619.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-484035602.7846395</v>
+        <v>-90269181.22613968</v>
       </c>
       <c r="J81" t="n">
-        <v>64674188.74536043</v>
+        <v>43642438.13386033</v>
       </c>
       <c r="K81" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L81" t="n">
-        <v>128674188.7453604</v>
+        <v>111642438.1338603</v>
       </c>
       <c r="M81" t="n">
         <v>0.05822765833026367</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01004192341464538</v>
       </c>
       <c r="P81" t="n">
-        <v>-1184458.31975399</v>
+        <v>-1027679.412434135</v>
       </c>
       <c r="Q81" t="n">
-        <v>-1184458.31975399</v>
+        <v>-1027679.412434135</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>1990072267.9</v>
+        <v>2364336920.83</v>
       </c>
       <c r="I82" t="n">
-        <v>-446135269.4812486</v>
+        <v>-51490547.94520548</v>
       </c>
       <c r="J82" t="n">
-        <v>1543936998.418751</v>
+        <v>2312846372.884794</v>
       </c>
       <c r="K82" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L82" t="n">
-        <v>1607936998.418751</v>
+        <v>2380846372.884794</v>
       </c>
       <c r="M82" t="n">
         <v>0.05839364669442126</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01008473632087492</v>
       </c>
       <c r="P82" t="n">
-        <v>-13513017.20802682</v>
+        <v>-20008506.57587884</v>
       </c>
       <c r="Q82" t="n">
-        <v>-13513017.20802682</v>
+        <v>-20008506.57587884</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>321318332.1300001</v>
+        <v>-157998693</v>
       </c>
       <c r="I83" t="n">
-        <v>-496658630.361554</v>
+        <v>-92049904.10958904</v>
       </c>
       <c r="J83" t="n">
-        <v>-175340298.2315539</v>
+        <v>-250048597.109589</v>
       </c>
       <c r="K83" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L83" t="n">
-        <v>-111340298.2315539</v>
+        <v>-182048597.109589</v>
       </c>
       <c r="M83" t="n">
         <v>0.05851824187679444</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01013182991584927</v>
       </c>
       <c r="P83" t="n">
-        <v>846060.7233465279</v>
+        <v>1383364.066749993</v>
       </c>
       <c r="Q83" t="n">
-        <v>423030.3616732639</v>
+        <v>691682.0333749967</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>82481230.3</v>
+        <v>-194599255.21</v>
       </c>
       <c r="I84" t="n">
-        <v>-119458296.2048057</v>
+        <v>-51458493.15068493</v>
       </c>
       <c r="J84" t="n">
-        <v>-36977065.90480575</v>
+        <v>-246057748.3606849</v>
       </c>
       <c r="K84" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L84" t="n">
-        <v>27022934.09519425</v>
+        <v>-178057748.3606849</v>
       </c>
       <c r="M84" t="n">
         <v>0.05821004393128892</v>
@@ -6512,10 +6512,10 @@
         <v>-0.01017508542911516</v>
       </c>
       <c r="P84" t="n">
-        <v>-183307.1086426336</v>
+        <v>1207835.200590573</v>
       </c>
       <c r="Q84" t="n">
-        <v>-183307.1086426336</v>
+        <v>603917.6002952865</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>518697858.84</v>
+        <v>398501812.66</v>
       </c>
       <c r="I85" t="n">
-        <v>-119426252.4590164</v>
+        <v>-51445520.54794521</v>
       </c>
       <c r="J85" t="n">
-        <v>399271606.3809837</v>
+        <v>347056292.1120548</v>
       </c>
       <c r="K85" t="n">
-        <v>-64000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L85" t="n">
-        <v>463271606.3809837</v>
+        <v>415056292.1120548</v>
       </c>
       <c r="M85" t="n">
         <v>0.05808035784574397</v>
@@ -6573,10 +6573,10 @@
         <v>-0.01021994033044944</v>
       </c>
       <c r="P85" t="n">
-        <v>-2761854.76816965</v>
+        <v>-2474412.81451163</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2761854.76816965</v>
+        <v>-2474412.81451163</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>669118580.01</v>
+        <v>772422393.1500001</v>
       </c>
       <c r="I86" t="n">
-        <v>-207983441.3653717</v>
+        <v>-90799555.08645856</v>
       </c>
       <c r="J86" t="n">
-        <v>461135138.6446283</v>
+        <v>681622838.0635415</v>
       </c>
       <c r="K86" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L86" t="n">
-        <v>493135138.6446283</v>
+        <v>715622838.0635415</v>
       </c>
       <c r="M86" t="n">
         <v>0.0579990267461179</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01026331977023442</v>
       </c>
       <c r="P86" t="n">
-        <v>-2530601.808924354</v>
+        <v>-3672333.010964407</v>
       </c>
       <c r="Q86" t="n">
-        <v>-2530601.808924354</v>
+        <v>-3672333.010964407</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-153952841.84</v>
+        <v>-35157733.02</v>
       </c>
       <c r="I87" t="n">
-        <v>61685111.16101505</v>
+        <v>2247136.761733663</v>
       </c>
       <c r="J87" t="n">
-        <v>-92267730.67898495</v>
+        <v>-32910596.25826634</v>
       </c>
       <c r="K87" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L87" t="n">
-        <v>-60267730.67898495</v>
+        <v>1089403.741733659</v>
       </c>
       <c r="M87" t="n">
         <v>0.05738520780446178</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01030407096516736</v>
       </c>
       <c r="P87" t="n">
-        <v>258751.2390941062</v>
+        <v>-4677.205610226033</v>
       </c>
       <c r="Q87" t="n">
-        <v>129375.6195470531</v>
+        <v>-4677.205610226033</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-105287618.79</v>
+        <v>-35284909.43000001</v>
       </c>
       <c r="I88" t="n">
-        <v>9506772.962048057</v>
+        <v>2266152.03233775</v>
       </c>
       <c r="J88" t="n">
-        <v>-95780845.82795194</v>
+        <v>-33018757.39766226</v>
       </c>
       <c r="K88" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L88" t="n">
-        <v>-63780845.82795194</v>
+        <v>981242.6023377441</v>
       </c>
       <c r="M88" t="n">
         <v>0.05695407285841891</v>
@@ -6756,10 +6756,10 @@
         <v>-0.01034491853166675</v>
       </c>
       <c r="P88" t="n">
-        <v>219935.8846569866</v>
+        <v>-3383.624926994878</v>
       </c>
       <c r="Q88" t="n">
-        <v>109967.9423284933</v>
+        <v>-3383.624926994878</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-8670744.480000019</v>
+        <v>-35779408.35</v>
       </c>
       <c r="I89" t="n">
-        <v>61673328.09342016</v>
+        <v>2248181.001571974</v>
       </c>
       <c r="J89" t="n">
-        <v>53002583.61342014</v>
+        <v>-33531227.34842803</v>
       </c>
       <c r="K89" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L89" t="n">
-        <v>85002583.61342014</v>
+        <v>468772.6515719742</v>
       </c>
       <c r="M89" t="n">
         <v>0.05664439372837885</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01038544122264451</v>
       </c>
       <c r="P89" t="n">
-        <v>-220697.3339725251</v>
+        <v>-1217.102704920988</v>
       </c>
       <c r="Q89" t="n">
-        <v>-220697.3339725251</v>
+        <v>-1217.102704920988</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>-105791543.79</v>
+        <v>-35814156.50999999</v>
       </c>
       <c r="I90" t="n">
-        <v>9444482.371434988</v>
+        <v>2248686.278913092</v>
       </c>
       <c r="J90" t="n">
-        <v>-96347061.41856501</v>
+        <v>-33565470.23108689</v>
       </c>
       <c r="K90" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L90" t="n">
-        <v>-64347061.41856501</v>
+        <v>434529.7689131051</v>
       </c>
       <c r="M90" t="n">
         <v>0.05642057743315654</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01042652380310684</v>
       </c>
       <c r="P90" t="n">
-        <v>111819.3612567743</v>
+        <v>-755.1058297885011</v>
       </c>
       <c r="Q90" t="n">
-        <v>55909.68062838717</v>
+        <v>-755.1058297885011</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>-105084497.29</v>
+        <v>-35845139.96</v>
       </c>
       <c r="I91" t="n">
-        <v>9498456.09701325</v>
+        <v>2261537.165955536</v>
       </c>
       <c r="J91" t="n">
-        <v>-95586041.19298677</v>
+        <v>-33583602.79404446</v>
       </c>
       <c r="K91" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L91" t="n">
-        <v>-63586041.19298677</v>
+        <v>416397.2059555352</v>
       </c>
       <c r="M91" t="n">
         <v>0.05625883751011833</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01046759094930644</v>
       </c>
       <c r="P91" t="n">
-        <v>55466.05577449461</v>
+        <v>-363.2229686980544</v>
       </c>
       <c r="Q91" t="n">
-        <v>27733.02788724731</v>
+        <v>-363.2229686980544</v>
       </c>
     </row>
     <row r="92">
@@ -6976,28 +6976,28 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>26344865.39000002</v>
+        <v>-36463708.53000001</v>
       </c>
       <c r="I92" t="n">
-        <v>9437731.866157647</v>
+        <v>4044566.584325174</v>
       </c>
       <c r="J92" t="n">
-        <v>35782597.25615767</v>
+        <v>-32419141.94567484</v>
       </c>
       <c r="K92" t="n">
-        <v>-32000000</v>
+        <v>-34000000</v>
       </c>
       <c r="L92" t="n">
-        <v>67782597.25615767</v>
+        <v>1580858.054325163</v>
       </c>
       <c r="M92" t="n">
-        <v>0.05612125523607059</v>
+        <v>0.05613367690325632</v>
       </c>
       <c r="N92" t="n">
-        <v>0.04561268519858142</v>
+        <v>0.04562501529258145</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.01050857003748917</v>
+        <v>-0.01050866161067487</v>
       </c>
       <c r="P92" t="n">
         <v>-0</v>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27261139.98000002</v>
+        <v>42626950.92000008</v>
       </c>
       <c r="D2" t="n">
-        <v>13630569.99000001</v>
+        <v>21313475.46000004</v>
       </c>
       <c r="E2" t="n">
-        <v>1.703821248750001</v>
+        <v>3.552245910000006</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8519106243750006</v>
+        <v>1.776122955000003</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-24923766.77999997</v>
+        <v>-42539253.75999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-24923766.77999997</v>
+        <v>-42539253.75999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.557735423749998</v>
+        <v>-3.544937813333333</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.557735423749998</v>
+        <v>-3.544937813333333</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8734244.889999986</v>
+        <v>32979980.26000011</v>
       </c>
       <c r="D4" t="n">
-        <v>4367122.444999993</v>
+        <v>16489990.13000005</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5458903056249991</v>
+        <v>2.748331688333343</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2729451528124995</v>
+        <v>1.374165844166671</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-3401887.860000014</v>
+        <v>-29938964.05999994</v>
       </c>
       <c r="D5" t="n">
-        <v>-3401887.860000014</v>
+        <v>-29938964.05999994</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2126179912500009</v>
+        <v>-2.494913671666662</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2126179912500009</v>
+        <v>-2.494913671666662</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7559235.600000024</v>
+        <v>-9643667.439999938</v>
       </c>
       <c r="D6" t="n">
-        <v>3779617.800000012</v>
+        <v>-9643667.439999938</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4724522250000014</v>
+        <v>-0.8036389533333281</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2362261125000007</v>
+        <v>-0.8036389533333281</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-5138259.879999995</v>
+        <v>9588788.840000033</v>
       </c>
       <c r="D7" t="n">
-        <v>-5138259.879999995</v>
+        <v>4794394.420000017</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3211412424999997</v>
+        <v>0.7990657366666696</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3211412424999997</v>
+        <v>0.3995328683333348</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-9224288.169999957</v>
+        <v>-16991582.26999998</v>
       </c>
       <c r="D8" t="n">
-        <v>-9224288.169999957</v>
+        <v>-16991582.26999998</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5765180106249973</v>
+        <v>-1.415965189166665</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5765180106249973</v>
+        <v>-1.415965189166665</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="F2" t="n">
         <v>-680000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="J2" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="K2" t="n">
-        <v>-13317035.44209644</v>
+        <v>-14264047.08087014</v>
       </c>
       <c r="L2" t="n">
-        <v>6535665.579082741</v>
+        <v>7482677.21785644</v>
       </c>
       <c r="M2" t="n">
-        <v>-13317035.44209644</v>
+        <v>-14264047.08087014</v>
       </c>
       <c r="N2" t="n">
-        <v>6535665.579082741</v>
+        <v>7482677.21785644</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="F3" t="n">
         <v>-68000000</v>
       </c>
       <c r="G3" t="n">
-        <v>201911619.36</v>
+        <v>493995266.0600001</v>
       </c>
       <c r="H3" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="I3" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="J3" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="K3" t="n">
-        <v>1227523.177466667</v>
+        <v>3904956.605550001</v>
       </c>
       <c r="L3" t="n">
-        <v>-1850856.5108</v>
+        <v>-4528289.938883334</v>
       </c>
       <c r="M3" t="n">
-        <v>400055.6828937197</v>
+        <v>3077489.110977054</v>
       </c>
       <c r="N3" t="n">
-        <v>-1023389.016227053</v>
+        <v>-3700822.444310387</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="F4" t="n">
         <v>-68000000</v>
       </c>
       <c r="G4" t="n">
-        <v>2432336920.83</v>
+        <v>2407361769.16</v>
       </c>
       <c r="H4" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="I4" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="J4" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="K4" t="n">
-        <v>19702807.67358333</v>
+        <v>19494681.40966667</v>
       </c>
       <c r="L4" t="n">
-        <v>-20269474.34025</v>
+        <v>-20061348.07633334</v>
       </c>
       <c r="M4" t="n">
-        <v>19273719.77403995</v>
+        <v>19065593.51012329</v>
       </c>
       <c r="N4" t="n">
-        <v>-19840386.44070662</v>
+        <v>-19632260.17678996</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="F5" t="n">
         <v>-68000000</v>
       </c>
       <c r="G5" t="n">
-        <v>-89998693</v>
+        <v>436810148.66</v>
       </c>
       <c r="H5" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="I5" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="J5" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="K5" t="n">
-        <v>-1184990.1975</v>
+        <v>2766076.11495</v>
       </c>
       <c r="L5" t="n">
-        <v>674990.1975</v>
+        <v>-3276076.114949999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1875364.478321918</v>
+        <v>2075701.834128082</v>
       </c>
       <c r="N5" t="n">
-        <v>1365364.478321918</v>
+        <v>-2585701.834128082</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="F6" t="n">
         <v>-68000000</v>
       </c>
       <c r="G6" t="n">
-        <v>-126599255.21</v>
+        <v>-112822610.01</v>
       </c>
       <c r="H6" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="I6" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="J6" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="K6" t="n">
-        <v>-1297328.368066667</v>
+        <v>-1205484.066733334</v>
       </c>
       <c r="L6" t="n">
-        <v>843995.0347333335</v>
+        <v>752150.7334</v>
       </c>
       <c r="M6" t="n">
-        <v>-1640384.989071233</v>
+        <v>-1548540.6877379</v>
       </c>
       <c r="N6" t="n">
-        <v>1187051.6557379</v>
+        <v>1095207.354404566</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="F7" t="n">
         <v>-68000000</v>
       </c>
       <c r="G7" t="n">
-        <v>466501812.66</v>
+        <v>464368601.78</v>
       </c>
       <c r="H7" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="I7" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="J7" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="K7" t="n">
-        <v>2324593.907183333</v>
+        <v>2312150.17705</v>
       </c>
       <c r="L7" t="n">
-        <v>-2721260.57385</v>
+        <v>-2708816.843716667</v>
       </c>
       <c r="M7" t="n">
-        <v>2024495.03732032</v>
+        <v>2012051.307186986</v>
       </c>
       <c r="N7" t="n">
-        <v>-2421161.703986986</v>
+        <v>-2408717.973853653</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="F8" t="n">
         <v>-34000000</v>
       </c>
       <c r="G8" t="n">
-        <v>806422393.1500001</v>
+        <v>304725457.28</v>
       </c>
       <c r="H8" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="I8" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="J8" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="K8" t="n">
-        <v>3862111.96575</v>
+        <v>1353627.2864</v>
       </c>
       <c r="L8" t="n">
-        <v>-4032111.96575</v>
+        <v>-1523627.2864</v>
       </c>
       <c r="M8" t="n">
-        <v>3408114.190317708</v>
+        <v>899629.510967707</v>
       </c>
       <c r="N8" t="n">
-        <v>-3578114.190317708</v>
+        <v>-1069629.510967707</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="F9" t="n">
         <v>-34000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-1157733.020000003</v>
+        <v>-1174959.200000003</v>
       </c>
       <c r="H9" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="I9" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="J9" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="K9" t="n">
-        <v>-146490.55425</v>
+        <v>-146562.33</v>
       </c>
       <c r="L9" t="n">
-        <v>4823.887583333347</v>
+        <v>4895.663333333346</v>
       </c>
       <c r="M9" t="n">
-        <v>-137127.4844094431</v>
+        <v>-137199.2601594431</v>
       </c>
       <c r="N9" t="n">
-        <v>-4539.182257223579</v>
+        <v>-4467.406507223581</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="F10" t="n">
         <v>-34000000</v>
       </c>
       <c r="G10" t="n">
-        <v>-1284909.430000007</v>
+        <v>-1427280.720000006</v>
       </c>
       <c r="H10" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="I10" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="J10" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="K10" t="n">
-        <v>-117616.3647666667</v>
+        <v>-118090.9357333334</v>
       </c>
       <c r="L10" t="n">
-        <v>4283.031433333358</v>
+        <v>4757.602400000022</v>
       </c>
       <c r="M10" t="n">
-        <v>-110062.5246588742</v>
+        <v>-110537.0956255409</v>
       </c>
       <c r="N10" t="n">
-        <v>-3270.808674459147</v>
+        <v>-2796.237707792484</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="F11" t="n">
         <v>-34000000</v>
       </c>
       <c r="G11" t="n">
-        <v>-1779408.350000001</v>
+        <v>-1839034.460000001</v>
       </c>
       <c r="H11" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="I11" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="J11" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="K11" t="n">
-        <v>-89448.520875</v>
+        <v>-89597.58615</v>
       </c>
       <c r="L11" t="n">
-        <v>4448.520875000004</v>
+        <v>4597.586150000002</v>
       </c>
       <c r="M11" t="n">
-        <v>-83828.06837107007</v>
+        <v>-83977.13364607007</v>
       </c>
       <c r="N11" t="n">
-        <v>-1171.931628929935</v>
+        <v>-1022.866353929937</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="F12" t="n">
         <v>-34000000</v>
       </c>
       <c r="G12" t="n">
-        <v>-1814156.50999999</v>
+        <v>-1777615.539999992</v>
       </c>
       <c r="H12" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="I12" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="J12" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="K12" t="n">
-        <v>-59690.26084999997</v>
+        <v>-59629.35923333331</v>
       </c>
       <c r="L12" t="n">
-        <v>3023.594183333317</v>
+        <v>2962.692566666652</v>
       </c>
       <c r="M12" t="n">
-        <v>-55942.45038514481</v>
+        <v>-55881.54876847815</v>
       </c>
       <c r="N12" t="n">
-        <v>-724.2162815218418</v>
+        <v>-785.1178981885001</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="F13" t="n">
         <v>-34000000</v>
       </c>
       <c r="G13" t="n">
-        <v>-1845139.960000001</v>
+        <v>-1715304.730000004</v>
       </c>
       <c r="H13" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="I13" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="J13" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="K13" t="n">
-        <v>-29870.94996666668</v>
+        <v>-29762.75394166668</v>
       </c>
       <c r="L13" t="n">
-        <v>1537.616633333335</v>
+        <v>1429.420608333337</v>
       </c>
       <c r="M13" t="n">
-        <v>-27986.33566170373</v>
+        <v>-27878.13963670373</v>
       </c>
       <c r="N13" t="n">
-        <v>-346.9976716296128</v>
+        <v>-455.1936966296101</v>
       </c>
     </row>
     <row r="14">
@@ -1087,22 +1087,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="F14" t="n">
         <v>-34000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-2463708.530000009</v>
+        <v>-2430105.95000001</v>
       </c>
       <c r="H14" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="I14" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="J14" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="K14" t="n">
         <v>-0</v>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10874566.06561189</v>
+        <v>13918317.48095486</v>
       </c>
       <c r="C2" t="n">
-        <v>-20800935.92862559</v>
+        <v>-23844687.34396856</v>
       </c>
       <c r="D2" t="n">
-        <v>7858652.911595874</v>
+        <v>10902404.32693885</v>
       </c>
       <c r="E2" t="n">
-        <v>-17785022.77460957</v>
+        <v>-20828774.18995254</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-62182847.84</v>
+        <v>-61943865.06</v>
       </c>
       <c r="D2" t="n">
-        <v>-92931037.85249965</v>
+        <v>-92901952.96765411</v>
       </c>
       <c r="E2" t="n">
-        <v>-155113885.6924997</v>
+        <v>-154845818.0276541</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95246548.3</v>
+        <v>71711293.28</v>
       </c>
       <c r="D3" t="n">
-        <v>-53934.26191780856</v>
+        <v>23407847.00712329</v>
       </c>
       <c r="E3" t="n">
-        <v>95192614.0380822</v>
+        <v>95119140.28712329</v>
       </c>
     </row>
     <row r="4">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>620220848.35</v>
+        <v>617112661.22</v>
       </c>
       <c r="D5" t="n">
-        <v>59143938.52582265</v>
+        <v>59554577.14974996</v>
       </c>
       <c r="E5" t="n">
-        <v>679364786.8758227</v>
+        <v>676667238.3697499</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>648476714.88</v>
+        <v>622072255.51</v>
       </c>
       <c r="C2" t="n">
-        <v>-33841033.58859481</v>
+        <v>-9939528.810780868</v>
       </c>
       <c r="D2" t="n">
-        <v>614635681.2914052</v>
+        <v>612132726.6992191</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K2" t="n">
         <v>-680000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M2" t="n">
         <v>0.1050151041880321</v>
@@ -1510,10 +1510,10 @@
         <v>-0.02747158338321065</v>
       </c>
       <c r="P2" t="n">
-        <v>17954508.19205512</v>
+        <v>20556099.11199939</v>
       </c>
       <c r="Q2" t="n">
-        <v>8977254.096027562</v>
+        <v>10278049.55599969</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I3" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J3" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K3" t="n">
         <v>-68000000</v>
       </c>
       <c r="L3" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="M3" t="n">
         <v>0.05822765833026367</v>
@@ -1571,10 +1571,10 @@
         <v>0.02514989940008316</v>
       </c>
       <c r="P3" t="n">
-        <v>1006136.017920862</v>
+        <v>7739854.154592426</v>
       </c>
       <c r="Q3" t="n">
-        <v>503068.0089604312</v>
+        <v>3869927.077296213</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I4" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J4" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K4" t="n">
         <v>-68000000</v>
       </c>
       <c r="L4" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="M4" t="n">
         <v>0.05839364669442126</v>
@@ -1632,10 +1632,10 @@
         <v>0.02530014515467949</v>
       </c>
       <c r="P4" t="n">
-        <v>48762790.79538272</v>
+        <v>48236228.32662344</v>
       </c>
       <c r="Q4" t="n">
-        <v>24381395.39769136</v>
+        <v>24118114.16331172</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I5" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J5" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K5" t="n">
         <v>-68000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="M5" t="n">
         <v>0.05851824187679444</v>
@@ -1693,10 +1693,10 @@
         <v>0.02544697899977066</v>
       </c>
       <c r="P5" t="n">
-        <v>-4772236.049677371</v>
+        <v>5282034.098284275</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4772236.049677371</v>
+        <v>2641017.049142138</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I6" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J6" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K6" t="n">
         <v>-68000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="M6" t="n">
         <v>0.05821004393128892</v>
@@ -1754,10 +1754,10 @@
         <v>0.02559354982454409</v>
       </c>
       <c r="P6" t="n">
-        <v>-4198327.494922882</v>
+        <v>-3963265.324695371</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4198327.494922882</v>
+        <v>-3963265.324695371</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I7" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J7" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K7" t="n">
         <v>-68000000</v>
       </c>
       <c r="L7" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="M7" t="n">
         <v>0.05808035784574397</v>
@@ -1815,10 +1815,10 @@
         <v>0.02573959809769572</v>
       </c>
       <c r="P7" t="n">
-        <v>5210968.861140452</v>
+        <v>5178939.199893634</v>
       </c>
       <c r="Q7" t="n">
-        <v>2605484.430570226</v>
+        <v>2589469.599946817</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I8" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J8" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K8" t="n">
         <v>-34000000</v>
       </c>
       <c r="L8" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="M8" t="n">
         <v>0.0579990267461179</v>
@@ -1876,10 +1876,10 @@
         <v>0.02588744766971374</v>
       </c>
       <c r="P8" t="n">
-        <v>8822737.775425846</v>
+        <v>2328911.188730668</v>
       </c>
       <c r="Q8" t="n">
-        <v>4411368.887712923</v>
+        <v>1164455.594365334</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I9" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J9" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K9" t="n">
         <v>-34000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="M9" t="n">
         <v>0.05738520780446178</v>
@@ -1937,10 +1937,10 @@
         <v>0.02602676969992171</v>
       </c>
       <c r="P9" t="n">
-        <v>-356898.545625418</v>
+        <v>-357085.3547169468</v>
       </c>
       <c r="Q9" t="n">
-        <v>-356898.545625418</v>
+        <v>-357085.3547169468</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I10" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J10" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K10" t="n">
         <v>-34000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="M10" t="n">
         <v>0.05695407285841891</v>
@@ -1998,10 +1998,10 @@
         <v>0.02616692125524978</v>
       </c>
       <c r="P10" t="n">
-        <v>-287999.7415902748</v>
+        <v>-289241.5477017542</v>
       </c>
       <c r="Q10" t="n">
-        <v>-287999.7415902748</v>
+        <v>-289241.5477017542</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I11" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J11" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K11" t="n">
         <v>-34000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="M11" t="n">
         <v>0.05664439372837885</v>
@@ -2059,10 +2059,10 @@
         <v>0.02630835803903212</v>
       </c>
       <c r="P11" t="n">
-        <v>-220537.8836426575</v>
+        <v>-220930.0499052462</v>
       </c>
       <c r="Q11" t="n">
-        <v>-220537.8836426575</v>
+        <v>-220930.0499052462</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I12" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J12" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K12" t="n">
         <v>-34000000</v>
       </c>
       <c r="L12" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="M12" t="n">
         <v>0.05642057743315654</v>
@@ -2120,10 +2120,10 @@
         <v>0.02645013495868191</v>
       </c>
       <c r="P12" t="n">
-        <v>-147968.5362606447</v>
+        <v>-147807.4506626412</v>
       </c>
       <c r="Q12" t="n">
-        <v>-147968.5362606447</v>
+        <v>-147807.4506626412</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I13" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J13" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K13" t="n">
         <v>-34000000</v>
       </c>
       <c r="L13" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="M13" t="n">
         <v>0.05625883751011833</v>
@@ -2181,10 +2181,10 @@
         <v>0.02659286987606641</v>
       </c>
       <c r="P13" t="n">
-        <v>-74423.69825596042</v>
+        <v>-74135.97397456717</v>
       </c>
       <c r="Q13" t="n">
-        <v>-74423.69825596042</v>
+        <v>-74135.97397456717</v>
       </c>
     </row>
     <row r="14">
@@ -2218,28 +2218,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I14" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J14" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K14" t="n">
         <v>-34000000</v>
       </c>
       <c r="L14" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08286986959442011</v>
+        <v>0.08285261130760024</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02673619269116378</v>
+        <v>0.02673572856165385</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K15" t="n">
         <v>-680000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M15" t="n">
         <v>0.1050151041880321</v>
@@ -2303,10 +2303,10 @@
         <v>-0.07747761902794248</v>
       </c>
       <c r="P15" t="n">
-        <v>50636780.78302096</v>
+        <v>57974001.47941458</v>
       </c>
       <c r="Q15" t="n">
-        <v>25318390.39151048</v>
+        <v>28987000.73970729</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I16" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J16" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K16" t="n">
         <v>-68000000</v>
       </c>
       <c r="L16" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="M16" t="n">
         <v>0.05822765833026367</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02509271293939896</v>
       </c>
       <c r="P16" t="n">
-        <v>-2567960.680951935</v>
+        <v>-9286367.523476534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2567960.680951935</v>
+        <v>-9286367.523476534</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I17" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J17" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K17" t="n">
         <v>-68000000</v>
       </c>
       <c r="L17" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="M17" t="n">
         <v>0.05839364669442126</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02518665410778054</v>
       </c>
       <c r="P17" t="n">
-        <v>-49971295.06467766</v>
+        <v>-49447094.6426763</v>
       </c>
       <c r="Q17" t="n">
-        <v>-49971295.06467766</v>
+        <v>-49447094.6426763</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I18" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J18" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K18" t="n">
         <v>-68000000</v>
       </c>
       <c r="L18" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="M18" t="n">
         <v>0.05851824187679444</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02528484926412755</v>
       </c>
       <c r="P18" t="n">
-        <v>3452303.502496384</v>
+        <v>-6537908.111790668</v>
       </c>
       <c r="Q18" t="n">
-        <v>1726151.751248192</v>
+        <v>-6537908.111790668</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I19" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J19" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K19" t="n">
         <v>-68000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="M19" t="n">
         <v>0.05821004393128892</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02537722477452231</v>
       </c>
       <c r="P19" t="n">
-        <v>3012407.668662956</v>
+        <v>2779332.32074346</v>
       </c>
       <c r="Q19" t="n">
-        <v>1506203.834331478</v>
+        <v>1389666.16037173</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I20" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J20" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K20" t="n">
         <v>-68000000</v>
       </c>
       <c r="L20" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="M20" t="n">
         <v>0.05808035784574397</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02547134730704866</v>
       </c>
       <c r="P20" t="n">
-        <v>-6167025.064877826</v>
+        <v>-6135329.207675694</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6167025.064877826</v>
+        <v>-6135329.207675694</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I21" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J21" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K21" t="n">
         <v>-34000000</v>
       </c>
       <c r="L21" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="M21" t="n">
         <v>0.0579990267461179</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02556388968728518</v>
       </c>
       <c r="P21" t="n">
-        <v>-9147051.64497916</v>
+        <v>-2734389.082464326</v>
       </c>
       <c r="Q21" t="n">
-        <v>-9147051.64497916</v>
+        <v>-2734389.082464326</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I22" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J22" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K22" t="n">
         <v>-34000000</v>
       </c>
       <c r="L22" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="M22" t="n">
         <v>0.05738520780446178</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02564879692438105</v>
       </c>
       <c r="P22" t="n">
-        <v>-11642.45639182811</v>
+        <v>-11458.3602282436</v>
       </c>
       <c r="Q22" t="n">
-        <v>-11642.45639182811</v>
+        <v>-11458.3602282436</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I23" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J23" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K23" t="n">
         <v>-34000000</v>
       </c>
       <c r="L23" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="M23" t="n">
         <v>0.05695407285841891</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02573394353653935</v>
       </c>
       <c r="P23" t="n">
-        <v>-8417.080574735481</v>
+        <v>-7195.8223287074</v>
       </c>
       <c r="Q23" t="n">
-        <v>-8417.080574735481</v>
+        <v>-7195.8223287074</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I24" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J24" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K24" t="n">
         <v>-34000000</v>
       </c>
       <c r="L24" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="M24" t="n">
         <v>0.05664439372837885</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02581887365352179</v>
       </c>
       <c r="P24" t="n">
-        <v>-3025.795465790799</v>
+        <v>-2640.925715655555</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3025.795465790799</v>
+        <v>-2640.925715655555</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I25" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J25" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K25" t="n">
         <v>-34000000</v>
       </c>
       <c r="L25" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="M25" t="n">
         <v>0.05642057743315654</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02590450870981425</v>
       </c>
       <c r="P25" t="n">
-        <v>-1876.046697247183</v>
+        <v>-2033.809343185506</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1876.046697247183</v>
+        <v>-2033.809343185506</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I26" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J26" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K26" t="n">
         <v>-34000000</v>
       </c>
       <c r="L26" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="M26" t="n">
         <v>0.05625883751011833</v>
@@ -2974,10 +2974,10 @@
         <v>-0.025990262065432</v>
       </c>
       <c r="P26" t="n">
-        <v>-901.8560421748355</v>
+        <v>-1183.060346593632</v>
       </c>
       <c r="Q26" t="n">
-        <v>-901.8560421748355</v>
+        <v>-1183.060346593632</v>
       </c>
     </row>
     <row r="27">
@@ -3011,28 +3011,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I27" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J27" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K27" t="n">
         <v>-34000000</v>
       </c>
       <c r="L27" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="M27" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N27" t="n">
-        <v>0.03005768533093844</v>
+        <v>0.030041267032894</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.02607599157231788</v>
+        <v>-0.02607561571305239</v>
       </c>
       <c r="P27" t="n">
         <v>-0</v>
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K28" t="n">
         <v>-680000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M28" t="n">
         <v>0.1050151041880321</v>
@@ -3096,10 +3096,10 @@
         <v>-0.07502986587896165</v>
       </c>
       <c r="P28" t="n">
-        <v>49037011.18283243</v>
+        <v>56142426.80713306</v>
       </c>
       <c r="Q28" t="n">
-        <v>24518505.59141621</v>
+        <v>28071213.40356653</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I29" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J29" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K29" t="n">
         <v>-68000000</v>
       </c>
       <c r="L29" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="M29" t="n">
         <v>0.05822765833026367</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01988106139069767</v>
       </c>
       <c r="P29" t="n">
-        <v>-2034605.985817574</v>
+        <v>-7357627.821140663</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2034605.985817574</v>
+        <v>-7357627.821140663</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I30" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J30" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K30" t="n">
         <v>-68000000</v>
       </c>
       <c r="L30" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="M30" t="n">
         <v>0.05839364669442126</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01725628309459371</v>
       </c>
       <c r="P30" t="n">
-        <v>-34237132.51269718</v>
+        <v>-33877983.93974058</v>
       </c>
       <c r="Q30" t="n">
-        <v>-34237132.51269718</v>
+        <v>-33877983.93974058</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I31" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J31" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K31" t="n">
         <v>-68000000</v>
       </c>
       <c r="L31" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="M31" t="n">
         <v>0.05851824187679444</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01489062910622074</v>
       </c>
       <c r="P31" t="n">
-        <v>2033113.604150025</v>
+        <v>-3850272.699127598</v>
       </c>
       <c r="Q31" t="n">
-        <v>1016556.802075012</v>
+        <v>-3850272.699127598</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I32" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J32" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K32" t="n">
         <v>-68000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="M32" t="n">
         <v>0.05821004393128892</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01266202848122933</v>
       </c>
       <c r="P32" t="n">
-        <v>1503048.187364371</v>
+        <v>1386754.671432244</v>
       </c>
       <c r="Q32" t="n">
-        <v>751524.0936821856</v>
+        <v>693377.3357161219</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I33" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J33" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K33" t="n">
         <v>-68000000</v>
       </c>
       <c r="L33" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="M33" t="n">
         <v>0.05808035784574397</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01061579379409725</v>
       </c>
       <c r="P33" t="n">
-        <v>-2570255.339169097</v>
+        <v>-2557045.331856611</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2570255.339169097</v>
+        <v>-2557045.331856611</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I34" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J34" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K34" t="n">
         <v>-34000000</v>
       </c>
       <c r="L34" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="M34" t="n">
         <v>0.0579990267461179</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008701770963537303</v>
       </c>
       <c r="P34" t="n">
-        <v>-3113593.016552742</v>
+        <v>-930767.1020281399</v>
       </c>
       <c r="Q34" t="n">
-        <v>-3113593.016552742</v>
+        <v>-930767.1020281399</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I35" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J35" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K35" t="n">
         <v>-34000000</v>
       </c>
       <c r="L35" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="M35" t="n">
         <v>0.05738520780446178</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006933843412663093</v>
       </c>
       <c r="P35" t="n">
-        <v>-3147.397899312691</v>
+        <v>-3097.629718180046</v>
       </c>
       <c r="Q35" t="n">
-        <v>-3147.397899312691</v>
+        <v>-3097.629718180046</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I36" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J36" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K36" t="n">
         <v>-34000000</v>
       </c>
       <c r="L36" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="M36" t="n">
         <v>0.05695407285841891</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005293779960104272</v>
       </c>
       <c r="P36" t="n">
-        <v>-1731.494141418705</v>
+        <v>-1480.266714119976</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1731.494141418705</v>
+        <v>-1480.266714119976</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I37" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J37" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K37" t="n">
         <v>-34000000</v>
       </c>
       <c r="L37" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="M37" t="n">
         <v>0.05664439372837885</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003768699327115023</v>
       </c>
       <c r="P37" t="n">
-        <v>-441.665794137306</v>
+        <v>-385.487573978435</v>
       </c>
       <c r="Q37" t="n">
-        <v>-441.665794137306</v>
+        <v>-385.487573978435</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I38" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J38" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K38" t="n">
         <v>-34000000</v>
       </c>
       <c r="L38" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="M38" t="n">
         <v>0.05642057743315654</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002356874069323035</v>
       </c>
       <c r="P38" t="n">
-        <v>-170.688657450038</v>
+        <v>-185.0424015601879</v>
       </c>
       <c r="Q38" t="n">
-        <v>-170.688657450038</v>
+        <v>-185.0424015601879</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I39" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J39" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K39" t="n">
         <v>-34000000</v>
       </c>
       <c r="L39" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="M39" t="n">
         <v>0.05625883751011833</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001044890098674874</v>
       </c>
       <c r="P39" t="n">
-        <v>-36.25744313490175</v>
+        <v>-47.56273865874938</v>
       </c>
       <c r="Q39" t="n">
-        <v>-36.25744313490175</v>
+        <v>-47.56273865874938</v>
       </c>
     </row>
     <row r="40">
@@ -3804,28 +3804,28 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I40" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J40" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K40" t="n">
         <v>-34000000</v>
       </c>
       <c r="L40" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05630773793266308</v>
+        <v>0.05629090260522096</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0001740610294067579</v>
+        <v>0.0001740198592745656</v>
       </c>
       <c r="P40" t="n">
         <v>-0</v>
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K41" t="n">
         <v>-680000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M41" t="n">
         <v>0.1050151041880321</v>
@@ -3889,10 +3889,10 @@
         <v>-0.02468474605999638</v>
       </c>
       <c r="P41" t="n">
-        <v>16133124.51527166</v>
+        <v>18470798.69717064</v>
       </c>
       <c r="Q41" t="n">
-        <v>8066562.257635831</v>
+        <v>9235399.348585319</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I42" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J42" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K42" t="n">
         <v>-68000000</v>
       </c>
       <c r="L42" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="M42" t="n">
         <v>0.05822765833026367</v>
@@ -3950,10 +3950,10 @@
         <v>0.02495849603761435</v>
       </c>
       <c r="P42" t="n">
-        <v>998478.8176328007</v>
+        <v>7680949.978212211</v>
       </c>
       <c r="Q42" t="n">
-        <v>499239.4088164003</v>
+        <v>3840474.989106106</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I43" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J43" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K43" t="n">
         <v>-68000000</v>
       </c>
       <c r="L43" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="M43" t="n">
         <v>0.05839364669442126</v>
@@ -4011,10 +4011,10 @@
         <v>0.02216014487646945</v>
       </c>
       <c r="P43" t="n">
-        <v>42710842.25011992</v>
+        <v>42249631.43402077</v>
       </c>
       <c r="Q43" t="n">
-        <v>21355421.12505996</v>
+        <v>21124815.71701039</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I44" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J44" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K44" t="n">
         <v>-68000000</v>
       </c>
       <c r="L44" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="M44" t="n">
         <v>0.05851824187679444</v>
@@ -4072,10 +4072,10 @@
         <v>0.01962016480210327</v>
       </c>
       <c r="P44" t="n">
-        <v>-3679496.012868645</v>
+        <v>4072561.206562099</v>
       </c>
       <c r="Q44" t="n">
-        <v>-3679496.012868645</v>
+        <v>2036280.60328105</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I45" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J45" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K45" t="n">
         <v>-68000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="M45" t="n">
         <v>0.05821004393128892</v>
@@ -4133,10 +4133,10 @@
         <v>0.01722340313955706</v>
       </c>
       <c r="P45" t="n">
-        <v>-2825301.197085175</v>
+        <v>-2667114.054291679</v>
       </c>
       <c r="Q45" t="n">
-        <v>-2825301.197085175</v>
+        <v>-2667114.054291679</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I46" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J46" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K46" t="n">
         <v>-68000000</v>
       </c>
       <c r="L46" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="M46" t="n">
         <v>0.05808035784574397</v>
@@ -4194,10 +4194,10 @@
         <v>0.01501522413586098</v>
       </c>
       <c r="P46" t="n">
-        <v>3039824.674730283</v>
+        <v>3021140.135026467</v>
       </c>
       <c r="Q46" t="n">
-        <v>1519912.337365141</v>
+        <v>1510570.067513233</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I47" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J47" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K47" t="n">
         <v>-34000000</v>
       </c>
       <c r="L47" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="M47" t="n">
         <v>0.0579990267461179</v>
@@ -4255,10 +4255,10 @@
         <v>0.01294941997535037</v>
       </c>
       <c r="P47" t="n">
-        <v>4413310.197437519</v>
+        <v>1164968.035973991</v>
       </c>
       <c r="Q47" t="n">
-        <v>2206655.09871876</v>
+        <v>582484.0179869956</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I48" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J48" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K48" t="n">
         <v>-34000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="M48" t="n">
         <v>0.05738520780446178</v>
@@ -4316,10 +4316,10 @@
         <v>0.01103784963125674</v>
       </c>
       <c r="P48" t="n">
-        <v>-151359.2553223936</v>
+        <v>-151438.4803159607</v>
       </c>
       <c r="Q48" t="n">
-        <v>-151359.2553223936</v>
+        <v>-151438.4803159607</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I49" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J49" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K49" t="n">
         <v>-34000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="M49" t="n">
         <v>0.05695407285841891</v>
@@ -4377,10 +4377,10 @@
         <v>0.009264716116377802</v>
       </c>
       <c r="P49" t="n">
-        <v>-101969.8046016301</v>
+        <v>-102409.4811299543</v>
       </c>
       <c r="Q49" t="n">
-        <v>-101969.8046016301</v>
+        <v>-102409.4811299543</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I50" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J50" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K50" t="n">
         <v>-34000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="M50" t="n">
         <v>0.05664439372837885</v>
@@ -4438,10 +4438,10 @@
         <v>0.007618063727031256</v>
       </c>
       <c r="P50" t="n">
-        <v>-63860.7566964745</v>
+        <v>-63974.31557291824</v>
       </c>
       <c r="Q50" t="n">
-        <v>-63860.7566964745</v>
+        <v>-63974.31557291824</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I51" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J51" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K51" t="n">
         <v>-34000000</v>
       </c>
       <c r="L51" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="M51" t="n">
         <v>0.05642057743315654</v>
@@ -4499,10 +4499,10 @@
         <v>0.006094907231449384</v>
       </c>
       <c r="P51" t="n">
-        <v>-34096.40453974175</v>
+        <v>-34059.28556935889</v>
       </c>
       <c r="Q51" t="n">
-        <v>-34096.40453974175</v>
+        <v>-34059.28556935889</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I52" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J52" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K52" t="n">
         <v>-34000000</v>
       </c>
       <c r="L52" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="M52" t="n">
         <v>0.05625883751011833</v>
@@ -4560,10 +4560,10 @@
         <v>0.004682431355023151</v>
       </c>
       <c r="P52" t="n">
-        <v>-13104.40956145641</v>
+        <v>-13053.74751546153</v>
       </c>
       <c r="Q52" t="n">
-        <v>-13104.40956145641</v>
+        <v>-13053.74751546153</v>
       </c>
     </row>
     <row r="53">
@@ -4597,28 +4597,28 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I53" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J53" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K53" t="n">
         <v>-34000000</v>
       </c>
       <c r="L53" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N53" t="n">
-        <v>0.05950694809658197</v>
+        <v>0.05949006088389019</v>
       </c>
       <c r="O53" t="n">
-        <v>0.003373271193325644</v>
+        <v>0.0033731781379438</v>
       </c>
       <c r="P53" t="n">
         <v>-0</v>
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K54" t="n">
         <v>-680000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M54" t="n">
         <v>0.1050151041880321</v>
@@ -4682,10 +4682,10 @@
         <v>-0.01765980557248192</v>
       </c>
       <c r="P54" t="n">
-        <v>11541858.34133637</v>
+        <v>13214262.48289847</v>
       </c>
       <c r="Q54" t="n">
-        <v>5770929.170668184</v>
+        <v>6607131.241449235</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I55" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J55" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K55" t="n">
         <v>-68000000</v>
       </c>
       <c r="L55" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="M55" t="n">
         <v>0.05822765833026367</v>
@@ -4743,10 +4743,10 @@
         <v>0.03235719235381929</v>
       </c>
       <c r="P55" t="n">
-        <v>1294467.868363062</v>
+        <v>9957890.713066883</v>
       </c>
       <c r="Q55" t="n">
-        <v>647233.9341815311</v>
+        <v>4978945.356533442</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I56" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J56" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K56" t="n">
         <v>-68000000</v>
       </c>
       <c r="L56" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="M56" t="n">
         <v>0.05839364669442126</v>
@@ -4804,10 +4804,10 @@
         <v>0.02992819194854235</v>
       </c>
       <c r="P56" t="n">
-        <v>57682758.4959884</v>
+        <v>57059874.21838531</v>
       </c>
       <c r="Q56" t="n">
-        <v>28841379.2479942</v>
+        <v>28529937.10919265</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I57" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J57" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K57" t="n">
         <v>-68000000</v>
       </c>
       <c r="L57" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="M57" t="n">
         <v>0.05851824187679444</v>
@@ -4865,10 +4865,10 @@
         <v>0.02772661859587089</v>
       </c>
       <c r="P57" t="n">
-        <v>-5199751.561867619</v>
+        <v>5755219.307361899</v>
       </c>
       <c r="Q57" t="n">
-        <v>-5199751.561867619</v>
+        <v>2877609.653680949</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I58" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J58" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K58" t="n">
         <v>-68000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="M58" t="n">
         <v>0.05821004393128892</v>
@@ -4926,10 +4926,10 @@
         <v>0.02564903369930005</v>
       </c>
       <c r="P58" t="n">
-        <v>-4207428.9864514</v>
+        <v>-3971857.228452666</v>
       </c>
       <c r="Q58" t="n">
-        <v>-4207428.9864514</v>
+        <v>-3971857.228452666</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I59" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J59" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K59" t="n">
         <v>-68000000</v>
       </c>
       <c r="L59" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="M59" t="n">
         <v>0.05808035784574397</v>
@@ -4987,10 +4987,10 @@
         <v>0.02373722363569292</v>
       </c>
       <c r="P59" t="n">
-        <v>4805589.145022292</v>
+        <v>4776051.184518578</v>
       </c>
       <c r="Q59" t="n">
-        <v>2402794.572511146</v>
+        <v>2388025.592259289</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I60" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J60" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K60" t="n">
         <v>-34000000</v>
       </c>
       <c r="L60" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="M60" t="n">
         <v>0.0579990267461179</v>
@@ -5048,10 +5048,10 @@
         <v>0.02195017150422629</v>
       </c>
       <c r="P60" t="n">
-        <v>7480869.0983461</v>
+        <v>1974702.20560044</v>
       </c>
       <c r="Q60" t="n">
-        <v>3740434.54917305</v>
+        <v>987351.1028002198</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I61" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J61" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K61" t="n">
         <v>-34000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="M61" t="n">
         <v>0.05738520780446178</v>
@@ -5109,10 +5109,10 @@
         <v>0.02029522229252897</v>
       </c>
       <c r="P61" t="n">
-        <v>-278303.2778504948</v>
+        <v>-278448.9483306411</v>
       </c>
       <c r="Q61" t="n">
-        <v>-278303.2778504948</v>
+        <v>-278448.9483306411</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I62" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J62" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K62" t="n">
         <v>-34000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="M62" t="n">
         <v>0.05695407285841891</v>
@@ -5170,10 +5170,10 @@
         <v>0.01876196760334525</v>
       </c>
       <c r="P62" t="n">
-        <v>-206498.9521992186</v>
+        <v>-207389.3407094274</v>
       </c>
       <c r="Q62" t="n">
-        <v>-206498.9521992186</v>
+        <v>-207389.3407094274</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I63" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J63" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K63" t="n">
         <v>-34000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="M63" t="n">
         <v>0.05664439372837885</v>
@@ -5231,10 +5231,10 @@
         <v>0.01733996627504109</v>
       </c>
       <c r="P63" t="n">
-        <v>-145357.5878456194</v>
+        <v>-145616.0665297474</v>
       </c>
       <c r="Q63" t="n">
-        <v>-145357.5878456194</v>
+        <v>-145616.0665297474</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I64" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J64" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K64" t="n">
         <v>-34000000</v>
       </c>
       <c r="L64" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="M64" t="n">
         <v>0.05642057743315654</v>
@@ -5292,10 +5292,10 @@
         <v>0.01602670204966161</v>
       </c>
       <c r="P64" t="n">
-        <v>-89657.29842506933</v>
+        <v>-89559.69321860342</v>
       </c>
       <c r="Q64" t="n">
-        <v>-89657.29842506933</v>
+        <v>-89559.69321860342</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I65" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J65" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K65" t="n">
         <v>-34000000</v>
       </c>
       <c r="L65" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="M65" t="n">
         <v>0.05625883751011833</v>
@@ -5353,10 +5353,10 @@
         <v>0.01481092208165177</v>
       </c>
       <c r="P65" t="n">
-        <v>-41450.34368364463</v>
+        <v>-41290.09539406269</v>
       </c>
       <c r="Q65" t="n">
-        <v>-41450.34368364463</v>
+        <v>-41290.09539406269</v>
       </c>
     </row>
     <row r="66">
@@ -5390,28 +5390,28 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I66" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J66" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K66" t="n">
         <v>-34000000</v>
       </c>
       <c r="L66" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="M66" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N66" t="n">
-        <v>0.06981978911298969</v>
+        <v>0.06980273792339808</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01368611220973337</v>
+        <v>0.01368585517745169</v>
       </c>
       <c r="P66" t="n">
         <v>-0</v>
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K67" t="n">
         <v>-680000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M67" t="n">
         <v>0.1050151041880321</v>
@@ -5475,10 +5475,10 @@
         <v>-0.08728823124945828</v>
       </c>
       <c r="P67" t="n">
-        <v>57048668.84360989</v>
+        <v>65314965.9357306</v>
       </c>
       <c r="Q67" t="n">
-        <v>28524334.42180495</v>
+        <v>32657482.9678653</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I68" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J68" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K68" t="n">
         <v>-68000000</v>
       </c>
       <c r="L68" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="M68" t="n">
         <v>0.05822765833026367</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03226565096877909</v>
       </c>
       <c r="P68" t="n">
-        <v>-3302031.280286429</v>
+        <v>-11940944.52855428</v>
       </c>
       <c r="Q68" t="n">
-        <v>-3302031.280286429</v>
+        <v>-11940944.52855428</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I69" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J69" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K69" t="n">
         <v>-68000000</v>
       </c>
       <c r="L69" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="M69" t="n">
         <v>0.05839364669442126</v>
@@ -5597,10 +5597,10 @@
         <v>-0.0297728173926024</v>
       </c>
       <c r="P69" t="n">
-        <v>-59070420.24978229</v>
+        <v>-58450769.72476275</v>
       </c>
       <c r="Q69" t="n">
-        <v>-59070420.24978229</v>
+        <v>-58450769.72476275</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I70" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J70" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K70" t="n">
         <v>-68000000</v>
       </c>
       <c r="L70" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="M70" t="n">
         <v>0.05851824187679444</v>
@@ -5658,10 +5658,10 @@
         <v>-0.02753489969717293</v>
       </c>
       <c r="P70" t="n">
-        <v>3759517.396067685</v>
+        <v>-7119704.064951282</v>
       </c>
       <c r="Q70" t="n">
-        <v>1879758.698033842</v>
+        <v>-7119704.064951282</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I71" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J71" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K71" t="n">
         <v>-68000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="M71" t="n">
         <v>0.05821004393128892</v>
@@ -5719,10 +5719,10 @@
         <v>-0.02543179398870032</v>
       </c>
       <c r="P71" t="n">
-        <v>3018885.316267188</v>
+        <v>2785308.781212643</v>
       </c>
       <c r="Q71" t="n">
-        <v>1509442.658133594</v>
+        <v>1392654.390606322</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I72" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J72" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K72" t="n">
         <v>-68000000</v>
       </c>
       <c r="L72" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="M72" t="n">
         <v>0.05808035784574397</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02350867571892774</v>
       </c>
       <c r="P72" t="n">
-        <v>-5691830.536211658</v>
+        <v>-5662576.97456782</v>
       </c>
       <c r="Q72" t="n">
-        <v>-5691830.536211658</v>
+        <v>-5662576.97456782</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I73" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J73" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K73" t="n">
         <v>-34000000</v>
       </c>
       <c r="L73" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="M73" t="n">
         <v>0.0579990267461179</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02171656780992581</v>
       </c>
       <c r="P73" t="n">
-        <v>-7770435.944569229</v>
+        <v>-2322868.180642799</v>
       </c>
       <c r="Q73" t="n">
-        <v>-7770435.944569229</v>
+        <v>-2322868.180642799</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I74" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J74" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K74" t="n">
         <v>-34000000</v>
       </c>
       <c r="L74" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="M74" t="n">
         <v>0.05738520780446178</v>
@@ -5902,10 +5902,10 @@
         <v>-0.02006419037968943</v>
       </c>
       <c r="P74" t="n">
-        <v>-9107.501697704229</v>
+        <v>-8963.489466439732</v>
       </c>
       <c r="Q74" t="n">
-        <v>-9107.501697704229</v>
+        <v>-8963.489466439732</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I75" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J75" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K75" t="n">
         <v>-34000000</v>
       </c>
       <c r="L75" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="M75" t="n">
         <v>0.05695407285841891</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01853809135614659</v>
       </c>
       <c r="P75" t="n">
-        <v>-6063.455001560041</v>
+        <v>-5183.6910080559</v>
       </c>
       <c r="Q75" t="n">
-        <v>-6063.455001560041</v>
+        <v>-5183.6910080559</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I76" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J76" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K76" t="n">
         <v>-34000000</v>
       </c>
       <c r="L76" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="M76" t="n">
         <v>0.05664439372837885</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01712553721773909</v>
       </c>
       <c r="P76" t="n">
-        <v>-2006.99587278852</v>
+        <v>-1751.713581300022</v>
       </c>
       <c r="Q76" t="n">
-        <v>-2006.99587278852</v>
+        <v>-1751.713581300022</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I77" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J77" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K77" t="n">
         <v>-34000000</v>
       </c>
       <c r="L77" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="M77" t="n">
         <v>0.05642057743315654</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01582455504283544</v>
       </c>
       <c r="P77" t="n">
-        <v>-1146.040040985999</v>
+        <v>-1242.414139499919</v>
       </c>
       <c r="Q77" t="n">
-        <v>-1146.040040985999</v>
+        <v>-1242.414139499919</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I78" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J78" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K78" t="n">
         <v>-34000000</v>
       </c>
       <c r="L78" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="M78" t="n">
         <v>0.05625883751011833</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01462200030522725</v>
       </c>
       <c r="P78" t="n">
-        <v>-507.3800060481344</v>
+        <v>-665.5842371055679</v>
       </c>
       <c r="Q78" t="n">
-        <v>-507.3800060481344</v>
+        <v>-665.5842371055679</v>
       </c>
     </row>
     <row r="79">
@@ -6183,28 +6183,28 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I79" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J79" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K79" t="n">
         <v>-34000000</v>
       </c>
       <c r="L79" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="M79" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N79" t="n">
-        <v>0.0426227362277094</v>
+        <v>0.04260611853542318</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.01351094067554692</v>
+        <v>-0.01351076421052322</v>
       </c>
       <c r="P79" t="n">
         <v>-0</v>
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1335362070.43</v>
+        <v>-1430323402.34</v>
       </c>
       <c r="K80" t="n">
         <v>-680000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-655362070.4300001</v>
+        <v>-750323402.3400002</v>
       </c>
       <c r="M80" t="n">
         <v>0.1050151041880321</v>
@@ -6268,10 +6268,10 @@
         <v>-0.06247613761654947</v>
       </c>
       <c r="P80" t="n">
-        <v>40832314.21345187</v>
+        <v>46748877.16030184</v>
       </c>
       <c r="Q80" t="n">
-        <v>20416157.10672593</v>
+        <v>23374438.58015092</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>133911619.36</v>
+        <v>425995266.0600001</v>
       </c>
       <c r="I81" t="n">
         <v>-90269181.22613968</v>
       </c>
       <c r="J81" t="n">
-        <v>43642438.13386033</v>
+        <v>335726084.8338604</v>
       </c>
       <c r="K81" t="n">
         <v>-68000000</v>
       </c>
       <c r="L81" t="n">
-        <v>111642438.1338603</v>
+        <v>403726084.8338604</v>
       </c>
       <c r="M81" t="n">
         <v>0.05822765833026367</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01004192341464538</v>
       </c>
       <c r="P81" t="n">
-        <v>-1027679.412434135</v>
+        <v>-3716337.555696563</v>
       </c>
       <c r="Q81" t="n">
-        <v>-1027679.412434135</v>
+        <v>-3716337.555696563</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>2364336920.83</v>
+        <v>2339361769.16</v>
       </c>
       <c r="I82" t="n">
         <v>-51490547.94520548</v>
       </c>
       <c r="J82" t="n">
-        <v>2312846372.884794</v>
+        <v>2287871221.214795</v>
       </c>
       <c r="K82" t="n">
         <v>-68000000</v>
       </c>
       <c r="L82" t="n">
-        <v>2380846372.884794</v>
+        <v>2355871221.214795</v>
       </c>
       <c r="M82" t="n">
         <v>0.05839364669442126</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01008473632087492</v>
       </c>
       <c r="P82" t="n">
-        <v>-20008506.57587884</v>
+        <v>-19798616.726574</v>
       </c>
       <c r="Q82" t="n">
-        <v>-20008506.57587884</v>
+        <v>-19798616.726574</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>-157998693</v>
+        <v>368810148.66</v>
       </c>
       <c r="I83" t="n">
         <v>-92049904.10958904</v>
       </c>
       <c r="J83" t="n">
-        <v>-250048597.109589</v>
+        <v>276760244.5504109</v>
       </c>
       <c r="K83" t="n">
         <v>-68000000</v>
       </c>
       <c r="L83" t="n">
-        <v>-182048597.109589</v>
+        <v>344760244.5504109</v>
       </c>
       <c r="M83" t="n">
         <v>0.05851824187679444</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01013182991584927</v>
       </c>
       <c r="P83" t="n">
-        <v>1383364.066749993</v>
+        <v>-2619789.119648522</v>
       </c>
       <c r="Q83" t="n">
-        <v>691682.0333749967</v>
+        <v>-2619789.119648522</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>-194599255.21</v>
+        <v>-180822610.01</v>
       </c>
       <c r="I84" t="n">
         <v>-51458493.15068493</v>
       </c>
       <c r="J84" t="n">
-        <v>-246057748.3606849</v>
+        <v>-232281103.1606849</v>
       </c>
       <c r="K84" t="n">
         <v>-68000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-178057748.3606849</v>
+        <v>-164281103.1606849</v>
       </c>
       <c r="M84" t="n">
         <v>0.05821004393128892</v>
@@ -6512,10 +6512,10 @@
         <v>-0.01017508542911516</v>
       </c>
       <c r="P84" t="n">
-        <v>1207835.200590573</v>
+        <v>1114382.839366167</v>
       </c>
       <c r="Q84" t="n">
-        <v>603917.6002952865</v>
+        <v>557191.4196830833</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>398501812.66</v>
+        <v>396368601.78</v>
       </c>
       <c r="I85" t="n">
         <v>-51445520.54794521</v>
       </c>
       <c r="J85" t="n">
-        <v>347056292.1120548</v>
+        <v>344923081.2320548</v>
       </c>
       <c r="K85" t="n">
         <v>-68000000</v>
       </c>
       <c r="L85" t="n">
-        <v>415056292.1120548</v>
+        <v>412923081.2320548</v>
       </c>
       <c r="M85" t="n">
         <v>0.05808035784574397</v>
@@ -6573,10 +6573,10 @@
         <v>-0.01021994033044944</v>
       </c>
       <c r="P85" t="n">
-        <v>-2474412.81451163</v>
+        <v>-2461695.396566541</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2474412.81451163</v>
+        <v>-2461695.396566541</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>772422393.1500001</v>
+        <v>270725457.28</v>
       </c>
       <c r="I86" t="n">
         <v>-90799555.08645856</v>
       </c>
       <c r="J86" t="n">
-        <v>681622838.0635415</v>
+        <v>179925902.1935414</v>
       </c>
       <c r="K86" t="n">
         <v>-34000000</v>
       </c>
       <c r="L86" t="n">
-        <v>715622838.0635415</v>
+        <v>213925902.1935414</v>
       </c>
       <c r="M86" t="n">
         <v>0.0579990267461179</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01026331977023442</v>
       </c>
       <c r="P86" t="n">
-        <v>-3672333.010964407</v>
+        <v>-1097794.970674105</v>
       </c>
       <c r="Q86" t="n">
-        <v>-3672333.010964407</v>
+        <v>-1097794.970674105</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-35157733.02</v>
+        <v>-35174959.2</v>
       </c>
       <c r="I87" t="n">
         <v>2247136.761733663</v>
       </c>
       <c r="J87" t="n">
-        <v>-32910596.25826634</v>
+        <v>-32927822.43826634</v>
       </c>
       <c r="K87" t="n">
         <v>-34000000</v>
       </c>
       <c r="L87" t="n">
-        <v>1089403.741733659</v>
+        <v>1072177.561733659</v>
       </c>
       <c r="M87" t="n">
         <v>0.05738520780446178</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01030407096516736</v>
       </c>
       <c r="P87" t="n">
-        <v>-4677.205610226033</v>
+        <v>-4603.247368068223</v>
       </c>
       <c r="Q87" t="n">
-        <v>-4677.205610226033</v>
+        <v>-4603.247368068223</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-35284909.43000001</v>
+        <v>-35427280.72000001</v>
       </c>
       <c r="I88" t="n">
         <v>2266152.03233775</v>
       </c>
       <c r="J88" t="n">
-        <v>-33018757.39766226</v>
+        <v>-33161128.68766226</v>
       </c>
       <c r="K88" t="n">
         <v>-34000000</v>
       </c>
       <c r="L88" t="n">
-        <v>981242.6023377441</v>
+        <v>838871.312337745</v>
       </c>
       <c r="M88" t="n">
         <v>0.05695407285841891</v>
@@ -6756,10 +6756,10 @@
         <v>-0.01034491853166675</v>
       </c>
       <c r="P88" t="n">
-        <v>-3383.624926994878</v>
+        <v>-2892.685128228781</v>
       </c>
       <c r="Q88" t="n">
-        <v>-3383.624926994878</v>
+        <v>-2892.685128228781</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-35779408.35</v>
+        <v>-35839034.46</v>
       </c>
       <c r="I89" t="n">
         <v>2248181.001571974</v>
       </c>
       <c r="J89" t="n">
-        <v>-33531227.34842803</v>
+        <v>-33590853.45842803</v>
       </c>
       <c r="K89" t="n">
         <v>-34000000</v>
       </c>
       <c r="L89" t="n">
-        <v>468772.6515719742</v>
+        <v>409146.5415719748</v>
       </c>
       <c r="M89" t="n">
         <v>0.05664439372837885</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01038544122264451</v>
       </c>
       <c r="P89" t="n">
-        <v>-1217.102704920988</v>
+        <v>-1062.291839736006</v>
       </c>
       <c r="Q89" t="n">
-        <v>-1217.102704920988</v>
+        <v>-1062.291839736006</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>-35814156.50999999</v>
+        <v>-35777615.53999999</v>
       </c>
       <c r="I90" t="n">
         <v>2248686.278913092</v>
       </c>
       <c r="J90" t="n">
-        <v>-33565470.23108689</v>
+        <v>-33528929.2610869</v>
       </c>
       <c r="K90" t="n">
         <v>-34000000</v>
       </c>
       <c r="L90" t="n">
-        <v>434529.7689131051</v>
+        <v>471070.7389131002</v>
       </c>
       <c r="M90" t="n">
         <v>0.05642057743315654</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01042652380310684</v>
       </c>
       <c r="P90" t="n">
-        <v>-755.1058297885011</v>
+        <v>-818.6050453707613</v>
       </c>
       <c r="Q90" t="n">
-        <v>-755.1058297885011</v>
+        <v>-818.6050453707613</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>-35845139.96</v>
+        <v>-35715304.73</v>
       </c>
       <c r="I91" t="n">
         <v>2261537.165955536</v>
       </c>
       <c r="J91" t="n">
-        <v>-33583602.79404446</v>
+        <v>-33453767.56404447</v>
       </c>
       <c r="K91" t="n">
         <v>-34000000</v>
       </c>
       <c r="L91" t="n">
-        <v>416397.2059555352</v>
+        <v>546232.4359555319</v>
       </c>
       <c r="M91" t="n">
         <v>0.05625883751011833</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01046759094930644</v>
       </c>
       <c r="P91" t="n">
-        <v>-363.2229686980544</v>
+        <v>-476.478141902145</v>
       </c>
       <c r="Q91" t="n">
-        <v>-363.2229686980544</v>
+        <v>-476.478141902145</v>
       </c>
     </row>
     <row r="92">
@@ -6976,28 +6976,28 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-36463708.53000001</v>
+        <v>-36430105.95000001</v>
       </c>
       <c r="I92" t="n">
         <v>4044566.584325174</v>
       </c>
       <c r="J92" t="n">
-        <v>-32419141.94567484</v>
+        <v>-32385539.36567484</v>
       </c>
       <c r="K92" t="n">
         <v>-34000000</v>
       </c>
       <c r="L92" t="n">
-        <v>1580858.054325163</v>
+        <v>1614460.634325162</v>
       </c>
       <c r="M92" t="n">
-        <v>0.05613367690325632</v>
+        <v>0.05611688274594639</v>
       </c>
       <c r="N92" t="n">
-        <v>0.04562501529258145</v>
+        <v>0.04560834936885638</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.01050866161067487</v>
+        <v>-0.01050853337709001</v>
       </c>
       <c r="P92" t="n">
         <v>-0</v>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42626950.92000008</v>
+        <v>61073262.91000009</v>
       </c>
       <c r="D2" t="n">
-        <v>21313475.46000004</v>
+        <v>30536631.45500004</v>
       </c>
       <c r="E2" t="n">
-        <v>3.552245910000006</v>
+        <v>5.08943857583334</v>
       </c>
       <c r="F2" t="n">
-        <v>1.776122955000003</v>
+        <v>2.54471928791667</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-42539253.75999999</v>
+        <v>-56816160.41999996</v>
       </c>
       <c r="D3" t="n">
-        <v>-42539253.75999999</v>
+        <v>-56816160.41999996</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.544937813333333</v>
+        <v>-4.734680034999996</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.544937813333333</v>
+        <v>-4.734680034999996</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32979980.26000011</v>
+        <v>26536310.04000008</v>
       </c>
       <c r="D4" t="n">
-        <v>16489990.13000005</v>
+        <v>13268155.02000004</v>
       </c>
       <c r="E4" t="n">
-        <v>2.748331688333343</v>
+        <v>2.211359170000007</v>
       </c>
       <c r="F4" t="n">
-        <v>1.374165844166671</v>
+        <v>1.105679585000003</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-29938964.05999994</v>
+        <v>-16482595.10000002</v>
       </c>
       <c r="D5" t="n">
-        <v>-29938964.05999994</v>
+        <v>-16482595.10000002</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.494913671666662</v>
+        <v>-1.373549591666669</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.494913671666662</v>
+        <v>-1.373549591666669</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-9643667.439999938</v>
+        <v>9155646.850000024</v>
       </c>
       <c r="D6" t="n">
-        <v>-9643667.439999938</v>
+        <v>4577823.425000012</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8036389533333281</v>
+        <v>0.7629705708333353</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8036389533333281</v>
+        <v>0.3814852854166677</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9588788.840000033</v>
+        <v>-5077214.439999938</v>
       </c>
       <c r="D7" t="n">
-        <v>4794394.420000017</v>
+        <v>-5077214.439999938</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7990657366666696</v>
+        <v>-0.4231012033333282</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3995328683333348</v>
+        <v>-0.4231012033333282</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-16991582.26999998</v>
+        <v>-21484632.63</v>
       </c>
       <c r="D8" t="n">
-        <v>-16991582.26999998</v>
+        <v>-21484632.63</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.415965189166665</v>
+        <v>-1.790386052499999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.415965189166665</v>
+        <v>-1.790386052499999</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="F2" t="n">
         <v>-680000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="J2" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="K2" t="n">
-        <v>-14264047.08087014</v>
+        <v>-12966182.99095671</v>
       </c>
       <c r="L2" t="n">
-        <v>7482677.21785644</v>
+        <v>6184813.127943014</v>
       </c>
       <c r="M2" t="n">
-        <v>-14264047.08087014</v>
+        <v>-12966182.99095671</v>
       </c>
       <c r="N2" t="n">
-        <v>7482677.21785644</v>
+        <v>6184813.127943014</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="F3" t="n">
         <v>-68000000</v>
       </c>
       <c r="G3" t="n">
-        <v>493995266.0600001</v>
+        <v>980642221.4799999</v>
       </c>
       <c r="H3" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="J3" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="K3" t="n">
-        <v>3904956.605550001</v>
+        <v>8365887.030233331</v>
       </c>
       <c r="L3" t="n">
-        <v>-4528289.938883334</v>
+        <v>-8989220.363566665</v>
       </c>
       <c r="M3" t="n">
-        <v>3077489.110977054</v>
+        <v>7545077.929776711</v>
       </c>
       <c r="N3" t="n">
-        <v>-3700822.444310387</v>
+        <v>-8168411.263110044</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="F4" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2407361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="H4" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="J4" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K4" t="n">
-        <v>19494681.40966667</v>
+        <v>7332372.162916669</v>
       </c>
       <c r="L4" t="n">
-        <v>-20061348.07633334</v>
+        <v>-7332372.162916669</v>
       </c>
       <c r="M4" t="n">
-        <v>19065593.51012329</v>
+        <v>6907915.884377854</v>
       </c>
       <c r="N4" t="n">
-        <v>-19632260.17678996</v>
+        <v>-6907915.884377854</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="F5" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="G5" t="n">
-        <v>436810148.66</v>
+        <v>1376710907.89</v>
       </c>
       <c r="H5" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="I5" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="J5" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="K5" t="n">
-        <v>2766076.11495</v>
+        <v>9305331.809175</v>
       </c>
       <c r="L5" t="n">
-        <v>-3276076.114949999</v>
+        <v>-10325331.809175</v>
       </c>
       <c r="M5" t="n">
-        <v>2075701.834128082</v>
+        <v>8620230.85027089</v>
       </c>
       <c r="N5" t="n">
-        <v>-2585701.834128082</v>
+        <v>-9640230.85027089</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="F6" t="n">
         <v>-68000000</v>
       </c>
       <c r="G6" t="n">
-        <v>-112822610.01</v>
+        <v>-133932841.91</v>
       </c>
       <c r="H6" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="I6" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="J6" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="K6" t="n">
-        <v>-1205484.066733334</v>
+        <v>-1346218.946066667</v>
       </c>
       <c r="L6" t="n">
-        <v>752150.7334</v>
+        <v>892885.6127333336</v>
       </c>
       <c r="M6" t="n">
-        <v>-1548540.6877379</v>
+        <v>-1686036.662961644</v>
       </c>
       <c r="N6" t="n">
-        <v>1095207.354404566</v>
+        <v>1232703.329628311</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="F7" t="n">
         <v>-68000000</v>
       </c>
       <c r="G7" t="n">
-        <v>464368601.78</v>
+        <v>-128825268.73</v>
       </c>
       <c r="H7" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="I7" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="J7" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="K7" t="n">
-        <v>2312150.17705</v>
+        <v>-1148147.400925</v>
       </c>
       <c r="L7" t="n">
-        <v>-2708816.843716667</v>
+        <v>751480.7342583333</v>
       </c>
       <c r="M7" t="n">
-        <v>2012051.307186986</v>
+        <v>-1445579.478550571</v>
       </c>
       <c r="N7" t="n">
-        <v>-2408717.973853653</v>
+        <v>1048912.811883904</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="F8" t="n">
         <v>-34000000</v>
       </c>
       <c r="G8" t="n">
-        <v>304725457.28</v>
+        <v>103886647.3499999</v>
       </c>
       <c r="H8" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="J8" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="K8" t="n">
-        <v>1353627.2864</v>
+        <v>349433.2367499995</v>
       </c>
       <c r="L8" t="n">
-        <v>-1523627.2864</v>
+        <v>-519433.2367499995</v>
       </c>
       <c r="M8" t="n">
-        <v>899629.510967707</v>
+        <v>-100409.8043458909</v>
       </c>
       <c r="N8" t="n">
-        <v>-1069629.510967707</v>
+        <v>-69590.19565410912</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="F9" t="n">
         <v>-34000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-1174959.200000003</v>
+        <v>-47388394.01999998</v>
       </c>
       <c r="H9" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="J9" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="K9" t="n">
-        <v>-146562.33</v>
+        <v>-339118.3084166666</v>
       </c>
       <c r="L9" t="n">
-        <v>4895.663333333346</v>
+        <v>197451.6417499999</v>
       </c>
       <c r="M9" t="n">
-        <v>-137199.2601594431</v>
+        <v>-329743.3084166666</v>
       </c>
       <c r="N9" t="n">
-        <v>-4467.406507223581</v>
+        <v>188076.6417499999</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="F10" t="n">
         <v>-34000000</v>
       </c>
       <c r="G10" t="n">
-        <v>-1427280.720000006</v>
+        <v>9699411.539999992</v>
       </c>
       <c r="H10" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="J10" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-118090.9357333334</v>
+        <v>-81001.96153333336</v>
       </c>
       <c r="L10" t="n">
-        <v>4757.602400000022</v>
+        <v>-32331.37179999998</v>
       </c>
       <c r="M10" t="n">
-        <v>-110537.0956255409</v>
+        <v>-73501.96153333336</v>
       </c>
       <c r="N10" t="n">
-        <v>-2796.237707792484</v>
+        <v>-39831.37179999998</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="F11" t="n">
         <v>-34000000</v>
       </c>
       <c r="G11" t="n">
-        <v>-1839034.460000001</v>
+        <v>8770207.989999995</v>
       </c>
       <c r="H11" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="J11" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-89597.58615</v>
+        <v>-63074.48002500001</v>
       </c>
       <c r="L11" t="n">
-        <v>4597.586150000002</v>
+        <v>-21925.51997499999</v>
       </c>
       <c r="M11" t="n">
-        <v>-83977.13364607007</v>
+        <v>-57449.48002500001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1022.866353929937</v>
+        <v>-27550.51997499999</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="F12" t="n">
         <v>-34000000</v>
       </c>
       <c r="G12" t="n">
-        <v>-1777615.539999992</v>
+        <v>77083900.58</v>
       </c>
       <c r="H12" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="J12" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="K12" t="n">
-        <v>-59629.35923333331</v>
+        <v>71806.50096666664</v>
       </c>
       <c r="L12" t="n">
-        <v>2962.692566666652</v>
+        <v>-128473.1676333333</v>
       </c>
       <c r="M12" t="n">
-        <v>-55881.54876847815</v>
+        <v>75556.50096666664</v>
       </c>
       <c r="N12" t="n">
-        <v>-785.1178981885001</v>
+        <v>-132223.1676333333</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="F13" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-1715304.730000004</v>
+        <v>32635075.89</v>
       </c>
       <c r="H13" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="J13" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K13" t="n">
-        <v>-29762.75394166668</v>
+        <v>27195.89657500001</v>
       </c>
       <c r="L13" t="n">
-        <v>1429.420608333337</v>
+        <v>-27195.89657500001</v>
       </c>
       <c r="M13" t="n">
-        <v>-27878.13963670373</v>
+        <v>29081.17054760276</v>
       </c>
       <c r="N13" t="n">
-        <v>-455.1936966296101</v>
+        <v>-29081.17054760276</v>
       </c>
     </row>
     <row r="14">
@@ -1087,22 +1087,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-2430105.95000001</v>
+        <v>-17065078.76000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="J14" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="K14" t="n">
         <v>-0</v>
@@ -1114,7 +1114,7 @@
         <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13918317.48095486</v>
+        <v>9508282.548693284</v>
       </c>
       <c r="C2" t="n">
-        <v>-23844687.34396856</v>
+        <v>-19349652.41170698</v>
       </c>
       <c r="D2" t="n">
-        <v>10902404.32693885</v>
+        <v>6518958.649149906</v>
       </c>
       <c r="E2" t="n">
-        <v>-20828774.18995254</v>
+        <v>-16360328.5121636</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-61943865.06</v>
+        <v>-42396461.29</v>
       </c>
       <c r="D2" t="n">
-        <v>-92901952.96765411</v>
+        <v>-62912712.16636198</v>
       </c>
       <c r="E2" t="n">
-        <v>-154845818.0276541</v>
+        <v>-105309173.456362</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>71711293.28</v>
+        <v>62386746.03</v>
       </c>
       <c r="D3" t="n">
-        <v>23407847.00712329</v>
+        <v>5983713.538328768</v>
       </c>
       <c r="E3" t="n">
-        <v>95119140.28712329</v>
+        <v>68370459.56832877</v>
       </c>
     </row>
     <row r="4">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-4807833.930000001</v>
+        <v>2578680.23</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-4807833.930000001</v>
+        <v>2578680.23</v>
       </c>
     </row>
     <row r="5">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>617112661.22</v>
+        <v>516914934.53</v>
       </c>
       <c r="D5" t="n">
-        <v>59554577.14974996</v>
+        <v>48159367.84394944</v>
       </c>
       <c r="E5" t="n">
-        <v>676667238.3697499</v>
+        <v>565074302.3739494</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>622072255.51</v>
+        <v>539483899.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-9939528.810780868</v>
+        <v>-8769630.784083776</v>
       </c>
       <c r="D2" t="n">
-        <v>612132726.6992191</v>
+        <v>530714268.7159162</v>
       </c>
     </row>
   </sheetData>
@@ -1486,34 +1486,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K2" t="n">
         <v>-680000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-750323402.3400002</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07754352080482141</v>
+        <v>0.05933231753539991</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.02747158338321065</v>
+        <v>0.02500481880599148</v>
       </c>
       <c r="P2" t="n">
-        <v>20556099.11199939</v>
+        <v>-32421705.62942012</v>
       </c>
       <c r="Q2" t="n">
-        <v>10278049.55599969</v>
+        <v>-32421705.62942012</v>
       </c>
     </row>
     <row r="3">
@@ -1547,34 +1547,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I3" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J3" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K3" t="n">
         <v>-68000000</v>
       </c>
       <c r="L3" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08337755773034683</v>
+        <v>0.06293247021270165</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02514989940008316</v>
+        <v>0.0251058158502353</v>
       </c>
       <c r="P3" t="n">
-        <v>7739854.154592426</v>
+        <v>18942533.70806487</v>
       </c>
       <c r="Q3" t="n">
-        <v>3869927.077296213</v>
+        <v>9471266.854032435</v>
       </c>
     </row>
     <row r="4">
@@ -1608,34 +1608,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I4" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J4" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K4" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08369379184910075</v>
+        <v>0.06351793262205963</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02530014515467949</v>
+        <v>0.02521323244800655</v>
       </c>
       <c r="P4" t="n">
-        <v>48236228.32662344</v>
+        <v>17417088.89240956</v>
       </c>
       <c r="Q4" t="n">
-        <v>24118114.16331172</v>
+        <v>8708544.446204778</v>
       </c>
     </row>
     <row r="5">
@@ -1669,34 +1669,34 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J5" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K5" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L5" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08396522087656511</v>
+        <v>0.06384244431183639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02544697899977066</v>
+        <v>0.02532026333962101</v>
       </c>
       <c r="P5" t="n">
-        <v>5282034.098284275</v>
+        <v>21826651.5177184</v>
       </c>
       <c r="Q5" t="n">
-        <v>2641017.049142138</v>
+        <v>10913325.7588592</v>
       </c>
     </row>
     <row r="6">
@@ -1730,34 +1730,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J6" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K6" t="n">
         <v>-68000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08380359375583302</v>
+        <v>0.06416383416053839</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02559354982454409</v>
+        <v>0.02542872476626745</v>
       </c>
       <c r="P6" t="n">
-        <v>-3963265.324695371</v>
+        <v>-4287376.224828769</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3963265.324695371</v>
+        <v>-4287376.224828769</v>
       </c>
     </row>
     <row r="7">
@@ -1791,34 +1791,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I7" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J7" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K7" t="n">
         <v>-68000000</v>
       </c>
       <c r="L7" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08381995594343969</v>
+        <v>0.064427603552231</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02573959809769572</v>
+        <v>0.02553821260711615</v>
       </c>
       <c r="P7" t="n">
-        <v>5178939.199893634</v>
+        <v>-3691751.606370857</v>
       </c>
       <c r="Q7" t="n">
-        <v>2589469.599946817</v>
+        <v>-3691751.606370857</v>
       </c>
     </row>
     <row r="8">
@@ -1852,34 +1852,34 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I8" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J8" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K8" t="n">
         <v>-34000000</v>
       </c>
       <c r="L8" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08388647441583164</v>
+        <v>0.06466175178617339</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02588744766971374</v>
+        <v>0.02564775160277089</v>
       </c>
       <c r="P8" t="n">
-        <v>2328911.188730668</v>
+        <v>-257528.5720346234</v>
       </c>
       <c r="Q8" t="n">
-        <v>1164455.594365334</v>
+        <v>-257528.5720346234</v>
       </c>
     </row>
     <row r="9">
@@ -1913,34 +1913,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I9" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J9" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K9" t="n">
         <v>-34000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08341197750438349</v>
+        <v>0.06484684505880736</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02602676969992171</v>
+        <v>0.02575828679253624</v>
       </c>
       <c r="P9" t="n">
-        <v>-357085.3547169468</v>
+        <v>-849362.2706116225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-357085.3547169468</v>
+        <v>-849362.2706116225</v>
       </c>
     </row>
     <row r="10">
@@ -1974,34 +1974,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J10" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K10" t="n">
         <v>-34000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08312099411366869</v>
+        <v>0.06502656643195814</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02616692125524978</v>
+        <v>0.02586772256944581</v>
       </c>
       <c r="P10" t="n">
-        <v>-289241.5477017542</v>
+        <v>-190132.8349254345</v>
       </c>
       <c r="Q10" t="n">
-        <v>-289241.5477017542</v>
+        <v>-190132.8349254345</v>
       </c>
     </row>
     <row r="11">
@@ -2035,34 +2035,34 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J11" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K11" t="n">
         <v>-34000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08295275176741097</v>
+        <v>0.06520531674627043</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02630835803903212</v>
+        <v>0.02597850453979926</v>
       </c>
       <c r="P11" t="n">
-        <v>-220930.0499052462</v>
+        <v>-149245.157763857</v>
       </c>
       <c r="Q11" t="n">
-        <v>-220930.0499052462</v>
+        <v>-149245.157763857</v>
       </c>
     </row>
     <row r="12">
@@ -2096,34 +2096,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I12" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J12" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K12" t="n">
         <v>-34000000</v>
       </c>
       <c r="L12" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08287071239183845</v>
+        <v>0.06538378070787436</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02645013495868191</v>
+        <v>0.02608953222428303</v>
       </c>
       <c r="P12" t="n">
-        <v>-147807.4506626412</v>
+        <v>197123.3766723921</v>
       </c>
       <c r="Q12" t="n">
-        <v>-147807.4506626412</v>
+        <v>98561.68833619606</v>
       </c>
     </row>
     <row r="13">
@@ -2157,34 +2157,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I13" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J13" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K13" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08285170738618473</v>
+        <v>0.06556220011090294</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02659286987606641</v>
+        <v>0.02620112954634799</v>
       </c>
       <c r="P13" t="n">
-        <v>-74135.97397456717</v>
+        <v>76195.95168771796</v>
       </c>
       <c r="Q13" t="n">
-        <v>-74135.97397456717</v>
+        <v>38097.97584385898</v>
       </c>
     </row>
     <row r="14">
@@ -2218,28 +2218,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I14" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J14" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K14" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L14" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08285261130760024</v>
+        <v>0.06574199337207398</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02673572856165385</v>
+        <v>0.02631330603469872</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -2279,34 +2279,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K15" t="n">
         <v>-680000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02753748516008958</v>
+        <v>0.00932749994446147</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.07747761902794248</v>
+        <v>-0.02499999878494696</v>
       </c>
       <c r="P15" t="n">
-        <v>57974001.47941458</v>
+        <v>15462032.06836994</v>
       </c>
       <c r="Q15" t="n">
-        <v>28987000.73970729</v>
+        <v>7731016.034184968</v>
       </c>
     </row>
     <row r="16">
@@ -2340,34 +2340,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I16" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J16" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K16" t="n">
         <v>-68000000</v>
       </c>
       <c r="L16" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0331349453908647</v>
+        <v>0.01277490186754093</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.02509271293939896</v>
+        <v>-0.02505175249492542</v>
       </c>
       <c r="P16" t="n">
-        <v>-9286367.523476534</v>
+        <v>-20463301.72401939</v>
       </c>
       <c r="Q16" t="n">
-        <v>-9286367.523476534</v>
+        <v>-20463301.72401939</v>
       </c>
     </row>
     <row r="17">
@@ -2401,34 +2401,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I17" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J17" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K17" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N17" t="n">
-        <v>0.03320699258664073</v>
+        <v>0.01319862907416969</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.02518665410778054</v>
+        <v>-0.02510607109988339</v>
       </c>
       <c r="P17" t="n">
-        <v>-49447094.6426763</v>
+        <v>-17343062.73452042</v>
       </c>
       <c r="Q17" t="n">
-        <v>-49447094.6426763</v>
+        <v>-17343062.73452042</v>
       </c>
     </row>
     <row r="18">
@@ -2462,34 +2462,34 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J18" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K18" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L18" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="M18" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N18" t="n">
-        <v>0.03323339261266689</v>
+        <v>0.01336057997554096</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.02528484926412755</v>
+        <v>-0.02516160099667442</v>
       </c>
       <c r="P18" t="n">
-        <v>-6537908.111790668</v>
+        <v>-24256364.21703475</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6537908.111790668</v>
+        <v>-24256364.21703475</v>
       </c>
     </row>
     <row r="19">
@@ -2523,34 +2523,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I19" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J19" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K19" t="n">
         <v>-68000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03283281915676661</v>
+        <v>0.01351767801483916</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.02537722477452231</v>
+        <v>-0.02521743137943178</v>
       </c>
       <c r="P19" t="n">
-        <v>2779332.32074346</v>
+        <v>3108561.1626099</v>
       </c>
       <c r="Q19" t="n">
-        <v>1389666.16037173</v>
+        <v>1554280.58130495</v>
       </c>
     </row>
     <row r="20">
@@ -2584,34 +2584,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I20" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J20" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K20" t="n">
         <v>-68000000</v>
       </c>
       <c r="L20" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N20" t="n">
-        <v>0.03260901053869531</v>
+        <v>0.01361649928042201</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.02547134730704866</v>
+        <v>-0.02527289166469284</v>
       </c>
       <c r="P20" t="n">
-        <v>-6135329.207675694</v>
+        <v>2650905.986045025</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6135329.207675694</v>
+        <v>1325452.993022513</v>
       </c>
     </row>
     <row r="21">
@@ -2645,34 +2645,34 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I21" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J21" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K21" t="n">
         <v>-34000000</v>
       </c>
       <c r="L21" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N21" t="n">
-        <v>0.03243513705883272</v>
+        <v>0.01368509298833365</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.02556388968728518</v>
+        <v>-0.02532890719506886</v>
       </c>
       <c r="P21" t="n">
-        <v>-2734389.082464326</v>
+        <v>-176264.3607409614</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2734389.082464326</v>
+        <v>-176264.3607409614</v>
       </c>
     </row>
     <row r="22">
@@ -2706,34 +2706,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I22" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J22" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K22" t="n">
         <v>-34000000</v>
       </c>
       <c r="L22" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N22" t="n">
-        <v>0.03173641088008074</v>
+        <v>0.01370492491423558</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.02564879692438105</v>
+        <v>-0.02538363335203554</v>
       </c>
       <c r="P22" t="n">
-        <v>-11458.3602282436</v>
+        <v>477406.8516264138</v>
       </c>
       <c r="Q22" t="n">
-        <v>-11458.3602282436</v>
+        <v>238703.4258132069</v>
       </c>
     </row>
     <row r="23">
@@ -2767,34 +2767,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J23" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K23" t="n">
         <v>-34000000</v>
       </c>
       <c r="L23" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N23" t="n">
-        <v>0.03122012932187956</v>
+        <v>0.01371890926742469</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.02573394353653935</v>
+        <v>-0.02543993459508764</v>
       </c>
       <c r="P23" t="n">
-        <v>-7195.8223287074</v>
+        <v>-101330.7493424618</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7195.8223287074</v>
+        <v>-101330.7493424618</v>
       </c>
     </row>
     <row r="24">
@@ -2828,34 +2828,34 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I24" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J24" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K24" t="n">
         <v>-34000000</v>
       </c>
       <c r="L24" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N24" t="n">
-        <v>0.03082552007485706</v>
+        <v>0.01373128881977485</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.02581887365352179</v>
+        <v>-0.02549552338669633</v>
       </c>
       <c r="P24" t="n">
-        <v>-2640.925715655555</v>
+        <v>-70241.49263382565</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2640.925715655555</v>
+        <v>-70241.49263382565</v>
       </c>
     </row>
     <row r="25">
@@ -2889,34 +2889,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I25" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J25" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K25" t="n">
         <v>-34000000</v>
       </c>
       <c r="L25" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="M25" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N25" t="n">
-        <v>0.03051606872334229</v>
+        <v>0.01374277691480819</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.02590450870981425</v>
+        <v>-0.02555147156878314</v>
       </c>
       <c r="P25" t="n">
-        <v>-2033.809343185506</v>
+        <v>-337849.6508517564</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2033.809343185506</v>
+        <v>-337849.6508517564</v>
       </c>
     </row>
     <row r="26">
@@ -2950,34 +2950,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I26" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J26" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K26" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M26" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N26" t="n">
-        <v>0.03026857544468633</v>
+        <v>0.01375362077121506</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.025990262065432</v>
+        <v>-0.02560744979333988</v>
       </c>
       <c r="P26" t="n">
-        <v>-1183.060346593632</v>
+        <v>-74469.46147292921</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1183.060346593632</v>
+        <v>-74469.46147292921</v>
       </c>
     </row>
     <row r="27">
@@ -3011,34 +3011,34 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I27" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J27" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K27" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L27" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="M27" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N27" t="n">
-        <v>0.030041267032894</v>
+        <v>0.01376514673139084</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.02607561571305239</v>
+        <v>-0.02566354060598441</v>
       </c>
       <c r="P27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3072,34 +3072,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K28" t="n">
         <v>-680000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N28" t="n">
-        <v>0.02998523830907041</v>
+        <v>0.01167814650917531</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.07502986587896165</v>
+        <v>-0.02264935222023312</v>
       </c>
       <c r="P28" t="n">
-        <v>56142426.80713306</v>
+        <v>14008201.0951103</v>
       </c>
       <c r="Q28" t="n">
-        <v>28071213.40356653</v>
+        <v>7004100.547555152</v>
       </c>
     </row>
     <row r="29">
@@ -3133,34 +3133,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I29" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J29" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K29" t="n">
         <v>-68000000</v>
       </c>
       <c r="L29" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="M29" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N29" t="n">
-        <v>0.03834659693956599</v>
+        <v>0.01796790037339591</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.01988106139069767</v>
+        <v>-0.01985875398907044</v>
       </c>
       <c r="P29" t="n">
-        <v>-7357627.821140663</v>
+        <v>-16221446.97556545</v>
       </c>
       <c r="Q29" t="n">
-        <v>-7357627.821140663</v>
+        <v>-16221446.97556545</v>
       </c>
     </row>
     <row r="30">
@@ -3194,34 +3194,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I30" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J30" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K30" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M30" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N30" t="n">
-        <v>0.04113736359982756</v>
+        <v>0.02108193610380882</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.01725628309459371</v>
+        <v>-0.01722276407024426</v>
       </c>
       <c r="P30" t="n">
-        <v>-33877983.93974058</v>
+        <v>-11897340.54937325</v>
       </c>
       <c r="Q30" t="n">
-        <v>-33877983.93974058</v>
+        <v>-11897340.54937325</v>
       </c>
     </row>
     <row r="31">
@@ -3255,34 +3255,34 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J31" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K31" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L31" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="M31" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0436276127705737</v>
+        <v>0.02369222481558175</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.01489062910622074</v>
+        <v>-0.01482995615663363</v>
       </c>
       <c r="P31" t="n">
-        <v>-3850272.699127598</v>
+        <v>-14296420.08493442</v>
       </c>
       <c r="Q31" t="n">
-        <v>-3850272.699127598</v>
+        <v>-14296420.08493442</v>
       </c>
     </row>
     <row r="32">
@@ -3316,34 +3316,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I32" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J32" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K32" t="n">
         <v>-68000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="M32" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0455480154500596</v>
+        <v>0.02612995067642809</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.01266202848122933</v>
+        <v>-0.01260515871784285</v>
       </c>
       <c r="P32" t="n">
-        <v>1386754.671432244</v>
+        <v>1553842.112197821</v>
       </c>
       <c r="Q32" t="n">
-        <v>693377.3357161219</v>
+        <v>776921.0560989103</v>
       </c>
     </row>
     <row r="33">
@@ -3377,34 +3377,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I33" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J33" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K33" t="n">
         <v>-68000000</v>
       </c>
       <c r="L33" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04746456405164672</v>
+        <v>0.02835546395408812</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.01061579379409725</v>
+        <v>-0.01053392699102673</v>
       </c>
       <c r="P33" t="n">
-        <v>-2557045.331856611</v>
+        <v>1104917.09803376</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2557045.331856611</v>
+        <v>552458.54901688</v>
       </c>
     </row>
     <row r="34">
@@ -3438,34 +3438,34 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I34" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J34" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K34" t="n">
         <v>-34000000</v>
       </c>
       <c r="L34" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0492972557825806</v>
+        <v>0.03038307855295308</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.008701770963537303</v>
+        <v>-0.008630921630449429</v>
       </c>
       <c r="P34" t="n">
-        <v>-930767.1020281399</v>
+        <v>-60062.75249382582</v>
       </c>
       <c r="Q34" t="n">
-        <v>-930767.1020281399</v>
+        <v>-60062.75249382582</v>
       </c>
     </row>
     <row r="35">
@@ -3499,34 +3499,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I35" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J35" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K35" t="n">
         <v>-34000000</v>
       </c>
       <c r="L35" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N35" t="n">
-        <v>0.05045136439179869</v>
+        <v>0.03223800298531072</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.006933843412663093</v>
+        <v>-0.006850555280960409</v>
       </c>
       <c r="P35" t="n">
-        <v>-3097.629718180046</v>
+        <v>128842.9431365761</v>
       </c>
       <c r="Q35" t="n">
-        <v>-3097.629718180046</v>
+        <v>64421.47156828804</v>
       </c>
     </row>
     <row r="36">
@@ -3560,34 +3560,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J36" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K36" t="n">
         <v>-34000000</v>
       </c>
       <c r="L36" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="M36" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N36" t="n">
-        <v>0.05166029289831464</v>
+        <v>0.03392512279467386</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.005293779960104272</v>
+        <v>-0.005233721067838482</v>
       </c>
       <c r="P36" t="n">
-        <v>-1480.266714119976</v>
+        <v>-20846.62897505674</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1480.266714119976</v>
+        <v>-20846.62897505674</v>
       </c>
     </row>
     <row r="37">
@@ -3621,34 +3621,34 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I37" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J37" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K37" t="n">
         <v>-34000000</v>
       </c>
       <c r="L37" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N37" t="n">
-        <v>0.05287569440126383</v>
+        <v>0.03550516138352163</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.003768699327115023</v>
+        <v>-0.003721650822949542</v>
       </c>
       <c r="P37" t="n">
-        <v>-385.487573978435</v>
+        <v>-10253.34153376465</v>
       </c>
       <c r="Q37" t="n">
-        <v>-385.487573978435</v>
+        <v>-10253.34153376465</v>
       </c>
     </row>
     <row r="38">
@@ -3682,34 +3682,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I38" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J38" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K38" t="n">
         <v>-34000000</v>
       </c>
       <c r="L38" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="M38" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0540637033638335</v>
+        <v>0.03696944528723573</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.002356874069323035</v>
+        <v>-0.002324803196355599</v>
       </c>
       <c r="P38" t="n">
-        <v>-185.0424015601879</v>
+        <v>-30739.28427462354</v>
       </c>
       <c r="Q38" t="n">
-        <v>-185.0424015601879</v>
+        <v>-30739.28427462354</v>
       </c>
     </row>
     <row r="39">
@@ -3743,34 +3743,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I39" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J39" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K39" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N39" t="n">
-        <v>0.05521394741144346</v>
+        <v>0.03833155059502284</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.001044890098674874</v>
+        <v>-0.001029519969532107</v>
       </c>
       <c r="P39" t="n">
-        <v>-47.56273865874938</v>
+        <v>-2993.964581612599</v>
       </c>
       <c r="Q39" t="n">
-        <v>-47.56273865874938</v>
+        <v>-2993.964581612599</v>
       </c>
     </row>
     <row r="40">
@@ -3804,28 +3804,28 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I40" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J40" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K40" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L40" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05629090260522096</v>
+        <v>0.03959996871170457</v>
       </c>
       <c r="O40" t="n">
-        <v>0.0001740198592745656</v>
+        <v>0.0001712813743293129</v>
       </c>
       <c r="P40" t="n">
         <v>-0</v>
@@ -3865,34 +3865,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K41" t="n">
         <v>-680000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-750323402.3400002</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N41" t="n">
-        <v>0.08033035812803568</v>
+        <v>0.06222029331429346</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.02468474605999638</v>
+        <v>0.02789279458488503</v>
       </c>
       <c r="P41" t="n">
-        <v>18470798.69717064</v>
+        <v>-36166307.87167858</v>
       </c>
       <c r="Q41" t="n">
-        <v>9235399.348585319</v>
+        <v>-36166307.87167858</v>
       </c>
     </row>
     <row r="42">
@@ -3926,34 +3926,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I42" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J42" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K42" t="n">
         <v>-68000000</v>
       </c>
       <c r="L42" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N42" t="n">
-        <v>0.08318615436787802</v>
+        <v>0.06275211257538338</v>
       </c>
       <c r="O42" t="n">
-        <v>0.02495849603761435</v>
+        <v>0.02492545821291703</v>
       </c>
       <c r="P42" t="n">
-        <v>7680949.978212211</v>
+        <v>18806452.46518519</v>
       </c>
       <c r="Q42" t="n">
-        <v>3840474.989106106</v>
+        <v>9403226.232592596</v>
       </c>
     </row>
     <row r="43">
@@ -3987,34 +3987,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I43" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J43" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K43" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M43" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N43" t="n">
-        <v>0.08055379157089071</v>
+        <v>0.06041097162232134</v>
       </c>
       <c r="O43" t="n">
-        <v>0.02216014487646945</v>
+        <v>0.02210627144826827</v>
       </c>
       <c r="P43" t="n">
-        <v>42249631.43402077</v>
+        <v>15270826.3681861</v>
       </c>
       <c r="Q43" t="n">
-        <v>21124815.71701039</v>
+        <v>7635413.18409305</v>
       </c>
     </row>
     <row r="44">
@@ -4048,34 +4048,34 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I44" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J44" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K44" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L44" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="M44" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N44" t="n">
-        <v>0.07813840667889771</v>
+        <v>0.05805669396429369</v>
       </c>
       <c r="O44" t="n">
-        <v>0.01962016480210327</v>
+        <v>0.01953451299207831</v>
       </c>
       <c r="P44" t="n">
-        <v>4072561.206562099</v>
+        <v>16839201.1539331</v>
       </c>
       <c r="Q44" t="n">
-        <v>2036280.60328105</v>
+        <v>8419600.57696655</v>
       </c>
     </row>
     <row r="45">
@@ -4109,34 +4109,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J45" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K45" t="n">
         <v>-68000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="M45" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N45" t="n">
-        <v>0.07543344707084598</v>
+        <v>0.05587093092788775</v>
       </c>
       <c r="O45" t="n">
-        <v>0.01722340313955706</v>
+        <v>0.01713582153361681</v>
       </c>
       <c r="P45" t="n">
-        <v>-2667114.054291679</v>
+        <v>-2889162.335564557</v>
       </c>
       <c r="Q45" t="n">
-        <v>-2667114.054291679</v>
+        <v>-2889162.335564557</v>
       </c>
     </row>
     <row r="46">
@@ -4170,34 +4170,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J46" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K46" t="n">
         <v>-68000000</v>
       </c>
       <c r="L46" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="M46" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N46" t="n">
-        <v>0.07309558198160494</v>
+        <v>0.05378762523899869</v>
       </c>
       <c r="O46" t="n">
-        <v>0.01501522413586098</v>
+        <v>0.01489823429388384</v>
       </c>
       <c r="P46" t="n">
-        <v>3021140.135026467</v>
+        <v>-2153658.176187682</v>
       </c>
       <c r="Q46" t="n">
-        <v>1510570.067513233</v>
+        <v>-2153658.176187682</v>
       </c>
     </row>
     <row r="47">
@@ -4231,34 +4231,34 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I47" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J47" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K47" t="n">
         <v>-34000000</v>
       </c>
       <c r="L47" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N47" t="n">
-        <v>0.07094844672146827</v>
+        <v>0.05185246316878578</v>
       </c>
       <c r="O47" t="n">
-        <v>0.01294941997535037</v>
+        <v>0.01283846298538327</v>
       </c>
       <c r="P47" t="n">
-        <v>1164968.035973991</v>
+        <v>-128910.7556464296</v>
       </c>
       <c r="Q47" t="n">
-        <v>582484.0179869956</v>
+        <v>-128910.7556464296</v>
       </c>
     </row>
     <row r="48">
@@ -4292,34 +4292,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I48" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J48" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K48" t="n">
         <v>-34000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="M48" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N48" t="n">
-        <v>0.06842305743571853</v>
+        <v>0.05000022680113198</v>
       </c>
       <c r="O48" t="n">
-        <v>0.01103784963125674</v>
+        <v>0.01091166853486086</v>
       </c>
       <c r="P48" t="n">
-        <v>-151438.4803159607</v>
+        <v>-359804.968303106</v>
       </c>
       <c r="Q48" t="n">
-        <v>-151438.4803159607</v>
+        <v>-359804.968303106</v>
       </c>
     </row>
     <row r="49">
@@ -4353,34 +4353,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I49" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J49" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K49" t="n">
         <v>-34000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="M49" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N49" t="n">
-        <v>0.06621878897479672</v>
+        <v>0.04831788295882744</v>
       </c>
       <c r="O49" t="n">
-        <v>0.009264716116377802</v>
+        <v>0.009159039096315102</v>
       </c>
       <c r="P49" t="n">
-        <v>-102409.4811299543</v>
+        <v>-67320.7339339649</v>
       </c>
       <c r="Q49" t="n">
-        <v>-102409.4811299543</v>
+        <v>-67320.7339339649</v>
       </c>
     </row>
     <row r="50">
@@ -4414,34 +4414,34 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I50" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J50" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K50" t="n">
         <v>-34000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="M50" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N50" t="n">
-        <v>0.06426245745541011</v>
+        <v>0.04674923289971685</v>
       </c>
       <c r="O50" t="n">
-        <v>0.007618063727031256</v>
+        <v>0.007522420693245678</v>
       </c>
       <c r="P50" t="n">
-        <v>-63974.31557291824</v>
+        <v>-43215.91573562643</v>
       </c>
       <c r="Q50" t="n">
-        <v>-63974.31557291824</v>
+        <v>-43215.91573562643</v>
       </c>
     </row>
     <row r="51">
@@ -4475,34 +4475,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I51" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J51" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K51" t="n">
         <v>-34000000</v>
       </c>
       <c r="L51" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="M51" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N51" t="n">
-        <v>0.06251548466460592</v>
+        <v>0.04530601718826172</v>
       </c>
       <c r="O51" t="n">
-        <v>0.006094907231449384</v>
+        <v>0.006011768704670392</v>
       </c>
       <c r="P51" t="n">
-        <v>-34059.28556935889</v>
+        <v>45422.82079458048</v>
       </c>
       <c r="Q51" t="n">
-        <v>-34059.28556935889</v>
+        <v>22711.41039729024</v>
       </c>
     </row>
     <row r="52">
@@ -4536,34 +4536,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I52" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J52" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K52" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M52" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N52" t="n">
-        <v>0.06094126886514148</v>
+        <v>0.04397450230184618</v>
       </c>
       <c r="O52" t="n">
-        <v>0.004682431355023151</v>
+        <v>0.004613431737291229</v>
       </c>
       <c r="P52" t="n">
-        <v>-13053.74751546153</v>
+        <v>13416.39951618895</v>
       </c>
       <c r="Q52" t="n">
-        <v>-13053.74751546153</v>
+        <v>6708.199758094475</v>
       </c>
     </row>
     <row r="53">
@@ -4597,28 +4597,28 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I53" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J53" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K53" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L53" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N53" t="n">
-        <v>0.05949006088389019</v>
+        <v>0.042748642330797</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0033731781379438</v>
+        <v>0.003319954993421748</v>
       </c>
       <c r="P53" t="n">
         <v>-0</v>
@@ -4658,34 +4658,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K54" t="n">
         <v>-680000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-750323402.3400002</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N54" t="n">
-        <v>0.08735529861555014</v>
+        <v>0.06923584480754363</v>
       </c>
       <c r="O54" t="n">
-        <v>-0.01765980557248192</v>
+        <v>0.0349083460781352</v>
       </c>
       <c r="P54" t="n">
-        <v>13214262.48289847</v>
+        <v>-45262800.31607471</v>
       </c>
       <c r="Q54" t="n">
-        <v>6607131.241449235</v>
+        <v>-45262800.31607471</v>
       </c>
     </row>
     <row r="55">
@@ -4719,34 +4719,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I55" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J55" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K55" t="n">
         <v>-68000000</v>
       </c>
       <c r="L55" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="M55" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N55" t="n">
-        <v>0.09058485068408295</v>
+        <v>0.0701370260460914</v>
       </c>
       <c r="O55" t="n">
-        <v>0.03235719235381929</v>
+        <v>0.03231037168362505</v>
       </c>
       <c r="P55" t="n">
-        <v>9957890.713066883</v>
+        <v>24378427.22930017</v>
       </c>
       <c r="Q55" t="n">
-        <v>4978945.356533442</v>
+        <v>12189213.61465009</v>
       </c>
     </row>
     <row r="56">
@@ -4780,34 +4780,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I56" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J56" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K56" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M56" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N56" t="n">
-        <v>0.08832183864296361</v>
+        <v>0.06815087156775412</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02992819194854235</v>
+        <v>0.02984617139370105</v>
       </c>
       <c r="P56" t="n">
-        <v>57059874.21838531</v>
+        <v>20617484.14584114</v>
       </c>
       <c r="Q56" t="n">
-        <v>28529937.10919265</v>
+        <v>10308742.07292057</v>
       </c>
     </row>
     <row r="57">
@@ -4841,34 +4841,34 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I57" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J57" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K57" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L57" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="M57" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N57" t="n">
-        <v>0.08624486047266533</v>
+        <v>0.06612186834857425</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02772661859587089</v>
+        <v>0.02759968737635887</v>
       </c>
       <c r="P57" t="n">
-        <v>5755219.307361899</v>
+        <v>23791567.65795208</v>
       </c>
       <c r="Q57" t="n">
-        <v>2877609.653680949</v>
+        <v>11895783.82897604</v>
       </c>
     </row>
     <row r="58">
@@ -4902,34 +4902,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I58" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J58" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K58" t="n">
         <v>-68000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="M58" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N58" t="n">
-        <v>0.08385907763058897</v>
+        <v>0.06424038509770957</v>
       </c>
       <c r="O58" t="n">
-        <v>0.02564903369930005</v>
+        <v>0.02550527570343863</v>
       </c>
       <c r="P58" t="n">
-        <v>-3971857.228452666</v>
+        <v>-4300282.993494238</v>
       </c>
       <c r="Q58" t="n">
-        <v>-3971857.228452666</v>
+        <v>-4300282.993494238</v>
       </c>
     </row>
     <row r="59">
@@ -4963,34 +4963,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I59" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J59" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K59" t="n">
         <v>-68000000</v>
       </c>
       <c r="L59" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="M59" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N59" t="n">
-        <v>0.08181758148143689</v>
+        <v>0.06244146758862694</v>
       </c>
       <c r="O59" t="n">
-        <v>0.02373722363569292</v>
+        <v>0.02355207664351209</v>
       </c>
       <c r="P59" t="n">
-        <v>4776051.184518578</v>
+        <v>-3404639.867311128</v>
       </c>
       <c r="Q59" t="n">
-        <v>2388025.592259289</v>
+        <v>-3404639.867311128</v>
       </c>
     </row>
     <row r="60">
@@ -5024,34 +5024,34 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I60" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J60" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K60" t="n">
         <v>-34000000</v>
       </c>
       <c r="L60" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N60" t="n">
-        <v>0.07994919825034419</v>
+        <v>0.06076922424633224</v>
       </c>
       <c r="O60" t="n">
-        <v>0.02195017150422629</v>
+        <v>0.02175522406292973</v>
       </c>
       <c r="P60" t="n">
-        <v>1974702.20560044</v>
+        <v>-218443.7791659792</v>
       </c>
       <c r="Q60" t="n">
-        <v>987351.1028002198</v>
+        <v>-218443.7791659792</v>
       </c>
     </row>
     <row r="61">
@@ -5085,34 +5085,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I61" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J61" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K61" t="n">
         <v>-34000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N61" t="n">
-        <v>0.07768043009699076</v>
+        <v>0.05916330438233811</v>
       </c>
       <c r="O61" t="n">
-        <v>0.02029522229252897</v>
+        <v>0.02007474611606698</v>
       </c>
       <c r="P61" t="n">
-        <v>-278448.9483306411</v>
+        <v>-661951.3199936553</v>
       </c>
       <c r="Q61" t="n">
-        <v>-278448.9483306411</v>
+        <v>-661951.3199936553</v>
       </c>
     </row>
     <row r="62">
@@ -5146,34 +5146,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I62" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J62" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K62" t="n">
         <v>-34000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="M62" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N62" t="n">
-        <v>0.07571604046176417</v>
+        <v>0.05770655223741961</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01876196760334525</v>
+        <v>0.01854770837490727</v>
       </c>
       <c r="P62" t="n">
-        <v>-207389.3407094274</v>
+        <v>-136329.2947503919</v>
       </c>
       <c r="Q62" t="n">
-        <v>-207389.3407094274</v>
+        <v>-136329.2947503919</v>
       </c>
     </row>
     <row r="63">
@@ -5207,34 +5207,34 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I63" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J63" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K63" t="n">
         <v>-34000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="M63" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N63" t="n">
-        <v>0.07398436000341994</v>
+        <v>0.05634932501465103</v>
       </c>
       <c r="O63" t="n">
-        <v>0.01733996627504109</v>
+        <v>0.01712251280817986</v>
       </c>
       <c r="P63" t="n">
-        <v>-145616.0665297474</v>
+        <v>-98367.94575513355</v>
       </c>
       <c r="Q63" t="n">
-        <v>-145616.0665297474</v>
+        <v>-98367.94575513355</v>
       </c>
     </row>
     <row r="64">
@@ -5268,34 +5268,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I64" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J64" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K64" t="n">
         <v>-34000000</v>
       </c>
       <c r="L64" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="M64" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N64" t="n">
-        <v>0.07244727948281815</v>
+        <v>0.05510242140223998</v>
       </c>
       <c r="O64" t="n">
-        <v>0.01602670204966161</v>
+        <v>0.01580817291864865</v>
       </c>
       <c r="P64" t="n">
-        <v>-89559.69321860342</v>
+        <v>119441.023240911</v>
       </c>
       <c r="Q64" t="n">
-        <v>-89559.69321860342</v>
+        <v>59720.51162045549</v>
       </c>
     </row>
     <row r="65">
@@ -5329,34 +5329,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I65" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J65" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K65" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M65" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0710697595917701</v>
+        <v>0.05395379482856789</v>
       </c>
       <c r="O65" t="n">
-        <v>0.01481092208165177</v>
+        <v>0.01459272426401294</v>
       </c>
       <c r="P65" t="n">
-        <v>-41290.09539406269</v>
+        <v>42437.35030759013</v>
       </c>
       <c r="Q65" t="n">
-        <v>-41290.09539406269</v>
+        <v>21218.67515379507</v>
       </c>
     </row>
     <row r="66">
@@ -5390,28 +5390,28 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I66" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J66" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K66" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L66" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="M66" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N66" t="n">
-        <v>0.06980273792339808</v>
+        <v>0.05289836689808713</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01368585517745169</v>
+        <v>0.01346967956071188</v>
       </c>
       <c r="P66" t="n">
         <v>-0</v>
@@ -5451,34 +5451,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K67" t="n">
         <v>-680000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N67" t="n">
-        <v>0.01772687293857378</v>
+        <v>3.905509319279687e-06</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.08728823124945828</v>
+        <v>-0.03432359322008915</v>
       </c>
       <c r="P67" t="n">
-        <v>65314965.9357306</v>
+        <v>21228500.99457832</v>
       </c>
       <c r="Q67" t="n">
-        <v>32657482.9678653</v>
+        <v>10614250.49728916</v>
       </c>
     </row>
     <row r="68">
@@ -5512,34 +5512,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I68" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J68" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K68" t="n">
         <v>-68000000</v>
       </c>
       <c r="L68" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="M68" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N68" t="n">
-        <v>0.02596200736148457</v>
+        <v>0.005604549383080304</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.03226565096877909</v>
+        <v>-0.03222210497938605</v>
       </c>
       <c r="P68" t="n">
-        <v>-11940944.52855428</v>
+        <v>-26320340.52347312</v>
       </c>
       <c r="Q68" t="n">
-        <v>-11940944.52855428</v>
+        <v>-26320340.52347312</v>
       </c>
     </row>
     <row r="69">
@@ -5573,34 +5573,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I69" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J69" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K69" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M69" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N69" t="n">
-        <v>0.02862082930181886</v>
+        <v>0.008607652840505686</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.0297728173926024</v>
+        <v>-0.02969704733354739</v>
       </c>
       <c r="P69" t="n">
-        <v>-58450769.72476275</v>
+        <v>-20514470.4994533</v>
       </c>
       <c r="Q69" t="n">
-        <v>-58450769.72476275</v>
+        <v>-20514470.4994533</v>
       </c>
     </row>
     <row r="70">
@@ -5634,34 +5634,34 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I70" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J70" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K70" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L70" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="M70" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N70" t="n">
-        <v>0.03098334217962151</v>
+        <v>0.01111073063790968</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.02753489969717293</v>
+        <v>-0.0274114503343057</v>
       </c>
       <c r="P70" t="n">
-        <v>-7119704.064951282</v>
+        <v>-26425270.91634421</v>
       </c>
       <c r="Q70" t="n">
-        <v>-7119704.064951282</v>
+        <v>-26425270.91634421</v>
       </c>
     </row>
     <row r="71">
@@ -5695,34 +5695,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J71" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K71" t="n">
         <v>-68000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="M71" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N71" t="n">
-        <v>0.0327782499425886</v>
+        <v>0.01344239168081884</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.02543179398870032</v>
+        <v>-0.0252927177134521</v>
       </c>
       <c r="P71" t="n">
-        <v>2785308.781212643</v>
+        <v>3117841.734072135</v>
       </c>
       <c r="Q71" t="n">
-        <v>1392654.390606322</v>
+        <v>1558920.867036068</v>
       </c>
     </row>
     <row r="72">
@@ -5756,34 +5756,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I72" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J72" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K72" t="n">
         <v>-68000000</v>
       </c>
       <c r="L72" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="M72" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N72" t="n">
-        <v>0.03457168212681622</v>
+        <v>0.01556325719149214</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.02350867571892774</v>
+        <v>-0.02332613375362271</v>
       </c>
       <c r="P72" t="n">
-        <v>-5662576.97456782</v>
+        <v>2446708.054589245</v>
       </c>
       <c r="Q72" t="n">
-        <v>-5662576.97456782</v>
+        <v>1223354.027294622</v>
       </c>
     </row>
     <row r="73">
@@ -5817,34 +5817,34 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I73" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J73" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K73" t="n">
         <v>-34000000</v>
       </c>
       <c r="L73" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="M73" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N73" t="n">
-        <v>0.03628245893619209</v>
+        <v>0.01748869575344569</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.02171656780992581</v>
+        <v>-0.02152530442995682</v>
       </c>
       <c r="P73" t="n">
-        <v>-2322868.180642799</v>
+        <v>-149795.0146794957</v>
       </c>
       <c r="Q73" t="n">
-        <v>-2322868.180642799</v>
+        <v>-149795.0146794957</v>
       </c>
     </row>
     <row r="74">
@@ -5878,34 +5878,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I74" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J74" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K74" t="n">
         <v>-34000000</v>
       </c>
       <c r="L74" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="M74" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N74" t="n">
-        <v>0.03732101742477235</v>
+        <v>0.01924277012483852</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.02006419037968943</v>
+        <v>-0.01984578814143261</v>
       </c>
       <c r="P74" t="n">
-        <v>-8963.489466439732</v>
+        <v>373252.9186522617</v>
       </c>
       <c r="Q74" t="n">
-        <v>-8963.489466439732</v>
+        <v>186626.4593261308</v>
       </c>
     </row>
     <row r="75">
@@ -5939,34 +5939,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I75" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J75" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K75" t="n">
         <v>-34000000</v>
       </c>
       <c r="L75" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="M75" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N75" t="n">
-        <v>0.03841598150227232</v>
+        <v>0.02083222112667182</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.01853809135614659</v>
+        <v>-0.01832662273584051</v>
       </c>
       <c r="P75" t="n">
-        <v>-5183.6910080559</v>
+        <v>-72997.45240295962</v>
       </c>
       <c r="Q75" t="n">
-        <v>-5183.6910080559</v>
+        <v>-72997.45240295962</v>
       </c>
     </row>
     <row r="76">
@@ -6000,34 +6000,34 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I76" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J76" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K76" t="n">
         <v>-34000000</v>
       </c>
       <c r="L76" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="M76" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N76" t="n">
-        <v>0.03951885651063976</v>
+        <v>0.02231570526743809</v>
       </c>
       <c r="O76" t="n">
-        <v>-0.01712553721773909</v>
+        <v>-0.01691110693903308</v>
       </c>
       <c r="P76" t="n">
-        <v>-1751.713581300022</v>
+        <v>-46590.97895231918</v>
       </c>
       <c r="Q76" t="n">
-        <v>-1751.713581300022</v>
+        <v>-46590.97895231918</v>
       </c>
     </row>
     <row r="77">
@@ -6061,34 +6061,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I77" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J77" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K77" t="n">
         <v>-34000000</v>
       </c>
       <c r="L77" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="M77" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N77" t="n">
-        <v>0.0405960223903211</v>
+        <v>0.0236853362338775</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.01582455504283544</v>
+        <v>-0.01560891224971384</v>
       </c>
       <c r="P77" t="n">
-        <v>-1242.414139499919</v>
+        <v>-206385.9820967902</v>
       </c>
       <c r="Q77" t="n">
-        <v>-1242.414139499919</v>
+        <v>-206385.9820967902</v>
       </c>
     </row>
     <row r="78">
@@ -6122,34 +6122,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I78" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J78" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K78" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M78" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N78" t="n">
-        <v>0.04163683720489108</v>
+        <v>0.02495441337388436</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.01462200030522725</v>
+        <v>-0.01440665719067059</v>
       </c>
       <c r="P78" t="n">
-        <v>-665.5842371055679</v>
+        <v>-41896.24547827392</v>
       </c>
       <c r="Q78" t="n">
-        <v>-665.5842371055679</v>
+        <v>-41896.24547827392</v>
       </c>
     </row>
     <row r="79">
@@ -6183,34 +6183,34 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I79" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J79" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K79" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L79" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="M79" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N79" t="n">
-        <v>0.04260611853542318</v>
+        <v>0.02613142037969185</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.01351076421052322</v>
+        <v>-0.01329726695768341</v>
       </c>
       <c r="P79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6244,34 +6244,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1430323402.34</v>
+        <v>-1300180437.28</v>
       </c>
       <c r="K80" t="n">
         <v>-680000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-750323402.3400002</v>
+        <v>-620180437.28</v>
       </c>
       <c r="M80" t="n">
-        <v>0.1050151041880321</v>
+        <v>0.03432749872940843</v>
       </c>
       <c r="N80" t="n">
-        <v>0.04253896657148259</v>
+        <v>0.02432604806207772</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.06247613761654947</v>
+        <v>-0.01000145066733071</v>
       </c>
       <c r="P80" t="n">
-        <v>46748877.16030184</v>
+        <v>6185710.33857814</v>
       </c>
       <c r="Q80" t="n">
-        <v>23374438.58015092</v>
+        <v>3092855.16928907</v>
       </c>
     </row>
     <row r="81">
@@ -6305,34 +6305,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>425995266.0600001</v>
+        <v>912642221.4799999</v>
       </c>
       <c r="I81" t="n">
-        <v>-90269181.22613968</v>
+        <v>-89542810.95890412</v>
       </c>
       <c r="J81" t="n">
-        <v>335726084.8338604</v>
+        <v>823099410.5210958</v>
       </c>
       <c r="K81" t="n">
         <v>-68000000</v>
       </c>
       <c r="L81" t="n">
-        <v>403726084.8338604</v>
+        <v>891099410.5210958</v>
       </c>
       <c r="M81" t="n">
-        <v>0.05822765833026367</v>
+        <v>0.03782665436246635</v>
       </c>
       <c r="N81" t="n">
-        <v>0.04818573491561828</v>
+        <v>0.02780019384037136</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.01004192341464538</v>
+        <v>-0.01002646052209499</v>
       </c>
       <c r="P81" t="n">
-        <v>-3716337.555696563</v>
+        <v>-8190025.305780896</v>
       </c>
       <c r="Q81" t="n">
-        <v>-3716337.555696563</v>
+        <v>-8190025.305780896</v>
       </c>
     </row>
     <row r="82">
@@ -6366,34 +6366,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>2339361769.16</v>
+        <v>879884659.5500001</v>
       </c>
       <c r="I82" t="n">
-        <v>-51490547.94520548</v>
+        <v>-50934753.42465753</v>
       </c>
       <c r="J82" t="n">
-        <v>2287871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="K82" t="n">
-        <v>-68000000</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>2355871221.214795</v>
+        <v>828949906.1253425</v>
       </c>
       <c r="M82" t="n">
-        <v>0.05839364669442126</v>
+        <v>0.03830470017405307</v>
       </c>
       <c r="N82" t="n">
-        <v>0.04830891037354634</v>
+        <v>0.02825040386828537</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.01008473632087492</v>
+        <v>-0.01005429630576771</v>
       </c>
       <c r="P82" t="n">
-        <v>-19798616.726574</v>
+        <v>-6945423.315685432</v>
       </c>
       <c r="Q82" t="n">
-        <v>-19798616.726574</v>
+        <v>-6945423.315685432</v>
       </c>
     </row>
     <row r="83">
@@ -6427,34 +6427,34 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>368810148.66</v>
+        <v>1240710907.89</v>
       </c>
       <c r="I83" t="n">
-        <v>-92049904.10958904</v>
+        <v>-91346794.52054794</v>
       </c>
       <c r="J83" t="n">
-        <v>276760244.5504109</v>
+        <v>1149364113.369452</v>
       </c>
       <c r="K83" t="n">
-        <v>-68000000</v>
+        <v>-136000000</v>
       </c>
       <c r="L83" t="n">
-        <v>344760244.5504109</v>
+        <v>1285364113.369452</v>
       </c>
       <c r="M83" t="n">
-        <v>0.05851824187679444</v>
+        <v>0.03852218097221538</v>
       </c>
       <c r="N83" t="n">
-        <v>0.04838641196094517</v>
+        <v>0.02843895423713594</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.01013182991584927</v>
+        <v>-0.01008322673507944</v>
       </c>
       <c r="P83" t="n">
-        <v>-2619789.119648522</v>
+        <v>-9720463.344178906</v>
       </c>
       <c r="Q83" t="n">
-        <v>-2619789.119648522</v>
+        <v>-9720463.344178906</v>
       </c>
     </row>
     <row r="84">
@@ -6488,34 +6488,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>-180822610.01</v>
+        <v>-201932841.91</v>
       </c>
       <c r="I84" t="n">
-        <v>-51458493.15068493</v>
+        <v>-50972657.53424658</v>
       </c>
       <c r="J84" t="n">
-        <v>-232281103.1606849</v>
+        <v>-252905499.4442466</v>
       </c>
       <c r="K84" t="n">
         <v>-68000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-164281103.1606849</v>
+        <v>-184905499.4442466</v>
       </c>
       <c r="M84" t="n">
-        <v>0.05821004393128892</v>
+        <v>0.03873510939427094</v>
       </c>
       <c r="N84" t="n">
-        <v>0.04803495850217376</v>
+        <v>0.02862299468186214</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.01017508542911516</v>
+        <v>-0.0101121147124088</v>
       </c>
       <c r="P84" t="n">
-        <v>1114382.839366167</v>
+        <v>1246523.747556976</v>
       </c>
       <c r="Q84" t="n">
-        <v>557191.4196830833</v>
+        <v>623261.873778488</v>
       </c>
     </row>
     <row r="85">
@@ -6549,34 +6549,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>396368601.78</v>
+        <v>-196825268.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-51445520.54794521</v>
+        <v>-50988356.16438356</v>
       </c>
       <c r="J85" t="n">
-        <v>344923081.2320548</v>
+        <v>-247813624.8943836</v>
       </c>
       <c r="K85" t="n">
         <v>-68000000</v>
       </c>
       <c r="L85" t="n">
-        <v>412923081.2320548</v>
+        <v>-179813624.8943836</v>
       </c>
       <c r="M85" t="n">
-        <v>0.05808035784574397</v>
+        <v>0.03888939094511485</v>
       </c>
       <c r="N85" t="n">
-        <v>0.04786041751529452</v>
+        <v>0.02874882009588635</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.01021994033044944</v>
+        <v>-0.0101405708492285</v>
       </c>
       <c r="P85" t="n">
-        <v>-2461695.396566541</v>
+        <v>1063657.468357222</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2461695.396566541</v>
+        <v>531828.7341786108</v>
       </c>
     </row>
     <row r="86">
@@ -6610,34 +6610,34 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>270725457.28</v>
+        <v>69886647.3499999</v>
       </c>
       <c r="I86" t="n">
-        <v>-90799555.08645856</v>
+        <v>-89968608.21917808</v>
       </c>
       <c r="J86" t="n">
-        <v>179925902.1935414</v>
+        <v>-20081960.86917818</v>
       </c>
       <c r="K86" t="n">
         <v>-34000000</v>
       </c>
       <c r="L86" t="n">
-        <v>213925902.1935414</v>
+        <v>13918039.13082182</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0579990267461179</v>
+        <v>0.03901400018340251</v>
       </c>
       <c r="N86" t="n">
-        <v>0.04773570697588347</v>
+        <v>0.02884450571632646</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.01026331977023442</v>
+        <v>-0.01016949446707605</v>
       </c>
       <c r="P86" t="n">
-        <v>-1097794.970674105</v>
+        <v>-70769.71096672022</v>
       </c>
       <c r="Q86" t="n">
-        <v>-1097794.970674105</v>
+        <v>-70769.71096672022</v>
       </c>
     </row>
     <row r="87">
@@ -6671,34 +6671,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-35174959.2</v>
+        <v>-81388394.01999998</v>
       </c>
       <c r="I87" t="n">
-        <v>2247136.761733663</v>
+        <v>2250000</v>
       </c>
       <c r="J87" t="n">
-        <v>-32927822.43826634</v>
+        <v>-79138394.01999998</v>
       </c>
       <c r="K87" t="n">
         <v>-34000000</v>
       </c>
       <c r="L87" t="n">
-        <v>1072177.561733659</v>
+        <v>-45138394.01999998</v>
       </c>
       <c r="M87" t="n">
-        <v>0.05738520780446178</v>
+        <v>0.03908855826627113</v>
       </c>
       <c r="N87" t="n">
-        <v>0.04708113683929442</v>
+        <v>0.02889118764186969</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.01030407096516736</v>
+        <v>-0.01019737062440143</v>
       </c>
       <c r="P87" t="n">
-        <v>-4603.247368068223</v>
+        <v>191788.7221717521</v>
       </c>
       <c r="Q87" t="n">
-        <v>-4603.247368068223</v>
+        <v>95894.36108587607</v>
       </c>
     </row>
     <row r="88">
@@ -6732,34 +6732,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-35427280.72000001</v>
+        <v>-24300588.46000001</v>
       </c>
       <c r="I88" t="n">
-        <v>2266152.03233775</v>
+        <v>2250000</v>
       </c>
       <c r="J88" t="n">
-        <v>-33161128.68766226</v>
+        <v>-22050588.46000001</v>
       </c>
       <c r="K88" t="n">
         <v>-34000000</v>
       </c>
       <c r="L88" t="n">
-        <v>838871.312337745</v>
+        <v>11949411.53999999</v>
       </c>
       <c r="M88" t="n">
-        <v>0.05695407285841891</v>
+        <v>0.03915884386251234</v>
       </c>
       <c r="N88" t="n">
-        <v>0.04660915432675217</v>
+        <v>0.02893202524084604</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.01034491853166675</v>
+        <v>-0.0102268186216663</v>
       </c>
       <c r="P88" t="n">
-        <v>-2892.685128228781</v>
+        <v>-40734.82148507537</v>
       </c>
       <c r="Q88" t="n">
-        <v>-2892.685128228781</v>
+        <v>-40734.82148507537</v>
       </c>
     </row>
     <row r="89">
@@ -6793,34 +6793,34 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-35839034.46</v>
+        <v>-25229792.01000001</v>
       </c>
       <c r="I89" t="n">
-        <v>2248181.001571974</v>
+        <v>2250000</v>
       </c>
       <c r="J89" t="n">
-        <v>-33590853.45842803</v>
+        <v>-22979792.01000001</v>
       </c>
       <c r="K89" t="n">
         <v>-34000000</v>
       </c>
       <c r="L89" t="n">
-        <v>409146.5415719748</v>
+        <v>11020207.98999999</v>
       </c>
       <c r="M89" t="n">
-        <v>0.05664439372837885</v>
+        <v>0.03922681220647117</v>
       </c>
       <c r="N89" t="n">
-        <v>0.04625895250573434</v>
+        <v>0.02897133545183994</v>
       </c>
       <c r="O89" t="n">
-        <v>-0.01038544122264451</v>
+        <v>-0.01025547675463123</v>
       </c>
       <c r="P89" t="n">
-        <v>-1062.291839736006</v>
+        <v>-28254.37171816158</v>
       </c>
       <c r="Q89" t="n">
-        <v>-1062.291839736006</v>
+        <v>-28254.37171816158</v>
       </c>
     </row>
     <row r="90">
@@ -6854,34 +6854,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>-35777615.53999999</v>
+        <v>43083900.58</v>
       </c>
       <c r="I90" t="n">
-        <v>2248686.278913092</v>
+        <v>2250000</v>
       </c>
       <c r="J90" t="n">
-        <v>-33528929.2610869</v>
+        <v>45333900.58</v>
       </c>
       <c r="K90" t="n">
         <v>-34000000</v>
       </c>
       <c r="L90" t="n">
-        <v>471070.7389131002</v>
+        <v>79333900.58</v>
       </c>
       <c r="M90" t="n">
-        <v>0.05642057743315654</v>
+        <v>0.03929424848359133</v>
       </c>
       <c r="N90" t="n">
-        <v>0.04599405363004969</v>
+        <v>0.02900978976389527</v>
       </c>
       <c r="O90" t="n">
-        <v>-0.01042652380310684</v>
+        <v>-0.01028445871969606</v>
       </c>
       <c r="P90" t="n">
-        <v>-818.6050453707613</v>
+        <v>-135984.3709312468</v>
       </c>
       <c r="Q90" t="n">
-        <v>-818.6050453707613</v>
+        <v>-135984.3709312468</v>
       </c>
     </row>
     <row r="91">
@@ -6915,34 +6915,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>-35715304.73</v>
+        <v>32635075.89</v>
       </c>
       <c r="I91" t="n">
-        <v>2261537.165955536</v>
+        <v>2262328.767123288</v>
       </c>
       <c r="J91" t="n">
-        <v>-33453767.56404447</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="K91" t="n">
-        <v>-34000000</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>546232.4359555319</v>
+        <v>34897404.65712329</v>
       </c>
       <c r="M91" t="n">
-        <v>0.05625883751011833</v>
+        <v>0.03936107056455495</v>
       </c>
       <c r="N91" t="n">
-        <v>0.04579124656081188</v>
+        <v>0.02904763456151544</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.01046759094930644</v>
+        <v>-0.01031343600303951</v>
       </c>
       <c r="P91" t="n">
-        <v>-476.478141902145</v>
+        <v>-29992.67913361784</v>
       </c>
       <c r="Q91" t="n">
-        <v>-476.478141902145</v>
+        <v>-29992.67913361784</v>
       </c>
     </row>
     <row r="92">
@@ -6976,34 +6976,34 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-36430105.95000001</v>
+        <v>-85065078.76000001</v>
       </c>
       <c r="I92" t="n">
-        <v>4044566.584325174</v>
+        <v>4045068.493150685</v>
       </c>
       <c r="J92" t="n">
-        <v>-32385539.36567484</v>
+        <v>-81020010.26684932</v>
       </c>
       <c r="K92" t="n">
-        <v>-34000000</v>
+        <v>-68000000</v>
       </c>
       <c r="L92" t="n">
-        <v>1614460.634325162</v>
+        <v>-13020010.26684932</v>
       </c>
       <c r="M92" t="n">
-        <v>0.05611688274594639</v>
+        <v>0.03942868733737526</v>
       </c>
       <c r="N92" t="n">
-        <v>0.04560834936885638</v>
+        <v>0.02908625014097033</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.01050853337709001</v>
+        <v>-0.01034243719640493</v>
       </c>
       <c r="P92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61073262.91000009</v>
+        <v>42411854.98000002</v>
       </c>
       <c r="D2" t="n">
-        <v>30536631.45500004</v>
+        <v>21205927.49000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.08943857583334</v>
+        <v>3.534321248333335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.54471928791667</v>
+        <v>1.767160624166668</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-56816160.41999996</v>
+        <v>-45895908.52000004</v>
       </c>
       <c r="D3" t="n">
-        <v>-56816160.41999996</v>
+        <v>-45895908.52000004</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.734680034999996</v>
+        <v>-3.824659043333337</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.734680034999996</v>
+        <v>-3.824659043333337</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26536310.04000008</v>
+        <v>22464775.51999998</v>
       </c>
       <c r="D4" t="n">
-        <v>13268155.02000004</v>
+        <v>11232387.75999999</v>
       </c>
       <c r="E4" t="n">
-        <v>2.211359170000007</v>
+        <v>1.872064626666665</v>
       </c>
       <c r="F4" t="n">
-        <v>1.105679585000003</v>
+        <v>0.9360323133333326</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-16482595.10000002</v>
+        <v>-22015439.62</v>
       </c>
       <c r="D5" t="n">
-        <v>-16482595.10000002</v>
+        <v>-22015439.62</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.373549591666669</v>
+        <v>-1.834619968333334</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.373549591666669</v>
+        <v>-1.834619968333334</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9155646.850000024</v>
+        <v>-2133251.070000052</v>
       </c>
       <c r="D6" t="n">
-        <v>4577823.425000012</v>
+        <v>-2133251.070000052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7629705708333353</v>
+        <v>-0.1777709225000044</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3814852854166677</v>
+        <v>-0.1777709225000044</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-5077214.439999938</v>
+        <v>-1516111.100000024</v>
       </c>
       <c r="D7" t="n">
-        <v>-5077214.439999938</v>
+        <v>-1516111.100000024</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4231012033333282</v>
+        <v>-0.1263425916666686</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4231012033333282</v>
+        <v>-0.1263425916666686</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-21484632.63</v>
+        <v>-19388537.42000002</v>
       </c>
       <c r="D8" t="n">
-        <v>-21484632.63</v>
+        <v>-19388537.42000002</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.790386052499999</v>
+        <v>-1.615711451666668</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.790386052499999</v>
+        <v>-1.615711451666668</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/nii_results.xlsx
+++ b/irrbb_calc/output/nii_results.xlsx
@@ -511,34 +511,34 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="E2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="F2" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="J2" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="K2" t="n">
-        <v>-12966182.99095671</v>
+        <v>-13445193.69528329</v>
       </c>
       <c r="L2" t="n">
-        <v>6184813.127943014</v>
+        <v>7262179.996653151</v>
       </c>
       <c r="M2" t="n">
-        <v>-12966182.99095671</v>
+        <v>-13445193.69528329</v>
       </c>
       <c r="N2" t="n">
-        <v>6184813.127943014</v>
+        <v>7262179.996653151</v>
       </c>
     </row>
     <row r="3">
@@ -559,34 +559,34 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="G3" t="n">
-        <v>980642221.4799999</v>
+        <v>1036764849.6</v>
       </c>
       <c r="H3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="I3" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="J3" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="K3" t="n">
-        <v>8365887.030233331</v>
+        <v>8935344.454666667</v>
       </c>
       <c r="L3" t="n">
-        <v>-8989220.363566665</v>
+        <v>-9503677.788000001</v>
       </c>
       <c r="M3" t="n">
-        <v>7545077.929776711</v>
+        <v>8114535.354210047</v>
       </c>
       <c r="N3" t="n">
-        <v>-8168411.263110044</v>
+        <v>-8682868.687543381</v>
       </c>
     </row>
     <row r="4">
@@ -607,34 +607,34 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="H4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="I4" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="J4" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K4" t="n">
-        <v>7332372.162916669</v>
+        <v>7266542.022500001</v>
       </c>
       <c r="L4" t="n">
-        <v>-7332372.162916669</v>
+        <v>-7266542.022500001</v>
       </c>
       <c r="M4" t="n">
-        <v>6907915.884377854</v>
+        <v>6842085.743961188</v>
       </c>
       <c r="N4" t="n">
-        <v>-6907915.884377854</v>
+        <v>-6842085.743961188</v>
       </c>
     </row>
     <row r="5">
@@ -655,34 +655,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="G5" t="n">
-        <v>1376710907.89</v>
+        <v>1129206416.05</v>
       </c>
       <c r="H5" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="I5" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="J5" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="K5" t="n">
-        <v>9305331.809175</v>
+        <v>7539048.120375002</v>
       </c>
       <c r="L5" t="n">
-        <v>-10325331.809175</v>
+        <v>-8469048.120375002</v>
       </c>
       <c r="M5" t="n">
-        <v>8620230.85027089</v>
+        <v>6561701.462840755</v>
       </c>
       <c r="N5" t="n">
-        <v>-9640230.85027089</v>
+        <v>-7491701.462840755</v>
       </c>
     </row>
     <row r="6">
@@ -703,34 +703,34 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="F6" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="G6" t="n">
-        <v>-133932841.91</v>
+        <v>-181337598.87</v>
       </c>
       <c r="H6" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="I6" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="J6" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="K6" t="n">
-        <v>-1346218.946066667</v>
+        <v>-1622250.659133334</v>
       </c>
       <c r="L6" t="n">
-        <v>892885.6127333336</v>
+        <v>1208917.3258</v>
       </c>
       <c r="M6" t="n">
-        <v>-1686036.662961644</v>
+        <v>-2221922.549544293</v>
       </c>
       <c r="N6" t="n">
-        <v>1232703.329628311</v>
+        <v>1808589.216210959</v>
       </c>
     </row>
     <row r="7">
@@ -751,34 +751,34 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="F7" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="G7" t="n">
-        <v>-128825268.73</v>
+        <v>-179428019.53</v>
       </c>
       <c r="H7" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="I7" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="J7" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="K7" t="n">
-        <v>-1148147.400925</v>
+        <v>-1408330.113925</v>
       </c>
       <c r="L7" t="n">
-        <v>751480.7342583333</v>
+        <v>1046663.447258333</v>
       </c>
       <c r="M7" t="n">
-        <v>-1445579.478550571</v>
+        <v>-1933175.250911301</v>
       </c>
       <c r="N7" t="n">
-        <v>1048912.811883904</v>
+        <v>1571508.584244634</v>
       </c>
     </row>
     <row r="8">
@@ -799,34 +799,34 @@
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="F8" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="G8" t="n">
-        <v>103886647.3499999</v>
+        <v>180216557.22</v>
       </c>
       <c r="H8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="I8" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="J8" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="K8" t="n">
-        <v>349433.2367499995</v>
+        <v>746082.7861000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-519433.2367499995</v>
+        <v>-901082.7861000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-100409.8043458909</v>
+        <v>296239.7450041097</v>
       </c>
       <c r="N8" t="n">
-        <v>-69590.19565410912</v>
+        <v>-451239.7450041097</v>
       </c>
     </row>
     <row r="9">
@@ -847,34 +847,34 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="E9" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="F9" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="G9" t="n">
-        <v>-47388394.01999998</v>
+        <v>147432754.21</v>
       </c>
       <c r="H9" t="n">
         <v>2250000</v>
       </c>
       <c r="I9" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="J9" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="K9" t="n">
-        <v>-339118.3084166666</v>
+        <v>485136.4758750001</v>
       </c>
       <c r="L9" t="n">
-        <v>197451.6417499999</v>
+        <v>-614303.1425416667</v>
       </c>
       <c r="M9" t="n">
-        <v>-329743.3084166666</v>
+        <v>494511.4758750001</v>
       </c>
       <c r="N9" t="n">
-        <v>188076.6417499999</v>
+        <v>-623678.1425416667</v>
       </c>
     </row>
     <row r="10">
@@ -895,34 +895,34 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="E10" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="G10" t="n">
-        <v>9699411.539999992</v>
+        <v>9978227.919999994</v>
       </c>
       <c r="H10" t="n">
         <v>2250000</v>
       </c>
       <c r="I10" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="J10" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-81001.96153333336</v>
+        <v>-70072.57360000003</v>
       </c>
       <c r="L10" t="n">
-        <v>-32331.37179999998</v>
+        <v>-33260.75973333332</v>
       </c>
       <c r="M10" t="n">
-        <v>-73501.96153333336</v>
+        <v>-62572.57360000003</v>
       </c>
       <c r="N10" t="n">
-        <v>-39831.37179999998</v>
+        <v>-40760.75973333332</v>
       </c>
     </row>
     <row r="11">
@@ -943,34 +943,34 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="F11" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="G11" t="n">
-        <v>8770207.989999995</v>
+        <v>11974398.32</v>
       </c>
       <c r="H11" t="n">
         <v>2250000</v>
       </c>
       <c r="I11" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="J11" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="K11" t="n">
-        <v>-63074.48002500001</v>
+        <v>-47564.0042</v>
       </c>
       <c r="L11" t="n">
-        <v>-21925.51997499999</v>
+        <v>-29935.9958</v>
       </c>
       <c r="M11" t="n">
-        <v>-57449.48002500001</v>
+        <v>-41939.0042</v>
       </c>
       <c r="N11" t="n">
-        <v>-27550.51997499999</v>
+        <v>-35560.9958</v>
       </c>
     </row>
     <row r="12">
@@ -991,34 +991,34 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="F12" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="G12" t="n">
-        <v>77083900.58</v>
+        <v>132044465.29</v>
       </c>
       <c r="H12" t="n">
         <v>2250000</v>
       </c>
       <c r="I12" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="J12" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="K12" t="n">
-        <v>71806.50096666664</v>
+        <v>168407.44215</v>
       </c>
       <c r="L12" t="n">
-        <v>-128473.1676333333</v>
+        <v>-220074.1088166667</v>
       </c>
       <c r="M12" t="n">
-        <v>75556.50096666664</v>
+        <v>172157.44215</v>
       </c>
       <c r="N12" t="n">
-        <v>-132223.1676333333</v>
+        <v>-223824.1088166667</v>
       </c>
     </row>
     <row r="13">
@@ -1039,34 +1039,34 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="E13" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="H13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="I13" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="J13" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K13" t="n">
-        <v>27195.89657500001</v>
+        <v>28576.68173333334</v>
       </c>
       <c r="L13" t="n">
-        <v>-27195.89657500001</v>
+        <v>-28576.68173333334</v>
       </c>
       <c r="M13" t="n">
-        <v>29081.17054760276</v>
+        <v>30461.95570593608</v>
       </c>
       <c r="N13" t="n">
-        <v>-29081.17054760276</v>
+        <v>-30461.95570593608</v>
       </c>
     </row>
     <row r="14">
@@ -1087,22 +1087,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="F14" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="G14" t="n">
-        <v>-17065078.76000001</v>
+        <v>-14962502.42</v>
       </c>
       <c r="H14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="I14" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="J14" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="K14" t="n">
         <v>-0</v>
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9508282.548693284</v>
+        <v>8575726.937258381</v>
       </c>
       <c r="C2" t="n">
-        <v>-19349652.41170698</v>
+        <v>-17548740.63588852</v>
       </c>
       <c r="D2" t="n">
-        <v>6518958.649149906</v>
+        <v>4806890.106208154</v>
       </c>
       <c r="E2" t="n">
-        <v>-16360328.5121636</v>
+        <v>-13779903.80483829</v>
       </c>
     </row>
   </sheetData>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-42396461.29</v>
+        <v>-44845718.98</v>
       </c>
       <c r="D2" t="n">
-        <v>-62912712.16636198</v>
+        <v>-70005305.2013637</v>
       </c>
       <c r="E2" t="n">
-        <v>-105309173.456362</v>
+        <v>-114851024.1813637</v>
       </c>
     </row>
     <row r="3">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62386746.03</v>
+        <v>64383203.57</v>
       </c>
       <c r="D3" t="n">
-        <v>5983713.538328768</v>
+        <v>9175112.345246576</v>
       </c>
       <c r="E3" t="n">
-        <v>68370459.56832877</v>
+        <v>73558315.91524658</v>
       </c>
     </row>
     <row r="4">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2578680.23</v>
+        <v>3324300.7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2578680.23</v>
+        <v>3324300.7</v>
       </c>
     </row>
     <row r="5">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>516914934.53</v>
+        <v>519433585.1</v>
       </c>
       <c r="D5" t="n">
-        <v>48159367.84394944</v>
+        <v>47471274.13383399</v>
       </c>
       <c r="E5" t="n">
-        <v>565074302.3739494</v>
+        <v>566904859.233834</v>
       </c>
     </row>
   </sheetData>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>539483899.5</v>
+        <v>542295370.39</v>
       </c>
       <c r="C2" t="n">
-        <v>-8769630.784083776</v>
+        <v>-13358918.72228313</v>
       </c>
       <c r="D2" t="n">
-        <v>530714268.7159162</v>
+        <v>528936451.6677169</v>
       </c>
     </row>
   </sheetData>
@@ -1486,19 +1486,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K2" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="M2" t="n">
         <v>0.03432749872940843</v>
@@ -1510,10 +1510,10 @@
         <v>0.02500481880599148</v>
       </c>
       <c r="P2" t="n">
-        <v>-32421705.62942012</v>
+        <v>-33619463.21620177</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32421705.62942012</v>
+        <v>-33619463.21620177</v>
       </c>
     </row>
     <row r="3">
@@ -1547,19 +1547,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I3" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J3" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K3" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L3" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="M3" t="n">
         <v>0.03782665436246635</v>
@@ -1571,10 +1571,10 @@
         <v>0.0251058158502353</v>
       </c>
       <c r="P3" t="n">
-        <v>18942533.70806487</v>
+        <v>20372203.03130213</v>
       </c>
       <c r="Q3" t="n">
-        <v>9471266.854032435</v>
+        <v>10186101.51565107</v>
       </c>
     </row>
     <row r="4">
@@ -1608,19 +1608,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I4" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J4" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M4" t="n">
         <v>0.03830470017405307</v>
@@ -1632,10 +1632,10 @@
         <v>0.02521323244800655</v>
       </c>
       <c r="P4" t="n">
-        <v>17417088.89240956</v>
+        <v>17251109.82916852</v>
       </c>
       <c r="Q4" t="n">
-        <v>8708544.446204778</v>
+        <v>8625554.914584262</v>
       </c>
     </row>
     <row r="5">
@@ -1669,19 +1669,19 @@
         <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I5" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J5" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K5" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L5" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="M5" t="n">
         <v>0.03852218097221538</v>
@@ -1693,10 +1693,10 @@
         <v>0.02532026333962101</v>
       </c>
       <c r="P5" t="n">
-        <v>21826651.5177184</v>
+        <v>16614400.89951043</v>
       </c>
       <c r="Q5" t="n">
-        <v>10913325.7588592</v>
+        <v>8307200.449755214</v>
       </c>
     </row>
     <row r="6">
@@ -1730,19 +1730,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I6" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J6" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K6" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="M6" t="n">
         <v>0.03873510939427094</v>
@@ -1754,10 +1754,10 @@
         <v>0.02542872476626745</v>
       </c>
       <c r="P6" t="n">
-        <v>-4287376.224828769</v>
+        <v>-5650065.696432507</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4287376.224828769</v>
+        <v>-5650065.696432507</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1791,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I7" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J7" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K7" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L7" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="M7" t="n">
         <v>0.03888939094511485</v>
@@ -1815,10 +1815,10 @@
         <v>0.02553821260711615</v>
       </c>
       <c r="P7" t="n">
-        <v>-3691751.606370857</v>
+        <v>-4936984.056458791</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3691751.606370857</v>
+        <v>-4936984.056458791</v>
       </c>
     </row>
     <row r="8">
@@ -1852,19 +1852,19 @@
         <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I8" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J8" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K8" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L8" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="M8" t="n">
         <v>0.03901400018340251</v>
@@ -1876,10 +1876,10 @@
         <v>0.02564775160277089</v>
       </c>
       <c r="P8" t="n">
-        <v>-257528.5720346234</v>
+        <v>759788.3394733594</v>
       </c>
       <c r="Q8" t="n">
-        <v>-257528.5720346234</v>
+        <v>379894.1697366797</v>
       </c>
     </row>
     <row r="9">
@@ -1913,19 +1913,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I9" t="n">
         <v>2250000</v>
       </c>
       <c r="J9" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K9" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L9" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="M9" t="n">
         <v>0.03908855826627113</v>
@@ -1937,10 +1937,10 @@
         <v>0.02575828679253624</v>
       </c>
       <c r="P9" t="n">
-        <v>-849362.2706116225</v>
+        <v>1273776.841778861</v>
       </c>
       <c r="Q9" t="n">
-        <v>-849362.2706116225</v>
+        <v>636888.4208894307</v>
       </c>
     </row>
     <row r="10">
@@ -1974,19 +1974,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I10" t="n">
         <v>2250000</v>
       </c>
       <c r="J10" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L10" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="M10" t="n">
         <v>0.03915884386251234</v>
@@ -1998,10 +1998,10 @@
         <v>0.02586772256944581</v>
       </c>
       <c r="P10" t="n">
-        <v>-190132.8349254345</v>
+        <v>-161860.997434103</v>
       </c>
       <c r="Q10" t="n">
-        <v>-190132.8349254345</v>
+        <v>-161860.997434103</v>
       </c>
     </row>
     <row r="11">
@@ -2035,19 +2035,19 @@
         <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I11" t="n">
         <v>2250000</v>
       </c>
       <c r="J11" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L11" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="M11" t="n">
         <v>0.03922681220647117</v>
@@ -2059,10 +2059,10 @@
         <v>0.02597850453979926</v>
       </c>
       <c r="P11" t="n">
-        <v>-149245.157763857</v>
+        <v>-108951.261100436</v>
       </c>
       <c r="Q11" t="n">
-        <v>-149245.157763857</v>
+        <v>-108951.261100436</v>
       </c>
     </row>
     <row r="12">
@@ -2096,19 +2096,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I12" t="n">
         <v>2250000</v>
       </c>
       <c r="J12" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K12" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L12" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="M12" t="n">
         <v>0.03929424848359133</v>
@@ -2120,10 +2120,10 @@
         <v>0.02608953222428303</v>
       </c>
       <c r="P12" t="n">
-        <v>197123.3766723921</v>
+        <v>449150.7134622567</v>
       </c>
       <c r="Q12" t="n">
-        <v>98561.68833619606</v>
+        <v>224575.3567311283</v>
       </c>
     </row>
     <row r="13">
@@ -2157,19 +2157,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H13" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I13" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J13" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M13" t="n">
         <v>0.03936107056455495</v>
@@ -2181,10 +2181,10 @@
         <v>0.02620112954634799</v>
       </c>
       <c r="P13" t="n">
-        <v>76195.95168771796</v>
+        <v>79813.76476863457</v>
       </c>
       <c r="Q13" t="n">
-        <v>38097.97584385898</v>
+        <v>39906.88238431729</v>
       </c>
     </row>
     <row r="14">
@@ -2218,19 +2218,19 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I14" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J14" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K14" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L14" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="M14" t="n">
         <v>0.03942868733737526</v>
@@ -2279,19 +2279,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K15" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L15" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="M15" t="n">
         <v>0.03432749872940843</v>
@@ -2303,10 +2303,10 @@
         <v>-0.02499999878494696</v>
       </c>
       <c r="P15" t="n">
-        <v>15462032.06836994</v>
+        <v>18155449.10923949</v>
       </c>
       <c r="Q15" t="n">
-        <v>7731016.034184968</v>
+        <v>9077724.554619746</v>
       </c>
     </row>
     <row r="16">
@@ -2340,19 +2340,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I16" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J16" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K16" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L16" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="M16" t="n">
         <v>0.03782665436246635</v>
@@ -2364,10 +2364,10 @@
         <v>-0.02505175249492542</v>
       </c>
       <c r="P16" t="n">
-        <v>-20463301.72401939</v>
+        <v>-21752107.73062747</v>
       </c>
       <c r="Q16" t="n">
-        <v>-20463301.72401939</v>
+        <v>-21752107.73062747</v>
       </c>
     </row>
     <row r="17">
@@ -2401,19 +2401,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I17" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J17" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M17" t="n">
         <v>0.03830470017405307</v>
@@ -2425,10 +2425,10 @@
         <v>-0.02510607109988339</v>
       </c>
       <c r="P17" t="n">
-        <v>-17343062.73452042</v>
+        <v>-17177789.11593881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-17343062.73452042</v>
+        <v>-17177789.11593881</v>
       </c>
     </row>
     <row r="18">
@@ -2462,19 +2462,19 @@
         <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I18" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J18" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K18" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L18" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="M18" t="n">
         <v>0.03852218097221538</v>
@@ -2486,10 +2486,10 @@
         <v>-0.02516160099667442</v>
       </c>
       <c r="P18" t="n">
-        <v>-24256364.21703475</v>
+        <v>-18850320.29942011</v>
       </c>
       <c r="Q18" t="n">
-        <v>-24256364.21703475</v>
+        <v>-18850320.29942011</v>
       </c>
     </row>
     <row r="19">
@@ -2523,19 +2523,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J19" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K19" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L19" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="M19" t="n">
         <v>0.03873510939427094</v>
@@ -2547,10 +2547,10 @@
         <v>-0.02521743137943178</v>
       </c>
       <c r="P19" t="n">
-        <v>3108561.1626099</v>
+        <v>4560797.445338016</v>
       </c>
       <c r="Q19" t="n">
-        <v>1554280.58130495</v>
+        <v>2280398.722669008</v>
       </c>
     </row>
     <row r="20">
@@ -2584,19 +2584,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I20" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J20" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K20" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L20" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="M20" t="n">
         <v>0.03888939094511485</v>
@@ -2608,10 +2608,10 @@
         <v>-0.02527289166469284</v>
       </c>
       <c r="P20" t="n">
-        <v>2650905.986045025</v>
+        <v>3971656.619974947</v>
       </c>
       <c r="Q20" t="n">
-        <v>1325452.993022513</v>
+        <v>1985828.309987474</v>
       </c>
     </row>
     <row r="21">
@@ -2645,19 +2645,19 @@
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I21" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J21" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K21" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L21" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="M21" t="n">
         <v>0.03901400018340251</v>
@@ -2669,10 +2669,10 @@
         <v>-0.02532890719506886</v>
       </c>
       <c r="P21" t="n">
-        <v>-176264.3607409614</v>
+        <v>-1142940.962393563</v>
       </c>
       <c r="Q21" t="n">
-        <v>-176264.3607409614</v>
+        <v>-1142940.962393563</v>
       </c>
     </row>
     <row r="22">
@@ -2706,19 +2706,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I22" t="n">
         <v>2250000</v>
       </c>
       <c r="J22" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K22" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L22" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="M22" t="n">
         <v>0.03908855826627113</v>
@@ -2730,10 +2730,10 @@
         <v>-0.02538363335203554</v>
       </c>
       <c r="P22" t="n">
-        <v>477406.8516264138</v>
+        <v>-1583121.729995623</v>
       </c>
       <c r="Q22" t="n">
-        <v>238703.4258132069</v>
+        <v>-1583121.729995623</v>
       </c>
     </row>
     <row r="23">
@@ -2767,19 +2767,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I23" t="n">
         <v>2250000</v>
       </c>
       <c r="J23" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L23" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="M23" t="n">
         <v>0.03915884386251234</v>
@@ -2791,10 +2791,10 @@
         <v>-0.02543993459508764</v>
       </c>
       <c r="P23" t="n">
-        <v>-101330.7493424618</v>
+        <v>-103695.1061662082</v>
       </c>
       <c r="Q23" t="n">
-        <v>-101330.7493424618</v>
+        <v>-103695.1061662082</v>
       </c>
     </row>
     <row r="24">
@@ -2828,19 +2828,19 @@
         <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I24" t="n">
         <v>2250000</v>
       </c>
       <c r="J24" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K24" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L24" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="M24" t="n">
         <v>0.03922681220647117</v>
@@ -2852,10 +2852,10 @@
         <v>-0.02549552338669633</v>
       </c>
       <c r="P24" t="n">
-        <v>-70241.49263382565</v>
+        <v>-90664.62000731099</v>
       </c>
       <c r="Q24" t="n">
-        <v>-70241.49263382565</v>
+        <v>-90664.62000731099</v>
       </c>
     </row>
     <row r="25">
@@ -2889,19 +2889,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I25" t="n">
         <v>2250000</v>
       </c>
       <c r="J25" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K25" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L25" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="M25" t="n">
         <v>0.03929424848359133</v>
@@ -2913,10 +2913,10 @@
         <v>-0.02555147156878314</v>
       </c>
       <c r="P25" t="n">
-        <v>-337849.6508517564</v>
+        <v>-571903.5352837283</v>
       </c>
       <c r="Q25" t="n">
-        <v>-337849.6508517564</v>
+        <v>-571903.5352837283</v>
       </c>
     </row>
     <row r="26">
@@ -2950,19 +2950,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H26" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I26" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J26" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M26" t="n">
         <v>0.03936107056455495</v>
@@ -2974,10 +2974,10 @@
         <v>-0.02560744979333988</v>
       </c>
       <c r="P26" t="n">
-        <v>-74469.46147292921</v>
+        <v>-78005.30013467018</v>
       </c>
       <c r="Q26" t="n">
-        <v>-74469.46147292921</v>
+        <v>-78005.30013467018</v>
       </c>
     </row>
     <row r="27">
@@ -3011,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I27" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J27" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K27" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L27" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="M27" t="n">
         <v>0.03942868733737526</v>
@@ -3072,19 +3072,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H28" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K28" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L28" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="M28" t="n">
         <v>0.03432749872940843</v>
@@ -3096,10 +3096,10 @@
         <v>-0.02264935222023312</v>
       </c>
       <c r="P28" t="n">
-        <v>14008201.0951103</v>
+        <v>16448367.26309286</v>
       </c>
       <c r="Q28" t="n">
-        <v>7004100.547555152</v>
+        <v>8224183.631546429</v>
       </c>
     </row>
     <row r="29">
@@ -3133,19 +3133,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I29" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J29" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K29" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L29" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="M29" t="n">
         <v>0.03782665436246635</v>
@@ -3157,10 +3157,10 @@
         <v>-0.01985875398907044</v>
       </c>
       <c r="P29" t="n">
-        <v>-16221446.97556545</v>
+        <v>-17243095.31853269</v>
       </c>
       <c r="Q29" t="n">
-        <v>-16221446.97556545</v>
+        <v>-17243095.31853269</v>
       </c>
     </row>
     <row r="30">
@@ -3194,19 +3194,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I30" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J30" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M30" t="n">
         <v>0.03830470017405307</v>
@@ -3218,10 +3218,10 @@
         <v>-0.01722276407024426</v>
       </c>
       <c r="P30" t="n">
-        <v>-11897340.54937325</v>
+        <v>-11783962.85166252</v>
       </c>
       <c r="Q30" t="n">
-        <v>-11897340.54937325</v>
+        <v>-11783962.85166252</v>
       </c>
     </row>
     <row r="31">
@@ -3255,19 +3255,19 @@
         <v>0.75</v>
       </c>
       <c r="H31" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I31" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J31" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K31" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L31" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="M31" t="n">
         <v>0.03852218097221538</v>
@@ -3279,10 +3279,10 @@
         <v>-0.01482995615663363</v>
       </c>
       <c r="P31" t="n">
-        <v>-14296420.08493442</v>
+        <v>-11110160.42325164</v>
       </c>
       <c r="Q31" t="n">
-        <v>-14296420.08493442</v>
+        <v>-11110160.42325164</v>
       </c>
     </row>
     <row r="32">
@@ -3316,19 +3316,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I32" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J32" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K32" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L32" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="M32" t="n">
         <v>0.03873510939427094</v>
@@ -3340,10 +3340,10 @@
         <v>-0.01260515871784285</v>
       </c>
       <c r="P32" t="n">
-        <v>1553842.112197821</v>
+        <v>2279755.412571813</v>
       </c>
       <c r="Q32" t="n">
-        <v>776921.0560989103</v>
+        <v>1139877.706285907</v>
       </c>
     </row>
     <row r="33">
@@ -3377,19 +3377,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I33" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J33" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K33" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L33" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="M33" t="n">
         <v>0.03888939094511485</v>
@@ -3401,10 +3401,10 @@
         <v>-0.01053392699102673</v>
       </c>
       <c r="P33" t="n">
-        <v>1104917.09803376</v>
+        <v>1655415.669220475</v>
       </c>
       <c r="Q33" t="n">
-        <v>552458.54901688</v>
+        <v>827707.8346102377</v>
       </c>
     </row>
     <row r="34">
@@ -3438,19 +3438,19 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I34" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J34" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K34" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L34" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="M34" t="n">
         <v>0.03901400018340251</v>
@@ -3462,10 +3462,10 @@
         <v>-0.008630921630449429</v>
       </c>
       <c r="P34" t="n">
-        <v>-60062.75249382582</v>
+        <v>-389461.4875674455</v>
       </c>
       <c r="Q34" t="n">
-        <v>-60062.75249382582</v>
+        <v>-389461.4875674455</v>
       </c>
     </row>
     <row r="35">
@@ -3499,19 +3499,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I35" t="n">
         <v>2250000</v>
       </c>
       <c r="J35" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K35" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L35" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="M35" t="n">
         <v>0.03908855826627113</v>
@@ -3523,10 +3523,10 @@
         <v>-0.006850555280960409</v>
       </c>
       <c r="P35" t="n">
-        <v>128842.9431365761</v>
+        <v>-427254.1593008393</v>
       </c>
       <c r="Q35" t="n">
-        <v>64421.47156828804</v>
+        <v>-427254.1593008393</v>
       </c>
     </row>
     <row r="36">
@@ -3560,19 +3560,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I36" t="n">
         <v>2250000</v>
       </c>
       <c r="J36" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L36" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="M36" t="n">
         <v>0.03915884386251234</v>
@@ -3584,10 +3584,10 @@
         <v>-0.005233721067838482</v>
       </c>
       <c r="P36" t="n">
-        <v>-20846.62897505674</v>
+        <v>-21333.04469574491</v>
       </c>
       <c r="Q36" t="n">
-        <v>-20846.62897505674</v>
+        <v>-21333.04469574491</v>
       </c>
     </row>
     <row r="37">
@@ -3621,19 +3621,19 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I37" t="n">
         <v>2250000</v>
       </c>
       <c r="J37" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K37" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L37" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="M37" t="n">
         <v>0.03922681220647117</v>
@@ -3645,10 +3645,10 @@
         <v>-0.003721650822949542</v>
       </c>
       <c r="P37" t="n">
-        <v>-10253.34153376465</v>
+        <v>-13234.56092839752</v>
       </c>
       <c r="Q37" t="n">
-        <v>-10253.34153376465</v>
+        <v>-13234.56092839752</v>
       </c>
     </row>
     <row r="38">
@@ -3682,19 +3682,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I38" t="n">
         <v>2250000</v>
       </c>
       <c r="J38" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L38" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="M38" t="n">
         <v>0.03929424848359133</v>
@@ -3706,10 +3706,10 @@
         <v>-0.002324803196355599</v>
       </c>
       <c r="P38" t="n">
-        <v>-30739.28427462354</v>
+        <v>-52034.700359843</v>
       </c>
       <c r="Q38" t="n">
-        <v>-30739.28427462354</v>
+        <v>-52034.700359843</v>
       </c>
     </row>
     <row r="39">
@@ -3743,19 +3743,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H39" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I39" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J39" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M39" t="n">
         <v>0.03936107056455495</v>
@@ -3767,10 +3767,10 @@
         <v>-0.001029519969532107</v>
       </c>
       <c r="P39" t="n">
-        <v>-2993.964581612599</v>
+        <v>-3136.119171026371</v>
       </c>
       <c r="Q39" t="n">
-        <v>-2993.964581612599</v>
+        <v>-3136.119171026371</v>
       </c>
     </row>
     <row r="40">
@@ -3804,19 +3804,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I40" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J40" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K40" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L40" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="M40" t="n">
         <v>0.03942868733737526</v>
@@ -3865,19 +3865,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H41" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K41" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L41" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="M41" t="n">
         <v>0.03432749872940843</v>
@@ -3889,10 +3889,10 @@
         <v>0.02789279458488503</v>
       </c>
       <c r="P41" t="n">
-        <v>-36166307.87167858</v>
+        <v>-37502402.5896528</v>
       </c>
       <c r="Q41" t="n">
-        <v>-36166307.87167858</v>
+        <v>-37502402.5896528</v>
       </c>
     </row>
     <row r="42">
@@ -3926,19 +3926,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H42" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I42" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J42" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K42" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L42" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="M42" t="n">
         <v>0.03782665436246635</v>
@@ -3950,10 +3950,10 @@
         <v>0.02492545821291703</v>
       </c>
       <c r="P42" t="n">
-        <v>18806452.46518519</v>
+        <v>20225851.18886004</v>
       </c>
       <c r="Q42" t="n">
-        <v>9403226.232592596</v>
+        <v>10112925.59443002</v>
       </c>
     </row>
     <row r="43">
@@ -3987,19 +3987,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I43" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J43" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M43" t="n">
         <v>0.03830470017405307</v>
@@ -4011,10 +4011,10 @@
         <v>0.02210627144826827</v>
       </c>
       <c r="P43" t="n">
-        <v>15270826.3681861</v>
+        <v>15125300.47283325</v>
       </c>
       <c r="Q43" t="n">
-        <v>7635413.18409305</v>
+        <v>7562650.236416627</v>
       </c>
     </row>
     <row r="44">
@@ -4048,19 +4048,19 @@
         <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I44" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J44" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K44" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L44" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="M44" t="n">
         <v>0.03852218097221538</v>
@@ -4072,10 +4072,10 @@
         <v>0.01953451299207831</v>
       </c>
       <c r="P44" t="n">
-        <v>16839201.1539331</v>
+        <v>12817964.2476002</v>
       </c>
       <c r="Q44" t="n">
-        <v>8419600.57696655</v>
+        <v>6408982.1238001</v>
       </c>
     </row>
     <row r="45">
@@ -4109,19 +4109,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J45" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K45" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L45" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="M45" t="n">
         <v>0.03873510939427094</v>
@@ -4133,10 +4133,10 @@
         <v>0.01713582153361681</v>
       </c>
       <c r="P45" t="n">
-        <v>-2889162.335564557</v>
+        <v>-3807446.827050986</v>
       </c>
       <c r="Q45" t="n">
-        <v>-2889162.335564557</v>
+        <v>-3807446.827050986</v>
       </c>
     </row>
     <row r="46">
@@ -4170,19 +4170,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I46" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J46" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K46" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L46" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="M46" t="n">
         <v>0.03888939094511485</v>
@@ -4194,10 +4194,10 @@
         <v>0.01489823429388384</v>
       </c>
       <c r="P46" t="n">
-        <v>-2153658.176187682</v>
+        <v>-2880089.781921424</v>
       </c>
       <c r="Q46" t="n">
-        <v>-2153658.176187682</v>
+        <v>-2880089.781921424</v>
       </c>
     </row>
     <row r="47">
@@ -4231,19 +4231,19 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I47" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J47" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K47" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L47" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="M47" t="n">
         <v>0.03901400018340251</v>
@@ -4255,10 +4255,10 @@
         <v>0.01283846298538327</v>
       </c>
       <c r="P47" t="n">
-        <v>-128910.7556464296</v>
+        <v>380326.3001034642</v>
       </c>
       <c r="Q47" t="n">
-        <v>-128910.7556464296</v>
+        <v>190163.1500517321</v>
       </c>
     </row>
     <row r="48">
@@ -4292,19 +4292,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H48" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I48" t="n">
         <v>2250000</v>
       </c>
       <c r="J48" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K48" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L48" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="M48" t="n">
         <v>0.03908855826627113</v>
@@ -4316,10 +4316,10 @@
         <v>0.01091166853486086</v>
       </c>
       <c r="P48" t="n">
-        <v>-359804.968303106</v>
+        <v>539594.5311432841</v>
       </c>
       <c r="Q48" t="n">
-        <v>-359804.968303106</v>
+        <v>269797.265571642</v>
       </c>
     </row>
     <row r="49">
@@ -4353,19 +4353,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H49" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I49" t="n">
         <v>2250000</v>
       </c>
       <c r="J49" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L49" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="M49" t="n">
         <v>0.03915884386251234</v>
@@ -4377,10 +4377,10 @@
         <v>0.009159039096315102</v>
       </c>
       <c r="P49" t="n">
-        <v>-67320.7339339649</v>
+        <v>-57310.46479594545</v>
       </c>
       <c r="Q49" t="n">
-        <v>-67320.7339339649</v>
+        <v>-57310.46479594545</v>
       </c>
     </row>
     <row r="50">
@@ -4414,19 +4414,19 @@
         <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I50" t="n">
         <v>2250000</v>
       </c>
       <c r="J50" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K50" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L50" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="M50" t="n">
         <v>0.03922681220647117</v>
@@ -4438,10 +4438,10 @@
         <v>0.007522420693245678</v>
       </c>
       <c r="P50" t="n">
-        <v>-43215.91573562643</v>
+        <v>-31548.28330481974</v>
       </c>
       <c r="Q50" t="n">
-        <v>-43215.91573562643</v>
+        <v>-31548.28330481974</v>
       </c>
     </row>
     <row r="51">
@@ -4475,19 +4475,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I51" t="n">
         <v>2250000</v>
       </c>
       <c r="J51" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K51" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L51" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="M51" t="n">
         <v>0.03929424848359133</v>
@@ -4499,10 +4499,10 @@
         <v>0.006011768704670392</v>
       </c>
       <c r="P51" t="n">
-        <v>45422.82079458048</v>
+        <v>103497.0722993473</v>
       </c>
       <c r="Q51" t="n">
-        <v>22711.41039729024</v>
+        <v>51748.53614967367</v>
       </c>
     </row>
     <row r="52">
@@ -4536,19 +4536,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H52" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I52" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J52" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M52" t="n">
         <v>0.03936107056455495</v>
@@ -4560,10 +4560,10 @@
         <v>0.004613431737291229</v>
       </c>
       <c r="P52" t="n">
-        <v>13416.39951618895</v>
+        <v>14053.41532337252</v>
       </c>
       <c r="Q52" t="n">
-        <v>6708.199758094475</v>
+        <v>7026.70766168626</v>
       </c>
     </row>
     <row r="53">
@@ -4597,19 +4597,19 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I53" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J53" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K53" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L53" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="M53" t="n">
         <v>0.03942868733737526</v>
@@ -4658,19 +4658,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H54" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K54" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L54" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="M54" t="n">
         <v>0.03432749872940843</v>
@@ -4682,10 +4682,10 @@
         <v>0.0349083460781352</v>
       </c>
       <c r="P54" t="n">
-        <v>-45262800.31607471</v>
+        <v>-46934947.46025104</v>
       </c>
       <c r="Q54" t="n">
-        <v>-45262800.31607471</v>
+        <v>-46934947.46025104</v>
       </c>
     </row>
     <row r="55">
@@ -4719,19 +4719,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H55" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I55" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J55" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K55" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L55" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="M55" t="n">
         <v>0.03782665436246635</v>
@@ -4743,10 +4743,10 @@
         <v>0.03231037168362505</v>
       </c>
       <c r="P55" t="n">
-        <v>24378427.22930017</v>
+        <v>26218365.33344426</v>
       </c>
       <c r="Q55" t="n">
-        <v>12189213.61465009</v>
+        <v>13109182.66672213</v>
       </c>
     </row>
     <row r="56">
@@ -4780,19 +4780,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I56" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J56" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M56" t="n">
         <v>0.03830470017405307</v>
@@ -4804,10 +4804,10 @@
         <v>0.02984617139370105</v>
       </c>
       <c r="P56" t="n">
-        <v>20617484.14584114</v>
+        <v>20421006.38046642</v>
       </c>
       <c r="Q56" t="n">
-        <v>10308742.07292057</v>
+        <v>10210503.19023321</v>
       </c>
     </row>
     <row r="57">
@@ -4841,19 +4841,19 @@
         <v>0.75</v>
       </c>
       <c r="H57" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I57" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J57" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K57" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L57" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="M57" t="n">
         <v>0.03852218097221538</v>
@@ -4865,10 +4865,10 @@
         <v>0.02759968737635887</v>
       </c>
       <c r="P57" t="n">
-        <v>23791567.65795208</v>
+        <v>18110090.90314015</v>
       </c>
       <c r="Q57" t="n">
-        <v>11895783.82897604</v>
+        <v>9055045.451570075</v>
       </c>
     </row>
     <row r="58">
@@ -4902,19 +4902,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I58" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J58" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K58" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L58" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="M58" t="n">
         <v>0.03873510939427094</v>
@@ -4926,10 +4926,10 @@
         <v>0.02550527570343863</v>
       </c>
       <c r="P58" t="n">
-        <v>-4300282.993494238</v>
+        <v>-5667074.721781447</v>
       </c>
       <c r="Q58" t="n">
-        <v>-4300282.993494238</v>
+        <v>-5667074.721781447</v>
       </c>
     </row>
     <row r="59">
@@ -4963,19 +4963,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H59" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I59" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J59" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K59" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L59" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="M59" t="n">
         <v>0.03888939094511485</v>
@@ -4987,10 +4987,10 @@
         <v>0.02355207664351209</v>
       </c>
       <c r="P59" t="n">
-        <v>-3404639.867311128</v>
+        <v>-4553029.167480368</v>
       </c>
       <c r="Q59" t="n">
-        <v>-3404639.867311128</v>
+        <v>-4553029.167480368</v>
       </c>
     </row>
     <row r="60">
@@ -5024,19 +5024,19 @@
         <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I60" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J60" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K60" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L60" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="M60" t="n">
         <v>0.03901400018340251</v>
@@ -5048,10 +5048,10 @@
         <v>0.02175522406292973</v>
       </c>
       <c r="P60" t="n">
-        <v>-218443.7791659792</v>
+        <v>644476.2028909577</v>
       </c>
       <c r="Q60" t="n">
-        <v>-218443.7791659792</v>
+        <v>322238.1014454789</v>
       </c>
     </row>
     <row r="61">
@@ -5085,19 +5085,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H61" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I61" t="n">
         <v>2250000</v>
       </c>
       <c r="J61" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K61" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L61" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="M61" t="n">
         <v>0.03908855826627113</v>
@@ -5109,10 +5109,10 @@
         <v>0.02007474611606698</v>
       </c>
       <c r="P61" t="n">
-        <v>-661951.3199936553</v>
+        <v>992719.2329672207</v>
       </c>
       <c r="Q61" t="n">
-        <v>-661951.3199936553</v>
+        <v>496359.6164836104</v>
       </c>
     </row>
     <row r="62">
@@ -5146,19 +5146,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H62" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I62" t="n">
         <v>2250000</v>
       </c>
       <c r="J62" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L62" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="M62" t="n">
         <v>0.03915884386251234</v>
@@ -5170,10 +5170,10 @@
         <v>0.01854770837490727</v>
       </c>
       <c r="P62" t="n">
-        <v>-136329.2947503919</v>
+        <v>-116057.7847400222</v>
       </c>
       <c r="Q62" t="n">
-        <v>-136329.2947503919</v>
+        <v>-116057.7847400222</v>
       </c>
     </row>
     <row r="63">
@@ -5207,19 +5207,19 @@
         <v>0.25</v>
       </c>
       <c r="H63" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I63" t="n">
         <v>2250000</v>
       </c>
       <c r="J63" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K63" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L63" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="M63" t="n">
         <v>0.03922681220647117</v>
@@ -5231,10 +5231,10 @@
         <v>0.01712251280817986</v>
       </c>
       <c r="P63" t="n">
-        <v>-98367.94575513355</v>
+        <v>-71810.11365768088</v>
       </c>
       <c r="Q63" t="n">
-        <v>-98367.94575513355</v>
+        <v>-71810.11365768088</v>
       </c>
     </row>
     <row r="64">
@@ -5268,19 +5268,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I64" t="n">
         <v>2250000</v>
       </c>
       <c r="J64" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K64" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L64" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="M64" t="n">
         <v>0.03929424848359133</v>
@@ -5292,10 +5292,10 @@
         <v>0.01580817291864865</v>
       </c>
       <c r="P64" t="n">
-        <v>119441.023240911</v>
+        <v>272149.4614739451</v>
       </c>
       <c r="Q64" t="n">
-        <v>59720.51162045549</v>
+        <v>136074.7307369725</v>
       </c>
     </row>
     <row r="65">
@@ -5329,19 +5329,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H65" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I65" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J65" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M65" t="n">
         <v>0.03936107056455495</v>
@@ -5353,10 +5353,10 @@
         <v>0.01459272426401294</v>
       </c>
       <c r="P65" t="n">
-        <v>42437.35030759013</v>
+        <v>44452.29201593011</v>
       </c>
       <c r="Q65" t="n">
-        <v>21218.67515379507</v>
+        <v>22226.14600796506</v>
       </c>
     </row>
     <row r="66">
@@ -5390,19 +5390,19 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I66" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J66" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K66" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L66" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="M66" t="n">
         <v>0.03942868733737526</v>
@@ -5451,19 +5451,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H67" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K67" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L67" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="M67" t="n">
         <v>0.03432749872940843</v>
@@ -5475,10 +5475,10 @@
         <v>-0.03432359322008915</v>
       </c>
       <c r="P67" t="n">
-        <v>21228500.99457832</v>
+        <v>24926411.20961912</v>
       </c>
       <c r="Q67" t="n">
-        <v>10614250.49728916</v>
+        <v>12463205.60480956</v>
       </c>
     </row>
     <row r="68">
@@ -5512,19 +5512,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H68" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I68" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J68" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K68" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L68" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="M68" t="n">
         <v>0.03782665436246635</v>
@@ -5536,10 +5536,10 @@
         <v>-0.03222210497938605</v>
       </c>
       <c r="P68" t="n">
-        <v>-26320340.52347312</v>
+        <v>-27978030.63722467</v>
       </c>
       <c r="Q68" t="n">
-        <v>-26320340.52347312</v>
+        <v>-27978030.63722467</v>
       </c>
     </row>
     <row r="69">
@@ -5573,19 +5573,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I69" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J69" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M69" t="n">
         <v>0.03830470017405307</v>
@@ -5597,10 +5597,10 @@
         <v>-0.02969704733354739</v>
       </c>
       <c r="P69" t="n">
-        <v>-20514470.4994533</v>
+        <v>-20318974.41986052</v>
       </c>
       <c r="Q69" t="n">
-        <v>-20514470.4994533</v>
+        <v>-20318974.41986052</v>
       </c>
     </row>
     <row r="70">
@@ -5634,19 +5634,19 @@
         <v>0.75</v>
       </c>
       <c r="H70" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I70" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J70" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K70" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L70" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="M70" t="n">
         <v>0.03852218097221538</v>
@@ -5658,10 +5658,10 @@
         <v>-0.0274114503343057</v>
       </c>
       <c r="P70" t="n">
-        <v>-26425270.91634421</v>
+        <v>-20535840.25681047</v>
       </c>
       <c r="Q70" t="n">
-        <v>-26425270.91634421</v>
+        <v>-20535840.25681047</v>
       </c>
     </row>
     <row r="71">
@@ -5695,19 +5695,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J71" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K71" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L71" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="M71" t="n">
         <v>0.03873510939427094</v>
@@ -5719,10 +5719,10 @@
         <v>-0.0252927177134521</v>
       </c>
       <c r="P71" t="n">
-        <v>3117841.734072135</v>
+        <v>4574413.650521738</v>
       </c>
       <c r="Q71" t="n">
-        <v>1558920.867036068</v>
+        <v>2287206.825260869</v>
       </c>
     </row>
     <row r="72">
@@ -5756,19 +5756,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I72" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J72" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K72" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L72" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="M72" t="n">
         <v>0.03888939094511485</v>
@@ -5780,10 +5780,10 @@
         <v>-0.02332613375362271</v>
       </c>
       <c r="P72" t="n">
-        <v>2446708.054589245</v>
+        <v>3665721.943105661</v>
       </c>
       <c r="Q72" t="n">
-        <v>1223354.027294622</v>
+        <v>1832860.971552831</v>
       </c>
     </row>
     <row r="73">
@@ -5817,19 +5817,19 @@
         <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I73" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J73" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K73" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L73" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="M73" t="n">
         <v>0.03901400018340251</v>
@@ -5841,10 +5841,10 @@
         <v>-0.02152530442995682</v>
       </c>
       <c r="P73" t="n">
-        <v>-149795.0146794957</v>
+        <v>-971307.2882109547</v>
       </c>
       <c r="Q73" t="n">
-        <v>-149795.0146794957</v>
+        <v>-971307.2882109547</v>
       </c>
     </row>
     <row r="74">
@@ -5878,19 +5878,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H74" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I74" t="n">
         <v>2250000</v>
       </c>
       <c r="J74" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K74" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L74" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="M74" t="n">
         <v>0.03908855826627113</v>
@@ -5902,10 +5902,10 @@
         <v>-0.01984578814143261</v>
       </c>
       <c r="P74" t="n">
-        <v>373252.9186522617</v>
+        <v>-1237738.428532413</v>
       </c>
       <c r="Q74" t="n">
-        <v>186626.4593261308</v>
+        <v>-1237738.428532413</v>
       </c>
     </row>
     <row r="75">
@@ -5939,19 +5939,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I75" t="n">
         <v>2250000</v>
       </c>
       <c r="J75" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L75" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="M75" t="n">
         <v>0.03915884386251234</v>
@@ -5963,10 +5963,10 @@
         <v>-0.01832662273584051</v>
       </c>
       <c r="P75" t="n">
-        <v>-72997.45240295962</v>
+        <v>-74700.70660590389</v>
       </c>
       <c r="Q75" t="n">
-        <v>-72997.45240295962</v>
+        <v>-74700.70660590389</v>
       </c>
     </row>
     <row r="76">
@@ -6000,19 +6000,19 @@
         <v>0.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I76" t="n">
         <v>2250000</v>
       </c>
       <c r="J76" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K76" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L76" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="M76" t="n">
         <v>0.03922681220647117</v>
@@ -6024,10 +6024,10 @@
         <v>-0.01691110693903308</v>
       </c>
       <c r="P76" t="n">
-        <v>-46590.97895231918</v>
+        <v>-60137.58028323063</v>
       </c>
       <c r="Q76" t="n">
-        <v>-46590.97895231918</v>
+        <v>-60137.58028323063</v>
       </c>
     </row>
     <row r="77">
@@ -6061,19 +6061,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I77" t="n">
         <v>2250000</v>
       </c>
       <c r="J77" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K77" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L77" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="M77" t="n">
         <v>0.03929424848359133</v>
@@ -6085,10 +6085,10 @@
         <v>-0.01560891224971384</v>
       </c>
       <c r="P77" t="n">
-        <v>-206385.9820967902</v>
+        <v>-349365.0873889751</v>
       </c>
       <c r="Q77" t="n">
-        <v>-206385.9820967902</v>
+        <v>-349365.0873889751</v>
       </c>
     </row>
     <row r="78">
@@ -6122,19 +6122,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H78" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I78" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J78" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M78" t="n">
         <v>0.03936107056455495</v>
@@ -6146,10 +6146,10 @@
         <v>-0.01440665719067059</v>
       </c>
       <c r="P78" t="n">
-        <v>-41896.24547827392</v>
+        <v>-43885.49532128132</v>
       </c>
       <c r="Q78" t="n">
-        <v>-41896.24547827392</v>
+        <v>-43885.49532128132</v>
       </c>
     </row>
     <row r="79">
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I79" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J79" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K79" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L79" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="M79" t="n">
         <v>0.03942868733737526</v>
@@ -6244,19 +6244,19 @@
         <v>0.9972602739726028</v>
       </c>
       <c r="H80" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1300180437.28</v>
+        <v>-1348213104.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-680000000</v>
+        <v>-620000000</v>
       </c>
       <c r="L80" t="n">
-        <v>-620180437.28</v>
+        <v>-728213104.0599999</v>
       </c>
       <c r="M80" t="n">
         <v>0.03432749872940843</v>
@@ -6268,10 +6268,10 @@
         <v>-0.01000145066733071</v>
       </c>
       <c r="P80" t="n">
-        <v>6185710.33857814</v>
+        <v>7263233.497380241</v>
       </c>
       <c r="Q80" t="n">
-        <v>3092855.16928907</v>
+        <v>3631616.74869012</v>
       </c>
     </row>
     <row r="81">
@@ -6305,19 +6305,19 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>912642221.4799999</v>
+        <v>974764849.6000001</v>
       </c>
       <c r="I81" t="n">
         <v>-89542810.95890412</v>
       </c>
       <c r="J81" t="n">
-        <v>823099410.5210958</v>
+        <v>885222038.641096</v>
       </c>
       <c r="K81" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L81" t="n">
-        <v>891099410.5210958</v>
+        <v>947222038.641096</v>
       </c>
       <c r="M81" t="n">
         <v>0.03782665436246635</v>
@@ -6329,10 +6329,10 @@
         <v>-0.01002646052209499</v>
       </c>
       <c r="P81" t="n">
-        <v>-8190025.305780896</v>
+        <v>-8705844.011418846</v>
       </c>
       <c r="Q81" t="n">
-        <v>-8190025.305780896</v>
+        <v>-8705844.011418846</v>
       </c>
     </row>
     <row r="82">
@@ -6366,19 +6366,19 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>879884659.5500001</v>
+        <v>871985042.7</v>
       </c>
       <c r="I82" t="n">
         <v>-50934753.42465753</v>
       </c>
       <c r="J82" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>828949906.1253425</v>
+        <v>821050289.2753425</v>
       </c>
       <c r="M82" t="n">
         <v>0.03830470017405307</v>
@@ -6390,10 +6390,10 @@
         <v>-0.01005429630576771</v>
       </c>
       <c r="P82" t="n">
-        <v>-6945423.315685432</v>
+        <v>-6879235.741925485</v>
       </c>
       <c r="Q82" t="n">
-        <v>-6945423.315685432</v>
+        <v>-6879235.741925485</v>
       </c>
     </row>
     <row r="83">
@@ -6427,19 +6427,19 @@
         <v>0.75</v>
       </c>
       <c r="H83" t="n">
-        <v>1240710907.89</v>
+        <v>1005206416.05</v>
       </c>
       <c r="I83" t="n">
-        <v>-91346794.52054794</v>
+        <v>-130312887.6712329</v>
       </c>
       <c r="J83" t="n">
-        <v>1149364113.369452</v>
+        <v>874893528.3787673</v>
       </c>
       <c r="K83" t="n">
-        <v>-136000000</v>
+        <v>-124000000</v>
       </c>
       <c r="L83" t="n">
-        <v>1285364113.369452</v>
+        <v>998893528.3787673</v>
       </c>
       <c r="M83" t="n">
         <v>0.03852218097221538</v>
@@ -6451,10 +6451,10 @@
         <v>-0.01008322673507944</v>
       </c>
       <c r="P83" t="n">
-        <v>-9720463.344178906</v>
+        <v>-7554052.448134966</v>
       </c>
       <c r="Q83" t="n">
-        <v>-9720463.344178906</v>
+        <v>-7554052.448134966</v>
       </c>
     </row>
     <row r="84">
@@ -6488,19 +6488,19 @@
         <v>0.6666666666666667</v>
       </c>
       <c r="H84" t="n">
-        <v>-201932841.91</v>
+        <v>-243337598.87</v>
       </c>
       <c r="I84" t="n">
-        <v>-50972657.53424658</v>
+        <v>-89950783.56164384</v>
       </c>
       <c r="J84" t="n">
-        <v>-252905499.4442466</v>
+        <v>-333288382.4316438</v>
       </c>
       <c r="K84" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L84" t="n">
-        <v>-184905499.4442466</v>
+        <v>-271288382.4316438</v>
       </c>
       <c r="M84" t="n">
         <v>0.03873510939427094</v>
@@ -6512,10 +6512,10 @@
         <v>-0.0101121147124088</v>
       </c>
       <c r="P84" t="n">
-        <v>1246523.747556976</v>
+        <v>1828866.162195075</v>
       </c>
       <c r="Q84" t="n">
-        <v>623261.873778488</v>
+        <v>914433.0810975374</v>
       </c>
     </row>
     <row r="85">
@@ -6549,19 +6549,19 @@
         <v>0.5833333333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>-196825268.73</v>
+        <v>-241428019.53</v>
       </c>
       <c r="I85" t="n">
-        <v>-50988356.16438356</v>
+        <v>-89973452.05479452</v>
       </c>
       <c r="J85" t="n">
-        <v>-247813624.8943836</v>
+        <v>-331401471.5847945</v>
       </c>
       <c r="K85" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L85" t="n">
-        <v>-179813624.8943836</v>
+        <v>-269401471.5847945</v>
       </c>
       <c r="M85" t="n">
         <v>0.03888939094511485</v>
@@ -6573,10 +6573,10 @@
         <v>-0.0101405708492285</v>
       </c>
       <c r="P85" t="n">
-        <v>1063657.468357222</v>
+        <v>1593599.413870349</v>
       </c>
       <c r="Q85" t="n">
-        <v>531828.7341786108</v>
+        <v>796799.7069351746</v>
       </c>
     </row>
     <row r="86">
@@ -6610,19 +6610,19 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>69886647.3499999</v>
+        <v>149216557.22</v>
       </c>
       <c r="I86" t="n">
         <v>-89968608.21917808</v>
       </c>
       <c r="J86" t="n">
-        <v>-20081960.86917818</v>
+        <v>59247949.00082195</v>
       </c>
       <c r="K86" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L86" t="n">
-        <v>13918039.13082182</v>
+        <v>90247949.00082195</v>
       </c>
       <c r="M86" t="n">
         <v>0.03901400018340251</v>
@@ -6634,10 +6634,10 @@
         <v>-0.01016949446707605</v>
       </c>
       <c r="P86" t="n">
-        <v>-70769.71096672022</v>
+        <v>-458888.00901441</v>
       </c>
       <c r="Q86" t="n">
-        <v>-70769.71096672022</v>
+        <v>-458888.00901441</v>
       </c>
     </row>
     <row r="87">
@@ -6671,19 +6671,19 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>-81388394.01999998</v>
+        <v>116432754.21</v>
       </c>
       <c r="I87" t="n">
         <v>2250000</v>
       </c>
       <c r="J87" t="n">
-        <v>-79138394.01999998</v>
+        <v>118682754.21</v>
       </c>
       <c r="K87" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L87" t="n">
-        <v>-45138394.01999998</v>
+        <v>149682754.21</v>
       </c>
       <c r="M87" t="n">
         <v>0.03908855826627113</v>
@@ -6695,10 +6695,10 @@
         <v>-0.01019737062440143</v>
       </c>
       <c r="P87" t="n">
-        <v>191788.7221717521</v>
+        <v>-635987.7169835642</v>
       </c>
       <c r="Q87" t="n">
-        <v>95894.36108587607</v>
+        <v>-635987.7169835642</v>
       </c>
     </row>
     <row r="88">
@@ -6732,19 +6732,19 @@
         <v>0.3333333333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>-24300588.46000001</v>
+        <v>-21021772.08000001</v>
       </c>
       <c r="I88" t="n">
         <v>2250000</v>
       </c>
       <c r="J88" t="n">
-        <v>-22050588.46000001</v>
+        <v>-18771772.08000001</v>
       </c>
       <c r="K88" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L88" t="n">
-        <v>11949411.53999999</v>
+        <v>12228227.91999999</v>
       </c>
       <c r="M88" t="n">
         <v>0.03915884386251234</v>
@@ -6756,10 +6756,10 @@
         <v>-0.0102268186216663</v>
       </c>
       <c r="P88" t="n">
-        <v>-40734.82148507537</v>
+        <v>-41685.28966741191</v>
       </c>
       <c r="Q88" t="n">
-        <v>-40734.82148507537</v>
+        <v>-41685.28966741191</v>
       </c>
     </row>
     <row r="89">
@@ -6793,19 +6793,19 @@
         <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>-25229792.01000001</v>
+        <v>-19025601.68</v>
       </c>
       <c r="I89" t="n">
         <v>2250000</v>
       </c>
       <c r="J89" t="n">
-        <v>-22979792.01000001</v>
+        <v>-16775601.68</v>
       </c>
       <c r="K89" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L89" t="n">
-        <v>11020207.98999999</v>
+        <v>14224398.32</v>
       </c>
       <c r="M89" t="n">
         <v>0.03922681220647117</v>
@@ -6817,10 +6817,10 @@
         <v>-0.01025547675463123</v>
       </c>
       <c r="P89" t="n">
-        <v>-28254.37171816158</v>
+        <v>-36469.49657984389</v>
       </c>
       <c r="Q89" t="n">
-        <v>-28254.37171816158</v>
+        <v>-36469.49657984389</v>
       </c>
     </row>
     <row r="90">
@@ -6854,19 +6854,19 @@
         <v>0.1666666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>43083900.58</v>
+        <v>101044465.29</v>
       </c>
       <c r="I90" t="n">
         <v>2250000</v>
       </c>
       <c r="J90" t="n">
-        <v>45333900.58</v>
+        <v>103294465.29</v>
       </c>
       <c r="K90" t="n">
-        <v>-34000000</v>
+        <v>-31000000</v>
       </c>
       <c r="L90" t="n">
-        <v>79333900.58</v>
+        <v>134294465.29</v>
       </c>
       <c r="M90" t="n">
         <v>0.03929424848359133</v>
@@ -6878,10 +6878,10 @@
         <v>-0.01028445871969606</v>
       </c>
       <c r="P90" t="n">
-        <v>-135984.3709312468</v>
+        <v>-230190.9807597766</v>
       </c>
       <c r="Q90" t="n">
-        <v>-135984.3709312468</v>
+        <v>-230190.9807597766</v>
       </c>
     </row>
     <row r="91">
@@ -6915,19 +6915,19 @@
         <v>0.08333333333333337</v>
       </c>
       <c r="H91" t="n">
-        <v>32635075.89</v>
+        <v>34292018.08</v>
       </c>
       <c r="I91" t="n">
         <v>2262328.767123288</v>
       </c>
       <c r="J91" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>34897404.65712329</v>
+        <v>36554346.84712329</v>
       </c>
       <c r="M91" t="n">
         <v>0.03936107056455495</v>
@@ -6939,10 +6939,10 @@
         <v>-0.01031343600303951</v>
       </c>
       <c r="P91" t="n">
-        <v>-29992.67913361784</v>
+        <v>-31416.7430700596</v>
       </c>
       <c r="Q91" t="n">
-        <v>-29992.67913361784</v>
+        <v>-31416.7430700596</v>
       </c>
     </row>
     <row r="92">
@@ -6976,19 +6976,19 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-85065078.76000001</v>
+        <v>-76962502.42</v>
       </c>
       <c r="I92" t="n">
         <v>4045068.493150685</v>
       </c>
       <c r="J92" t="n">
-        <v>-81020010.26684932</v>
+        <v>-72917433.92684932</v>
       </c>
       <c r="K92" t="n">
-        <v>-68000000</v>
+        <v>-62000000</v>
       </c>
       <c r="L92" t="n">
-        <v>-13020010.26684932</v>
+        <v>-10917433.92684932</v>
       </c>
       <c r="M92" t="n">
         <v>0.03942868733737526</v>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42411854.98000002</v>
+        <v>38693708.36000007</v>
       </c>
       <c r="D2" t="n">
-        <v>21205927.49000001</v>
+        <v>19346854.18000004</v>
       </c>
       <c r="E2" t="n">
-        <v>3.534321248333335</v>
+        <v>3.224475696666672</v>
       </c>
       <c r="F2" t="n">
-        <v>1.767160624166668</v>
+        <v>1.612237848333336</v>
       </c>
     </row>
     <row r="3">
@@ -7088,16 +7088,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-45895908.52000004</v>
+        <v>-42208098.56999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-45895908.52000004</v>
+        <v>-42208098.56999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.824659043333337</v>
+        <v>-3.5173415475</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.824659043333337</v>
+        <v>-3.5173415475</v>
       </c>
     </row>
     <row r="4">
@@ -7112,16 +7112,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22464775.51999998</v>
+        <v>23719590.56</v>
       </c>
       <c r="D4" t="n">
-        <v>11232387.75999999</v>
+        <v>11859795.28</v>
       </c>
       <c r="E4" t="n">
-        <v>1.872064626666665</v>
+        <v>1.976632546666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9360323133333326</v>
+        <v>0.9883162733333334</v>
       </c>
     </row>
     <row r="5">
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-22015439.62</v>
+        <v>-23887034.91999996</v>
       </c>
       <c r="D5" t="n">
-        <v>-22015439.62</v>
+        <v>-23887034.91999996</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.834619968333334</v>
+        <v>-1.99058624333333</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.834619968333334</v>
+        <v>-1.99058624333333</v>
       </c>
     </row>
     <row r="6">
@@ -7160,16 +7160,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2133251.070000052</v>
+        <v>-5286286.149999976</v>
       </c>
       <c r="D6" t="n">
-        <v>-2133251.070000052</v>
+        <v>-5286286.149999976</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1777709225000044</v>
+        <v>-0.4405238458333314</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1777709225000044</v>
+        <v>-0.4405238458333314</v>
       </c>
     </row>
     <row r="7">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1516111.100000024</v>
+        <v>1547548.280000031</v>
       </c>
       <c r="D7" t="n">
-        <v>-1516111.100000024</v>
+        <v>773774.1400000155</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1263425916666686</v>
+        <v>0.1289623566666692</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1263425916666686</v>
+        <v>0.06448117833333462</v>
       </c>
     </row>
     <row r="8">
@@ -7208,16 +7208,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-19388537.42000002</v>
+        <v>-17917160.22999996</v>
       </c>
       <c r="D8" t="n">
-        <v>-19388537.42000002</v>
+        <v>-17917160.22999996</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.615711451666668</v>
+        <v>-1.49309668583333</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.615711451666668</v>
+        <v>-1.49309668583333</v>
       </c>
     </row>
   </sheetData>
